--- a/projetos/gestao-ia-planilhas/produto/kit-medicos/11-repasse-e-pro-labore.xlsx
+++ b/projetos/gestao-ia-planilhas/produto/kit-medicos/11-repasse-e-pro-labore.xlsx
@@ -736,7 +736,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B17"/>
+  <dimension ref="A1:B18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -909,17 +909,29 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>Clínica Vida Plena é uma clínica fictícia. Pacientes, convênios, nomes, contatos e valores são inventados; não há nenhum dado clínico. Apague o exemplo antes de começar. Agenda futura e vencimentos em aberto do exemplo são relativos a hoje.</t>
+          <t>Clínica Vida Plena é uma clínica fictícia. Pacientes, convênios, nomes, contatos e valores são inventados; não há nenhum dado clínico. Apague o exemplo antes de começar.</t>
         </is>
       </c>
     </row>
     <row r="17" ht="46" customHeight="1">
       <c r="A17" s="3" t="inlineStr">
         <is>
+          <t>Data de referência</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>O exemplo está congelado em 14/09/2026, para todos os arquivos do kit mostrarem a mesma foto e os números fecharem entre eles. Ao começar a usar com os seus dados, troque a data de referência em Config por =HOJE(): daí em diante ela acompanha o dia.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="46" customHeight="1">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
           <t>Suporte</t>
         </is>
       </c>
-      <c r="B17" s="4" t="inlineStr">
+      <c r="B18" s="4" t="inlineStr">
         <is>
           <t>suporte@seusociogestor.com.br · resposta em até 5 dias úteis · reembolso em até 7 dias pelo mesmo canal.</t>
         </is>
@@ -1685,11 +1697,11 @@
       </c>
       <c r="H26" s="19">
         <f>IF(Config!$A$15="","",SUM($G$36:$G$39)*Config!$B$15)</f>
-        <v>1848.5675</v>
+        <v>3204.435</v>
       </c>
       <c r="I26" s="19">
         <f>IF(Config!$A$15="","",SUMIFS(Retiradas!$E$5:$E$404,Retiradas!$B$5:$B$404,Config!$A$15,Retiradas!$C$5:$C$404,"Distribuição de lucro",Retiradas!$G$5:$G$404,"&lt;="&amp;Config!$B$7,Retiradas!$H$5:$H$404,Config!$B$5))</f>
-        <v>1848</v>
+        <v>3204</v>
       </c>
       <c r="J26" s="20">
         <f>IF(Config!$A$15="","",IF(ABS(H26-I26)&lt;1,0,H26-I26))</f>
@@ -1727,11 +1739,11 @@
       </c>
       <c r="H27" s="19">
         <f>IF(Config!$A$16="","",SUM($G$36:$G$39)*Config!$B$16)</f>
-        <v>1848.5675</v>
+        <v>3204.435</v>
       </c>
       <c r="I27" s="19">
         <f>IF(Config!$A$16="","",SUMIFS(Retiradas!$E$5:$E$404,Retiradas!$B$5:$B$404,Config!$A$16,Retiradas!$C$5:$C$404,"Distribuição de lucro",Retiradas!$G$5:$G$404,"&lt;="&amp;Config!$B$7,Retiradas!$H$5:$H$404,Config!$B$5))</f>
-        <v>1849</v>
+        <v>3205</v>
       </c>
       <c r="J27" s="20">
         <f>IF(Config!$A$16="","",IF(ABS(H27-I27)&lt;1,0,H27-I27))</f>
@@ -1976,11 +1988,11 @@
       </c>
       <c r="B36" s="19">
         <f>SUM('Resultado mensal'!B5:B7)</f>
-        <v>106395</v>
+        <v>91500</v>
       </c>
       <c r="C36" s="19">
         <f>SUM('Resultado mensal'!C5:C7)</f>
-        <v>54736.09</v>
+        <v>53443.72</v>
       </c>
       <c r="D36" s="19">
         <f>SUM('Resultado mensal'!D5:D7)</f>
@@ -1988,7 +2000,7 @@
       </c>
       <c r="E36" s="19">
         <f>SUM('Resultado mensal'!E5:E7)</f>
-        <v>-2341.09</v>
+        <v>-15943.72</v>
       </c>
       <c r="F36" s="23" t="str">
         <f>IF(Config!$B$7&gt;3,"Sim","Em andamento")</f>
@@ -2015,11 +2027,11 @@
       </c>
       <c r="B37" s="19">
         <f>SUM('Resultado mensal'!B8:B10)</f>
-        <v>127840</v>
+        <v>132775</v>
       </c>
       <c r="C37" s="19">
         <f>SUM('Resultado mensal'!C8:C10)</f>
-        <v>66445.73</v>
+        <v>65957.26</v>
       </c>
       <c r="D37" s="19">
         <f>SUM('Resultado mensal'!D8:D10)</f>
@@ -2027,7 +2039,7 @@
       </c>
       <c r="E37" s="19">
         <f>SUM('Resultado mensal'!E8:E10)</f>
-        <v>7394.27</v>
+        <v>12817.74</v>
       </c>
       <c r="F37" s="23" t="str">
         <f>IF(Config!$B$7&gt;6,"Sim","Em andamento")</f>
@@ -2035,11 +2047,11 @@
       </c>
       <c r="G37" s="20">
         <f>IF(AND(F37="Sim",E37&gt;=Config!$B$10),E37*Config!$B$9,0)</f>
-        <v>3697.135</v>
+        <v>6408.87</v>
       </c>
       <c r="H37" s="19">
         <f>SUMIFS(Retiradas!$E$5:$E$404,Retiradas!$C$5:$C$404,"Distribuição de lucro",Retiradas!$F$5:$F$404,A37,Retiradas!$H$5:$H$404,Config!$B$5)</f>
-        <v>3697</v>
+        <v>6409</v>
       </c>
       <c r="I37" s="19">
         <f>IF(ABS(G37-H37)&lt;1,0,G37-H37)</f>
@@ -2054,11 +2066,11 @@
       </c>
       <c r="B38" s="19">
         <f>SUM('Resultado mensal'!B11:B13)</f>
-        <v>125032</v>
+        <v>121022</v>
       </c>
       <c r="C38" s="19">
         <f>SUM('Resultado mensal'!C11:C13)</f>
-        <v>58189.89</v>
+        <v>57441.21</v>
       </c>
       <c r="D38" s="19">
         <f>SUM('Resultado mensal'!D11:D13)</f>
@@ -2066,7 +2078,7 @@
       </c>
       <c r="E38" s="19">
         <f>SUM('Resultado mensal'!E11:E13)</f>
-        <v>12842.11</v>
+        <v>9580.79</v>
       </c>
       <c r="F38" s="23" t="str">
         <f>IF(Config!$B$7&gt;9,"Sim","Em andamento")</f>
@@ -4404,10 +4416,10 @@
         </is>
       </c>
       <c r="B5" s="31" t="n">
-        <v>33270</v>
+        <v>25310</v>
       </c>
       <c r="C5" s="31" t="n">
-        <v>18200.56</v>
+        <v>17932.05</v>
       </c>
       <c r="D5" s="43">
         <f>IF(AND(B5="",C5=""),0,Config!$C$21)</f>
@@ -4415,7 +4427,7 @@
       </c>
       <c r="E5" s="43">
         <f>B5-C5-D5</f>
-        <v>-2930.56</v>
+        <v>-10622.05</v>
       </c>
       <c r="F5" s="23" t="inlineStr">
         <is>
@@ -4430,10 +4442,10 @@
         </is>
       </c>
       <c r="B6" s="31" t="n">
-        <v>24795</v>
+        <v>25650</v>
       </c>
       <c r="C6" s="31" t="n">
-        <v>18470.28</v>
+        <v>17610.54</v>
       </c>
       <c r="D6" s="43">
         <f>IF(AND(B6="",C6=""),0,Config!$C$21)</f>
@@ -4441,7 +4453,7 @@
       </c>
       <c r="E6" s="43">
         <f>B6-C6-D6</f>
-        <v>-11675.28</v>
+        <v>-9960.54</v>
       </c>
       <c r="F6" s="23" t="inlineStr">
         <is>
@@ -4456,10 +4468,10 @@
         </is>
       </c>
       <c r="B7" s="31" t="n">
-        <v>48330</v>
+        <v>40540</v>
       </c>
       <c r="C7" s="31" t="n">
-        <v>18065.25</v>
+        <v>17901.13</v>
       </c>
       <c r="D7" s="43">
         <f>IF(AND(B7="",C7=""),0,Config!$C$21)</f>
@@ -4467,7 +4479,7 @@
       </c>
       <c r="E7" s="43">
         <f>B7-C7-D7</f>
-        <v>12264.75</v>
+        <v>4638.87</v>
       </c>
       <c r="F7" s="23" t="inlineStr">
         <is>
@@ -4482,10 +4494,10 @@
         </is>
       </c>
       <c r="B8" s="31" t="n">
-        <v>38935</v>
+        <v>40155</v>
       </c>
       <c r="C8" s="31" t="n">
-        <v>23061.7</v>
+        <v>22254.1</v>
       </c>
       <c r="D8" s="43">
         <f>IF(AND(B8="",C8=""),0,Config!$C$21)</f>
@@ -4493,7 +4505,7 @@
       </c>
       <c r="E8" s="43">
         <f>B8-C8-D8</f>
-        <v>-2126.7</v>
+        <v>-99.0999999999985</v>
       </c>
       <c r="F8" s="23" t="inlineStr">
         <is>
@@ -4508,10 +4520,10 @@
         </is>
       </c>
       <c r="B9" s="31" t="n">
-        <v>44745</v>
+        <v>45380</v>
       </c>
       <c r="C9" s="31" t="n">
-        <v>21352.12</v>
+        <v>21500.29</v>
       </c>
       <c r="D9" s="43">
         <f>IF(AND(B9="",C9=""),0,Config!$C$21)</f>
@@ -4519,7 +4531,7 @@
       </c>
       <c r="E9" s="43">
         <f>B9-C9-D9</f>
-        <v>5392.88</v>
+        <v>5879.71</v>
       </c>
       <c r="F9" s="23" t="inlineStr">
         <is>
@@ -4534,10 +4546,10 @@
         </is>
       </c>
       <c r="B10" s="31" t="n">
-        <v>44160</v>
+        <v>47240</v>
       </c>
       <c r="C10" s="31" t="n">
-        <v>22031.91</v>
+        <v>22202.87</v>
       </c>
       <c r="D10" s="43">
         <f>IF(AND(B10="",C10=""),0,Config!$C$21)</f>
@@ -4545,7 +4557,7 @@
       </c>
       <c r="E10" s="43">
         <f>B10-C10-D10</f>
-        <v>4128.09</v>
+        <v>7037.13</v>
       </c>
       <c r="F10" s="23" t="inlineStr">
         <is>
@@ -4560,10 +4572,10 @@
         </is>
       </c>
       <c r="B11" s="31" t="n">
-        <v>53461</v>
+        <v>44471</v>
       </c>
       <c r="C11" s="31" t="n">
-        <v>21519.77</v>
+        <v>21562.6</v>
       </c>
       <c r="D11" s="43">
         <f>IF(AND(B11="",C11=""),0,Config!$C$21)</f>
@@ -4571,7 +4583,7 @@
       </c>
       <c r="E11" s="43">
         <f>B11-C11-D11</f>
-        <v>13941.23</v>
+        <v>4908.4</v>
       </c>
       <c r="F11" s="23" t="inlineStr">
         <is>
@@ -4586,10 +4598,10 @@
         </is>
       </c>
       <c r="B12" s="31" t="n">
-        <v>49651</v>
+        <v>55841</v>
       </c>
       <c r="C12" s="31" t="n">
-        <v>23040.12</v>
+        <v>22248.61</v>
       </c>
       <c r="D12" s="43">
         <f>IF(AND(B12="",C12=""),0,Config!$C$21)</f>
@@ -4597,7 +4609,7 @@
       </c>
       <c r="E12" s="43">
         <f>B12-C12-D12</f>
-        <v>8610.88</v>
+        <v>15592.39</v>
       </c>
       <c r="F12" s="23" t="inlineStr">
         <is>
@@ -4612,7 +4624,7 @@
         </is>
       </c>
       <c r="B13" s="31" t="n">
-        <v>21920</v>
+        <v>20710</v>
       </c>
       <c r="C13" s="31" t="n">
         <v>13630</v>
@@ -4623,7 +4635,7 @@
       </c>
       <c r="E13" s="43">
         <f>B13-C13-D13</f>
-        <v>-9710</v>
+        <v>-10920</v>
       </c>
       <c r="F13" s="23" t="inlineStr">
         <is>
@@ -5390,7 +5402,7 @@
         </is>
       </c>
       <c r="E23" s="31" t="n">
-        <v>1849</v>
+        <v>3205</v>
       </c>
       <c r="F23" s="27" t="inlineStr">
         <is>
@@ -5426,7 +5438,7 @@
         </is>
       </c>
       <c r="E24" s="31" t="n">
-        <v>1848</v>
+        <v>3204</v>
       </c>
       <c r="F24" s="27" t="inlineStr">
         <is>

--- a/projetos/gestao-ia-planilhas/produto/kit-medicos/11-repasse-e-pro-labore.xlsx
+++ b/projetos/gestao-ia-planilhas/produto/kit-medicos/11-repasse-e-pro-labore.xlsx
@@ -23,11 +23,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
-    <numFmt numFmtId="164" formatCode="&quot;R$&quot; #,##0.00;[Red]-&quot;R$&quot; #,##0.00"/>
-    <numFmt numFmtId="165" formatCode="&quot;R$&quot; #,##0;[Red]-&quot;R$&quot; #,##0"/>
-    <numFmt numFmtId="166" formatCode="#,##0.0"/>
-    <numFmt numFmtId="167" formatCode="dd/mm/yyyy"/>
+  <numFmts count="5">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="165" formatCode="&quot;R$&quot; #,##0.00;[Red]-&quot;R$&quot; #,##0.00"/>
+    <numFmt numFmtId="166" formatCode="dd/mm/yyyy"/>
+    <numFmt numFmtId="167" formatCode="&quot;R$&quot; #,##0;[Red]-&quot;R$&quot; #,##0"/>
+    <numFmt numFmtId="168" formatCode="#,##0.0"/>
   </numFmts>
   <fonts count="17">
     <font>
@@ -186,7 +187,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -212,13 +213,13 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="1" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="1" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="1" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="1" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="13" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="13" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -228,13 +229,13 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -262,37 +263,43 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="4" fillId="2" borderId="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="2" borderId="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <protection locked="0" hidden="0"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="4" fillId="2" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
       <protection locked="0" hidden="0"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="4" fillId="2" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="4" fillId="2" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="166" fontId="4" fillId="2" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="168" fontId="4" fillId="2" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
       <protection locked="0" hidden="0"/>
     </xf>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="167" fontId="4" fillId="2" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="4" fillId="2" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="9" fillId="2" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -2003,7 +2010,7 @@
         <v>-15943.72</v>
       </c>
       <c r="F36" s="23" t="str">
-        <f>IF(Config!$B$7&gt;3,"Sim","Em andamento")</f>
+        <f>IF(AND(Config!$B$12&gt;=DATE(Config!$B$5,4,1),COUNT('Resultado mensal'!B5:B7)&gt;=3),"Sim","Em andamento")</f>
         <v>Sim</v>
       </c>
       <c r="G36" s="20">
@@ -2042,7 +2049,7 @@
         <v>12817.74</v>
       </c>
       <c r="F37" s="23" t="str">
-        <f>IF(Config!$B$7&gt;6,"Sim","Em andamento")</f>
+        <f>IF(AND(Config!$B$12&gt;=DATE(Config!$B$5,7,1),COUNT('Resultado mensal'!B8:B10)&gt;=3),"Sim","Em andamento")</f>
         <v>Sim</v>
       </c>
       <c r="G37" s="20">
@@ -2081,7 +2088,7 @@
         <v>9580.79</v>
       </c>
       <c r="F38" s="23" t="str">
-        <f>IF(Config!$B$7&gt;9,"Sim","Em andamento")</f>
+        <f>IF(AND(Config!$B$12&gt;=DATE(Config!$B$5,10,1),COUNT('Resultado mensal'!B11:B13)&gt;=3),"Sim","Em andamento")</f>
         <v>Em andamento</v>
       </c>
       <c r="G38" s="20">
@@ -2120,7 +2127,7 @@
         <v>0</v>
       </c>
       <c r="F39" s="23" t="str">
-        <f>IF(Config!$B$7&gt;12,"Sim","Em andamento")</f>
+        <f>IF(AND(Config!$B$12&gt;=DATE(Config!$B$5+1,1,1),COUNT('Resultado mensal'!B14:B16)&gt;=3),"Sim","Em andamento")</f>
         <v>Em andamento</v>
       </c>
       <c r="G39" s="20">
@@ -2426,6 +2433,14 @@
       </c>
     </row>
     <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Data de referência</t>
+        </is>
+      </c>
+      <c r="B12" s="32" t="n">
+        <v>46279</v>
+      </c>
       <c r="H12" s="28" t="inlineStr">
         <is>
           <t>Agosto</t>
@@ -2523,20 +2538,20 @@
       <c r="C20" s="31" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="32" t="inlineStr">
+      <c r="A21" s="33" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B21" s="33">
+      <c r="B21" s="34">
         <f>SUM(B15:B20)</f>
         <v>1</v>
       </c>
-      <c r="C21" s="34">
+      <c r="C21" s="35">
         <f>SUM(C15:C20)</f>
         <v>18000</v>
       </c>
-      <c r="D21" s="35">
+      <c r="D21" s="36">
         <f>IF(ROUND(B21,4)=1,"","A participação deve somar 100 %")</f>
         <v/>
       </c>
@@ -2584,7 +2599,7 @@
           <t>Produção do mês</t>
         </is>
       </c>
-      <c r="D25" s="36" t="n">
+      <c r="D25" s="37" t="n">
         <v>10</v>
       </c>
     </row>
@@ -2592,29 +2607,29 @@
       <c r="A26" s="26" t="n"/>
       <c r="B26" s="29" t="n"/>
       <c r="C26" s="27" t="n"/>
-      <c r="D26" s="36" t="n"/>
+      <c r="D26" s="37" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="26" t="n"/>
       <c r="B27" s="29" t="n"/>
       <c r="C27" s="27" t="n"/>
-      <c r="D27" s="36" t="n"/>
+      <c r="D27" s="37" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="26" t="n"/>
       <c r="B28" s="29" t="n"/>
       <c r="C28" s="27" t="n"/>
-      <c r="D28" s="36" t="n"/>
+      <c r="D28" s="37" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="37" t="inlineStr">
-        <is>
-          <t>Preencha de cima para baixo, sem pular linha. Repasse sobre a produção: o parceiro recebe pelo que atendeu, e a glosa do convênio fica com a clínica. Sobre o recebido: o parceiro espera o convênio pagar. Combine por escrito; a planilha só calcula.</t>
+      <c r="A29" s="38" t="inlineStr">
+        <is>
+          <t>Preencha de cima para baixo, sem pular linha. Repasse sobre a produção: o parceiro recebe pelo que atendeu, e a glosa do convênio fica com a clínica; a planilha usa a coluna "Produção do mês" da aba Repasse. Sobre o recebido: o parceiro espera o convênio pagar, e aí você precisa preencher a coluna "Recebido no mês" da aba Repasse — é ela que a planilha usa nesse caso. Combine por escrito; a planilha só calcula.</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="37" t="inlineStr">
+      <c r="A30" s="38" t="inlineStr">
         <is>
           <t>Pró-labore fixo: o valor combinado que cada sócio retira todo mês. Retirada extra e despesa pessoal paga pela clínica são o que passou do combinado.</t>
         </is>
@@ -2752,6 +2767,11 @@
           <t>Custo indireto das horas (informativo, R$)</t>
         </is>
       </c>
+      <c r="O4" s="17" t="inlineStr">
+        <is>
+          <t>Recebido no mês (R$) · só se o acordo for sobre o recebido</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="27" t="inlineStr">
@@ -2767,24 +2787,24 @@
           <t>Dra. Renata Sousa</t>
         </is>
       </c>
-      <c r="D5" s="38" t="n">
+      <c r="D5" s="39" t="n">
         <v>7450</v>
       </c>
-      <c r="E5" s="39" t="n">
+      <c r="E5" s="40" t="n">
         <v>17.7</v>
       </c>
-      <c r="F5" s="40">
+      <c r="F5" s="41">
         <f>IF(C5="","",IFERROR(INDEX(Config!$B$25:$B$28,MATCH(C5,Config!$A$25:$A$28,0)),""))</f>
         <v>0.5</v>
       </c>
       <c r="G5" s="19">
-        <f>IF(OR(C5="",D5="",F5=""),"",ROUND(D5*F5,0))</f>
+        <f>IF(OR(C5="",F5=""),"",IF(IF(IFERROR(INDEX(Config!$C$25:$C$28,MATCH(C5,Config!$A$25:$A$28,0)),"Produção do mês")="Recebido no mês",N(O5),N(D5))=0,"",ROUND(IF(IFERROR(INDEX(Config!$C$25:$C$28,MATCH(C5,Config!$A$25:$A$28,0)),"Produção do mês")="Recebido no mês",N(O5),N(D5))*F5,0)))</f>
         <v>3725</v>
       </c>
-      <c r="H5" s="41" t="n">
+      <c r="H5" s="42" t="n">
         <v>46063</v>
       </c>
-      <c r="I5" s="38" t="n">
+      <c r="I5" s="39" t="n">
         <v>3725</v>
       </c>
       <c r="J5" s="19">
@@ -2795,7 +2815,7 @@
         <f>IF(G5="","",D5-G5)</f>
         <v>3725</v>
       </c>
-      <c r="L5" s="38" t="n">
+      <c r="L5" s="39" t="n">
         <v>106</v>
       </c>
       <c r="M5" s="19">
@@ -2806,7 +2826,7 @@
         <f>IF(OR(G5="",E5=""),"",E5*Config!$B$11)</f>
         <v>1264.28622</v>
       </c>
-      <c r="O5" s="42">
+      <c r="O5" s="43">
         <f>IF(A5="","",MATCH(A5,Config!$H$5:$H$16,0))</f>
         <v>1</v>
       </c>
@@ -2825,24 +2845,24 @@
           <t>Dra. Renata Sousa</t>
         </is>
       </c>
-      <c r="D6" s="38" t="n">
+      <c r="D6" s="39" t="n">
         <v>6510</v>
       </c>
-      <c r="E6" s="39" t="n">
+      <c r="E6" s="40" t="n">
         <v>18.3</v>
       </c>
-      <c r="F6" s="40">
+      <c r="F6" s="41">
         <f>IF(C6="","",IFERROR(INDEX(Config!$B$25:$B$28,MATCH(C6,Config!$A$25:$A$28,0)),""))</f>
         <v>0.5</v>
       </c>
       <c r="G6" s="19">
-        <f>IF(OR(C6="",D6="",F6=""),"",ROUND(D6*F6,0))</f>
+        <f>IF(OR(C6="",F6=""),"",IF(IF(IFERROR(INDEX(Config!$C$25:$C$28,MATCH(C6,Config!$A$25:$A$28,0)),"Produção do mês")="Recebido no mês",N(O6),N(D6))=0,"",ROUND(IF(IFERROR(INDEX(Config!$C$25:$C$28,MATCH(C6,Config!$A$25:$A$28,0)),"Produção do mês")="Recebido no mês",N(O6),N(D6))*F6,0)))</f>
         <v>3255</v>
       </c>
-      <c r="H6" s="41" t="n">
+      <c r="H6" s="42" t="n">
         <v>46091</v>
       </c>
-      <c r="I6" s="38" t="n">
+      <c r="I6" s="39" t="n">
         <v>3255</v>
       </c>
       <c r="J6" s="19">
@@ -2853,7 +2873,7 @@
         <f>IF(G6="","",D6-G6)</f>
         <v>3255</v>
       </c>
-      <c r="L6" s="38" t="n">
+      <c r="L6" s="39" t="n">
         <v>110</v>
       </c>
       <c r="M6" s="19">
@@ -2864,7 +2884,7 @@
         <f>IF(OR(G6="",E6=""),"",E6*Config!$B$11)</f>
         <v>1307.14338</v>
       </c>
-      <c r="O6" s="42">
+      <c r="O6" s="43">
         <f>IF(A6="","",MATCH(A6,Config!$H$5:$H$16,0))</f>
         <v>2</v>
       </c>
@@ -2883,24 +2903,24 @@
           <t>Dra. Renata Sousa</t>
         </is>
       </c>
-      <c r="D7" s="38" t="n">
+      <c r="D7" s="39" t="n">
         <v>12100</v>
       </c>
-      <c r="E7" s="39" t="n">
+      <c r="E7" s="40" t="n">
         <v>28</v>
       </c>
-      <c r="F7" s="40">
+      <c r="F7" s="41">
         <f>IF(C7="","",IFERROR(INDEX(Config!$B$25:$B$28,MATCH(C7,Config!$A$25:$A$28,0)),""))</f>
         <v>0.5</v>
       </c>
       <c r="G7" s="19">
-        <f>IF(OR(C7="",D7="",F7=""),"",ROUND(D7*F7,0))</f>
+        <f>IF(OR(C7="",F7=""),"",IF(IF(IFERROR(INDEX(Config!$C$25:$C$28,MATCH(C7,Config!$A$25:$A$28,0)),"Produção do mês")="Recebido no mês",N(O7),N(D7))=0,"",ROUND(IF(IFERROR(INDEX(Config!$C$25:$C$28,MATCH(C7,Config!$A$25:$A$28,0)),"Produção do mês")="Recebido no mês",N(O7),N(D7))*F7,0)))</f>
         <v>6050</v>
       </c>
-      <c r="H7" s="41" t="n">
+      <c r="H7" s="42" t="n">
         <v>46122</v>
       </c>
-      <c r="I7" s="38" t="n">
+      <c r="I7" s="39" t="n">
         <v>6050</v>
       </c>
       <c r="J7" s="19">
@@ -2911,7 +2931,7 @@
         <f>IF(G7="","",D7-G7)</f>
         <v>6050</v>
       </c>
-      <c r="L7" s="38" t="n">
+      <c r="L7" s="39" t="n">
         <v>168</v>
       </c>
       <c r="M7" s="19">
@@ -2922,7 +2942,7 @@
         <f>IF(OR(G7="",E7=""),"",E7*Config!$B$11)</f>
         <v>2000.0008</v>
       </c>
-      <c r="O7" s="42">
+      <c r="O7" s="43">
         <f>IF(A7="","",MATCH(A7,Config!$H$5:$H$16,0))</f>
         <v>3</v>
       </c>
@@ -2941,24 +2961,24 @@
           <t>Dra. Renata Sousa</t>
         </is>
       </c>
-      <c r="D8" s="38" t="n">
+      <c r="D8" s="39" t="n">
         <v>8770</v>
       </c>
-      <c r="E8" s="39" t="n">
+      <c r="E8" s="40" t="n">
         <v>24</v>
       </c>
-      <c r="F8" s="40">
+      <c r="F8" s="41">
         <f>IF(C8="","",IFERROR(INDEX(Config!$B$25:$B$28,MATCH(C8,Config!$A$25:$A$28,0)),""))</f>
         <v>0.5</v>
       </c>
       <c r="G8" s="19">
-        <f>IF(OR(C8="",D8="",F8=""),"",ROUND(D8*F8,0))</f>
+        <f>IF(OR(C8="",F8=""),"",IF(IF(IFERROR(INDEX(Config!$C$25:$C$28,MATCH(C8,Config!$A$25:$A$28,0)),"Produção do mês")="Recebido no mês",N(O8),N(D8))=0,"",ROUND(IF(IFERROR(INDEX(Config!$C$25:$C$28,MATCH(C8,Config!$A$25:$A$28,0)),"Produção do mês")="Recebido no mês",N(O8),N(D8))*F8,0)))</f>
         <v>4385</v>
       </c>
-      <c r="H8" s="41" t="n">
+      <c r="H8" s="42" t="n">
         <v>46152</v>
       </c>
-      <c r="I8" s="38" t="n">
+      <c r="I8" s="39" t="n">
         <v>4385</v>
       </c>
       <c r="J8" s="19">
@@ -2969,7 +2989,7 @@
         <f>IF(G8="","",D8-G8)</f>
         <v>4385</v>
       </c>
-      <c r="L8" s="38" t="n">
+      <c r="L8" s="39" t="n">
         <v>144</v>
       </c>
       <c r="M8" s="19">
@@ -2980,7 +3000,7 @@
         <f>IF(OR(G8="",E8=""),"",E8*Config!$B$11)</f>
         <v>1714.2864</v>
       </c>
-      <c r="O8" s="42">
+      <c r="O8" s="43">
         <f>IF(A8="","",MATCH(A8,Config!$H$5:$H$16,0))</f>
         <v>4</v>
       </c>
@@ -2999,24 +3019,24 @@
           <t>Dra. Renata Sousa</t>
         </is>
       </c>
-      <c r="D9" s="38" t="n">
+      <c r="D9" s="39" t="n">
         <v>10490</v>
       </c>
-      <c r="E9" s="39" t="n">
+      <c r="E9" s="40" t="n">
         <v>26.7</v>
       </c>
-      <c r="F9" s="40">
+      <c r="F9" s="41">
         <f>IF(C9="","",IFERROR(INDEX(Config!$B$25:$B$28,MATCH(C9,Config!$A$25:$A$28,0)),""))</f>
         <v>0.5</v>
       </c>
       <c r="G9" s="19">
-        <f>IF(OR(C9="",D9="",F9=""),"",ROUND(D9*F9,0))</f>
+        <f>IF(OR(C9="",F9=""),"",IF(IF(IFERROR(INDEX(Config!$C$25:$C$28,MATCH(C9,Config!$A$25:$A$28,0)),"Produção do mês")="Recebido no mês",N(O9),N(D9))=0,"",ROUND(IF(IFERROR(INDEX(Config!$C$25:$C$28,MATCH(C9,Config!$A$25:$A$28,0)),"Produção do mês")="Recebido no mês",N(O9),N(D9))*F9,0)))</f>
         <v>5245</v>
       </c>
-      <c r="H9" s="41" t="n">
+      <c r="H9" s="42" t="n">
         <v>46183</v>
       </c>
-      <c r="I9" s="38" t="n">
+      <c r="I9" s="39" t="n">
         <v>5245</v>
       </c>
       <c r="J9" s="19">
@@ -3027,7 +3047,7 @@
         <f>IF(G9="","",D9-G9)</f>
         <v>5245</v>
       </c>
-      <c r="L9" s="38" t="n">
+      <c r="L9" s="39" t="n">
         <v>160</v>
       </c>
       <c r="M9" s="19">
@@ -3038,7 +3058,7 @@
         <f>IF(OR(G9="",E9=""),"",E9*Config!$B$11)</f>
         <v>1907.14362</v>
       </c>
-      <c r="O9" s="42">
+      <c r="O9" s="43">
         <f>IF(A9="","",MATCH(A9,Config!$H$5:$H$16,0))</f>
         <v>5</v>
       </c>
@@ -3057,24 +3077,24 @@
           <t>Dra. Renata Sousa</t>
         </is>
       </c>
-      <c r="D10" s="38" t="n">
+      <c r="D10" s="39" t="n">
         <v>9440</v>
       </c>
-      <c r="E10" s="39" t="n">
+      <c r="E10" s="40" t="n">
         <v>24</v>
       </c>
-      <c r="F10" s="40">
+      <c r="F10" s="41">
         <f>IF(C10="","",IFERROR(INDEX(Config!$B$25:$B$28,MATCH(C10,Config!$A$25:$A$28,0)),""))</f>
         <v>0.5</v>
       </c>
       <c r="G10" s="19">
-        <f>IF(OR(C10="",D10="",F10=""),"",ROUND(D10*F10,0))</f>
+        <f>IF(OR(C10="",F10=""),"",IF(IF(IFERROR(INDEX(Config!$C$25:$C$28,MATCH(C10,Config!$A$25:$A$28,0)),"Produção do mês")="Recebido no mês",N(O10),N(D10))=0,"",ROUND(IF(IFERROR(INDEX(Config!$C$25:$C$28,MATCH(C10,Config!$A$25:$A$28,0)),"Produção do mês")="Recebido no mês",N(O10),N(D10))*F10,0)))</f>
         <v>4720</v>
       </c>
-      <c r="H10" s="41" t="n">
+      <c r="H10" s="42" t="n">
         <v>46213</v>
       </c>
-      <c r="I10" s="38" t="n">
+      <c r="I10" s="39" t="n">
         <v>4720</v>
       </c>
       <c r="J10" s="19">
@@ -3085,7 +3105,7 @@
         <f>IF(G10="","",D10-G10)</f>
         <v>4720</v>
       </c>
-      <c r="L10" s="38" t="n">
+      <c r="L10" s="39" t="n">
         <v>144</v>
       </c>
       <c r="M10" s="19">
@@ -3096,7 +3116,7 @@
         <f>IF(OR(G10="",E10=""),"",E10*Config!$B$11)</f>
         <v>1714.2864</v>
       </c>
-      <c r="O10" s="42">
+      <c r="O10" s="43">
         <f>IF(A10="","",MATCH(A10,Config!$H$5:$H$16,0))</f>
         <v>6</v>
       </c>
@@ -3115,24 +3135,24 @@
           <t>Dra. Renata Sousa</t>
         </is>
       </c>
-      <c r="D11" s="38" t="n">
+      <c r="D11" s="39" t="n">
         <v>9690</v>
       </c>
-      <c r="E11" s="39" t="n">
+      <c r="E11" s="40" t="n">
         <v>28</v>
       </c>
-      <c r="F11" s="40">
+      <c r="F11" s="41">
         <f>IF(C11="","",IFERROR(INDEX(Config!$B$25:$B$28,MATCH(C11,Config!$A$25:$A$28,0)),""))</f>
         <v>0.5</v>
       </c>
       <c r="G11" s="19">
-        <f>IF(OR(C11="",D11="",F11=""),"",ROUND(D11*F11,0))</f>
+        <f>IF(OR(C11="",F11=""),"",IF(IF(IFERROR(INDEX(Config!$C$25:$C$28,MATCH(C11,Config!$A$25:$A$28,0)),"Produção do mês")="Recebido no mês",N(O11),N(D11))=0,"",ROUND(IF(IFERROR(INDEX(Config!$C$25:$C$28,MATCH(C11,Config!$A$25:$A$28,0)),"Produção do mês")="Recebido no mês",N(O11),N(D11))*F11,0)))</f>
         <v>4845</v>
       </c>
-      <c r="H11" s="41" t="n">
+      <c r="H11" s="42" t="n">
         <v>46244</v>
       </c>
-      <c r="I11" s="38" t="n">
+      <c r="I11" s="39" t="n">
         <v>4845</v>
       </c>
       <c r="J11" s="19">
@@ -3143,7 +3163,7 @@
         <f>IF(G11="","",D11-G11)</f>
         <v>4845</v>
       </c>
-      <c r="L11" s="38" t="n">
+      <c r="L11" s="39" t="n">
         <v>168</v>
       </c>
       <c r="M11" s="19">
@@ -3154,7 +3174,7 @@
         <f>IF(OR(G11="",E11=""),"",E11*Config!$B$11)</f>
         <v>2000.0008</v>
       </c>
-      <c r="O11" s="42">
+      <c r="O11" s="43">
         <f>IF(A11="","",MATCH(A11,Config!$H$5:$H$16,0))</f>
         <v>7</v>
       </c>
@@ -3173,24 +3193,24 @@
           <t>Dra. Renata Sousa</t>
         </is>
       </c>
-      <c r="D12" s="38" t="n">
+      <c r="D12" s="39" t="n">
         <v>10380</v>
       </c>
-      <c r="E12" s="39" t="n">
+      <c r="E12" s="40" t="n">
         <v>23.7</v>
       </c>
-      <c r="F12" s="40">
+      <c r="F12" s="41">
         <f>IF(C12="","",IFERROR(INDEX(Config!$B$25:$B$28,MATCH(C12,Config!$A$25:$A$28,0)),""))</f>
         <v>0.5</v>
       </c>
       <c r="G12" s="19">
-        <f>IF(OR(C12="",D12="",F12=""),"",ROUND(D12*F12,0))</f>
+        <f>IF(OR(C12="",F12=""),"",IF(IF(IFERROR(INDEX(Config!$C$25:$C$28,MATCH(C12,Config!$A$25:$A$28,0)),"Produção do mês")="Recebido no mês",N(O12),N(D12))=0,"",ROUND(IF(IFERROR(INDEX(Config!$C$25:$C$28,MATCH(C12,Config!$A$25:$A$28,0)),"Produção do mês")="Recebido no mês",N(O12),N(D12))*F12,0)))</f>
         <v>5190</v>
       </c>
-      <c r="H12" s="41" t="n">
+      <c r="H12" s="42" t="n">
         <v>46275</v>
       </c>
-      <c r="I12" s="38" t="n">
+      <c r="I12" s="39" t="n">
         <v>5190</v>
       </c>
       <c r="J12" s="19">
@@ -3201,7 +3221,7 @@
         <f>IF(G12="","",D12-G12)</f>
         <v>5190</v>
       </c>
-      <c r="L12" s="38" t="n">
+      <c r="L12" s="39" t="n">
         <v>142</v>
       </c>
       <c r="M12" s="19">
@@ -3212,7 +3232,7 @@
         <f>IF(OR(G12="",E12=""),"",E12*Config!$B$11)</f>
         <v>1692.85782</v>
       </c>
-      <c r="O12" s="42">
+      <c r="O12" s="43">
         <f>IF(A12="","",MATCH(A12,Config!$H$5:$H$16,0))</f>
         <v>8</v>
       </c>
@@ -3231,22 +3251,22 @@
           <t>Dra. Renata Sousa</t>
         </is>
       </c>
-      <c r="D13" s="38" t="n">
+      <c r="D13" s="39" t="n">
         <v>5850</v>
       </c>
-      <c r="E13" s="39" t="n">
+      <c r="E13" s="40" t="n">
         <v>14</v>
       </c>
-      <c r="F13" s="40">
+      <c r="F13" s="41">
         <f>IF(C13="","",IFERROR(INDEX(Config!$B$25:$B$28,MATCH(C13,Config!$A$25:$A$28,0)),""))</f>
         <v>0.5</v>
       </c>
       <c r="G13" s="19">
-        <f>IF(OR(C13="",D13="",F13=""),"",ROUND(D13*F13,0))</f>
+        <f>IF(OR(C13="",F13=""),"",IF(IF(IFERROR(INDEX(Config!$C$25:$C$28,MATCH(C13,Config!$A$25:$A$28,0)),"Produção do mês")="Recebido no mês",N(O13),N(D13))=0,"",ROUND(IF(IFERROR(INDEX(Config!$C$25:$C$28,MATCH(C13,Config!$A$25:$A$28,0)),"Produção do mês")="Recebido no mês",N(O13),N(D13))*F13,0)))</f>
         <v>2925</v>
       </c>
-      <c r="H13" s="41" t="n"/>
-      <c r="I13" s="38" t="n"/>
+      <c r="H13" s="42" t="n"/>
+      <c r="I13" s="39" t="n"/>
       <c r="J13" s="19">
         <f>IF(G13="","",IF(I13="",G13,G13-I13))</f>
         <v>2925</v>
@@ -3255,7 +3275,7 @@
         <f>IF(G13="","",D13-G13)</f>
         <v>2925</v>
       </c>
-      <c r="L13" s="38" t="n">
+      <c r="L13" s="39" t="n">
         <v>84</v>
       </c>
       <c r="M13" s="19">
@@ -3266,7 +3286,7 @@
         <f>IF(OR(G13="",E13=""),"",E13*Config!$B$11)</f>
         <v>1000.0004</v>
       </c>
-      <c r="O13" s="42">
+      <c r="O13" s="43">
         <f>IF(A13="","",MATCH(A13,Config!$H$5:$H$16,0))</f>
         <v>9</v>
       </c>
@@ -3275,18 +3295,18 @@
       <c r="A14" s="27" t="n"/>
       <c r="B14" s="27" t="n"/>
       <c r="C14" s="26" t="n"/>
-      <c r="D14" s="38" t="n"/>
-      <c r="E14" s="39" t="n"/>
-      <c r="F14" s="40">
+      <c r="D14" s="39" t="n"/>
+      <c r="E14" s="40" t="n"/>
+      <c r="F14" s="41">
         <f>IF(C14="","",IFERROR(INDEX(Config!$B$25:$B$28,MATCH(C14,Config!$A$25:$A$28,0)),""))</f>
         <v/>
       </c>
       <c r="G14" s="19">
-        <f>IF(OR(C14="",D14="",F14=""),"",ROUND(D14*F14,0))</f>
-        <v/>
-      </c>
-      <c r="H14" s="41" t="n"/>
-      <c r="I14" s="38" t="n"/>
+        <f>IF(OR(C14="",F14=""),"",IF(IF(IFERROR(INDEX(Config!$C$25:$C$28,MATCH(C14,Config!$A$25:$A$28,0)),"Produção do mês")="Recebido no mês",N(O14),N(D14))=0,"",ROUND(IF(IFERROR(INDEX(Config!$C$25:$C$28,MATCH(C14,Config!$A$25:$A$28,0)),"Produção do mês")="Recebido no mês",N(O14),N(D14))*F14,0)))</f>
+        <v/>
+      </c>
+      <c r="H14" s="42" t="n"/>
+      <c r="I14" s="39" t="n"/>
       <c r="J14" s="19">
         <f>IF(G14="","",IF(I14="",G14,G14-I14))</f>
         <v/>
@@ -3295,7 +3315,7 @@
         <f>IF(G14="","",D14-G14)</f>
         <v/>
       </c>
-      <c r="L14" s="38" t="n"/>
+      <c r="L14" s="39" t="n"/>
       <c r="M14" s="19">
         <f>IF(G14="","",K14-N(L14))</f>
         <v/>
@@ -3304,7 +3324,7 @@
         <f>IF(OR(G14="",E14=""),"",E14*Config!$B$11)</f>
         <v/>
       </c>
-      <c r="O14" s="42">
+      <c r="O14" s="43">
         <f>IF(A14="","",MATCH(A14,Config!$H$5:$H$16,0))</f>
         <v/>
       </c>
@@ -3313,18 +3333,18 @@
       <c r="A15" s="27" t="n"/>
       <c r="B15" s="27" t="n"/>
       <c r="C15" s="26" t="n"/>
-      <c r="D15" s="38" t="n"/>
-      <c r="E15" s="39" t="n"/>
-      <c r="F15" s="40">
+      <c r="D15" s="39" t="n"/>
+      <c r="E15" s="40" t="n"/>
+      <c r="F15" s="41">
         <f>IF(C15="","",IFERROR(INDEX(Config!$B$25:$B$28,MATCH(C15,Config!$A$25:$A$28,0)),""))</f>
         <v/>
       </c>
       <c r="G15" s="19">
-        <f>IF(OR(C15="",D15="",F15=""),"",ROUND(D15*F15,0))</f>
-        <v/>
-      </c>
-      <c r="H15" s="41" t="n"/>
-      <c r="I15" s="38" t="n"/>
+        <f>IF(OR(C15="",F15=""),"",IF(IF(IFERROR(INDEX(Config!$C$25:$C$28,MATCH(C15,Config!$A$25:$A$28,0)),"Produção do mês")="Recebido no mês",N(O15),N(D15))=0,"",ROUND(IF(IFERROR(INDEX(Config!$C$25:$C$28,MATCH(C15,Config!$A$25:$A$28,0)),"Produção do mês")="Recebido no mês",N(O15),N(D15))*F15,0)))</f>
+        <v/>
+      </c>
+      <c r="H15" s="42" t="n"/>
+      <c r="I15" s="39" t="n"/>
       <c r="J15" s="19">
         <f>IF(G15="","",IF(I15="",G15,G15-I15))</f>
         <v/>
@@ -3333,7 +3353,7 @@
         <f>IF(G15="","",D15-G15)</f>
         <v/>
       </c>
-      <c r="L15" s="38" t="n"/>
+      <c r="L15" s="39" t="n"/>
       <c r="M15" s="19">
         <f>IF(G15="","",K15-N(L15))</f>
         <v/>
@@ -3342,7 +3362,7 @@
         <f>IF(OR(G15="",E15=""),"",E15*Config!$B$11)</f>
         <v/>
       </c>
-      <c r="O15" s="42">
+      <c r="O15" s="43">
         <f>IF(A15="","",MATCH(A15,Config!$H$5:$H$16,0))</f>
         <v/>
       </c>
@@ -3351,18 +3371,18 @@
       <c r="A16" s="27" t="n"/>
       <c r="B16" s="27" t="n"/>
       <c r="C16" s="26" t="n"/>
-      <c r="D16" s="38" t="n"/>
-      <c r="E16" s="39" t="n"/>
-      <c r="F16" s="40">
+      <c r="D16" s="39" t="n"/>
+      <c r="E16" s="40" t="n"/>
+      <c r="F16" s="41">
         <f>IF(C16="","",IFERROR(INDEX(Config!$B$25:$B$28,MATCH(C16,Config!$A$25:$A$28,0)),""))</f>
         <v/>
       </c>
       <c r="G16" s="19">
-        <f>IF(OR(C16="",D16="",F16=""),"",ROUND(D16*F16,0))</f>
-        <v/>
-      </c>
-      <c r="H16" s="41" t="n"/>
-      <c r="I16" s="38" t="n"/>
+        <f>IF(OR(C16="",F16=""),"",IF(IF(IFERROR(INDEX(Config!$C$25:$C$28,MATCH(C16,Config!$A$25:$A$28,0)),"Produção do mês")="Recebido no mês",N(O16),N(D16))=0,"",ROUND(IF(IFERROR(INDEX(Config!$C$25:$C$28,MATCH(C16,Config!$A$25:$A$28,0)),"Produção do mês")="Recebido no mês",N(O16),N(D16))*F16,0)))</f>
+        <v/>
+      </c>
+      <c r="H16" s="42" t="n"/>
+      <c r="I16" s="39" t="n"/>
       <c r="J16" s="19">
         <f>IF(G16="","",IF(I16="",G16,G16-I16))</f>
         <v/>
@@ -3371,7 +3391,7 @@
         <f>IF(G16="","",D16-G16)</f>
         <v/>
       </c>
-      <c r="L16" s="38" t="n"/>
+      <c r="L16" s="39" t="n"/>
       <c r="M16" s="19">
         <f>IF(G16="","",K16-N(L16))</f>
         <v/>
@@ -3380,7 +3400,7 @@
         <f>IF(OR(G16="",E16=""),"",E16*Config!$B$11)</f>
         <v/>
       </c>
-      <c r="O16" s="42">
+      <c r="O16" s="43">
         <f>IF(A16="","",MATCH(A16,Config!$H$5:$H$16,0))</f>
         <v/>
       </c>
@@ -3389,18 +3409,18 @@
       <c r="A17" s="27" t="n"/>
       <c r="B17" s="27" t="n"/>
       <c r="C17" s="26" t="n"/>
-      <c r="D17" s="38" t="n"/>
-      <c r="E17" s="39" t="n"/>
-      <c r="F17" s="40">
+      <c r="D17" s="39" t="n"/>
+      <c r="E17" s="40" t="n"/>
+      <c r="F17" s="41">
         <f>IF(C17="","",IFERROR(INDEX(Config!$B$25:$B$28,MATCH(C17,Config!$A$25:$A$28,0)),""))</f>
         <v/>
       </c>
       <c r="G17" s="19">
-        <f>IF(OR(C17="",D17="",F17=""),"",ROUND(D17*F17,0))</f>
-        <v/>
-      </c>
-      <c r="H17" s="41" t="n"/>
-      <c r="I17" s="38" t="n"/>
+        <f>IF(OR(C17="",F17=""),"",IF(IF(IFERROR(INDEX(Config!$C$25:$C$28,MATCH(C17,Config!$A$25:$A$28,0)),"Produção do mês")="Recebido no mês",N(O17),N(D17))=0,"",ROUND(IF(IFERROR(INDEX(Config!$C$25:$C$28,MATCH(C17,Config!$A$25:$A$28,0)),"Produção do mês")="Recebido no mês",N(O17),N(D17))*F17,0)))</f>
+        <v/>
+      </c>
+      <c r="H17" s="42" t="n"/>
+      <c r="I17" s="39" t="n"/>
       <c r="J17" s="19">
         <f>IF(G17="","",IF(I17="",G17,G17-I17))</f>
         <v/>
@@ -3409,7 +3429,7 @@
         <f>IF(G17="","",D17-G17)</f>
         <v/>
       </c>
-      <c r="L17" s="38" t="n"/>
+      <c r="L17" s="39" t="n"/>
       <c r="M17" s="19">
         <f>IF(G17="","",K17-N(L17))</f>
         <v/>
@@ -3418,7 +3438,7 @@
         <f>IF(OR(G17="",E17=""),"",E17*Config!$B$11)</f>
         <v/>
       </c>
-      <c r="O17" s="42">
+      <c r="O17" s="43">
         <f>IF(A17="","",MATCH(A17,Config!$H$5:$H$16,0))</f>
         <v/>
       </c>
@@ -3427,18 +3447,18 @@
       <c r="A18" s="27" t="n"/>
       <c r="B18" s="27" t="n"/>
       <c r="C18" s="26" t="n"/>
-      <c r="D18" s="38" t="n"/>
-      <c r="E18" s="39" t="n"/>
-      <c r="F18" s="40">
+      <c r="D18" s="39" t="n"/>
+      <c r="E18" s="40" t="n"/>
+      <c r="F18" s="41">
         <f>IF(C18="","",IFERROR(INDEX(Config!$B$25:$B$28,MATCH(C18,Config!$A$25:$A$28,0)),""))</f>
         <v/>
       </c>
       <c r="G18" s="19">
-        <f>IF(OR(C18="",D18="",F18=""),"",ROUND(D18*F18,0))</f>
-        <v/>
-      </c>
-      <c r="H18" s="41" t="n"/>
-      <c r="I18" s="38" t="n"/>
+        <f>IF(OR(C18="",F18=""),"",IF(IF(IFERROR(INDEX(Config!$C$25:$C$28,MATCH(C18,Config!$A$25:$A$28,0)),"Produção do mês")="Recebido no mês",N(O18),N(D18))=0,"",ROUND(IF(IFERROR(INDEX(Config!$C$25:$C$28,MATCH(C18,Config!$A$25:$A$28,0)),"Produção do mês")="Recebido no mês",N(O18),N(D18))*F18,0)))</f>
+        <v/>
+      </c>
+      <c r="H18" s="42" t="n"/>
+      <c r="I18" s="39" t="n"/>
       <c r="J18" s="19">
         <f>IF(G18="","",IF(I18="",G18,G18-I18))</f>
         <v/>
@@ -3447,7 +3467,7 @@
         <f>IF(G18="","",D18-G18)</f>
         <v/>
       </c>
-      <c r="L18" s="38" t="n"/>
+      <c r="L18" s="39" t="n"/>
       <c r="M18" s="19">
         <f>IF(G18="","",K18-N(L18))</f>
         <v/>
@@ -3456,7 +3476,7 @@
         <f>IF(OR(G18="",E18=""),"",E18*Config!$B$11)</f>
         <v/>
       </c>
-      <c r="O18" s="42">
+      <c r="O18" s="43">
         <f>IF(A18="","",MATCH(A18,Config!$H$5:$H$16,0))</f>
         <v/>
       </c>
@@ -3465,18 +3485,18 @@
       <c r="A19" s="27" t="n"/>
       <c r="B19" s="27" t="n"/>
       <c r="C19" s="26" t="n"/>
-      <c r="D19" s="38" t="n"/>
-      <c r="E19" s="39" t="n"/>
-      <c r="F19" s="40">
+      <c r="D19" s="39" t="n"/>
+      <c r="E19" s="40" t="n"/>
+      <c r="F19" s="41">
         <f>IF(C19="","",IFERROR(INDEX(Config!$B$25:$B$28,MATCH(C19,Config!$A$25:$A$28,0)),""))</f>
         <v/>
       </c>
       <c r="G19" s="19">
-        <f>IF(OR(C19="",D19="",F19=""),"",ROUND(D19*F19,0))</f>
-        <v/>
-      </c>
-      <c r="H19" s="41" t="n"/>
-      <c r="I19" s="38" t="n"/>
+        <f>IF(OR(C19="",F19=""),"",IF(IF(IFERROR(INDEX(Config!$C$25:$C$28,MATCH(C19,Config!$A$25:$A$28,0)),"Produção do mês")="Recebido no mês",N(O19),N(D19))=0,"",ROUND(IF(IFERROR(INDEX(Config!$C$25:$C$28,MATCH(C19,Config!$A$25:$A$28,0)),"Produção do mês")="Recebido no mês",N(O19),N(D19))*F19,0)))</f>
+        <v/>
+      </c>
+      <c r="H19" s="42" t="n"/>
+      <c r="I19" s="39" t="n"/>
       <c r="J19" s="19">
         <f>IF(G19="","",IF(I19="",G19,G19-I19))</f>
         <v/>
@@ -3485,7 +3505,7 @@
         <f>IF(G19="","",D19-G19)</f>
         <v/>
       </c>
-      <c r="L19" s="38" t="n"/>
+      <c r="L19" s="39" t="n"/>
       <c r="M19" s="19">
         <f>IF(G19="","",K19-N(L19))</f>
         <v/>
@@ -3494,7 +3514,7 @@
         <f>IF(OR(G19="",E19=""),"",E19*Config!$B$11)</f>
         <v/>
       </c>
-      <c r="O19" s="42">
+      <c r="O19" s="43">
         <f>IF(A19="","",MATCH(A19,Config!$H$5:$H$16,0))</f>
         <v/>
       </c>
@@ -3503,18 +3523,18 @@
       <c r="A20" s="27" t="n"/>
       <c r="B20" s="27" t="n"/>
       <c r="C20" s="26" t="n"/>
-      <c r="D20" s="38" t="n"/>
-      <c r="E20" s="39" t="n"/>
-      <c r="F20" s="40">
+      <c r="D20" s="39" t="n"/>
+      <c r="E20" s="40" t="n"/>
+      <c r="F20" s="41">
         <f>IF(C20="","",IFERROR(INDEX(Config!$B$25:$B$28,MATCH(C20,Config!$A$25:$A$28,0)),""))</f>
         <v/>
       </c>
       <c r="G20" s="19">
-        <f>IF(OR(C20="",D20="",F20=""),"",ROUND(D20*F20,0))</f>
-        <v/>
-      </c>
-      <c r="H20" s="41" t="n"/>
-      <c r="I20" s="38" t="n"/>
+        <f>IF(OR(C20="",F20=""),"",IF(IF(IFERROR(INDEX(Config!$C$25:$C$28,MATCH(C20,Config!$A$25:$A$28,0)),"Produção do mês")="Recebido no mês",N(O20),N(D20))=0,"",ROUND(IF(IFERROR(INDEX(Config!$C$25:$C$28,MATCH(C20,Config!$A$25:$A$28,0)),"Produção do mês")="Recebido no mês",N(O20),N(D20))*F20,0)))</f>
+        <v/>
+      </c>
+      <c r="H20" s="42" t="n"/>
+      <c r="I20" s="39" t="n"/>
       <c r="J20" s="19">
         <f>IF(G20="","",IF(I20="",G20,G20-I20))</f>
         <v/>
@@ -3523,7 +3543,7 @@
         <f>IF(G20="","",D20-G20)</f>
         <v/>
       </c>
-      <c r="L20" s="38" t="n"/>
+      <c r="L20" s="39" t="n"/>
       <c r="M20" s="19">
         <f>IF(G20="","",K20-N(L20))</f>
         <v/>
@@ -3532,7 +3552,7 @@
         <f>IF(OR(G20="",E20=""),"",E20*Config!$B$11)</f>
         <v/>
       </c>
-      <c r="O20" s="42">
+      <c r="O20" s="43">
         <f>IF(A20="","",MATCH(A20,Config!$H$5:$H$16,0))</f>
         <v/>
       </c>
@@ -3541,18 +3561,18 @@
       <c r="A21" s="27" t="n"/>
       <c r="B21" s="27" t="n"/>
       <c r="C21" s="26" t="n"/>
-      <c r="D21" s="38" t="n"/>
-      <c r="E21" s="39" t="n"/>
-      <c r="F21" s="40">
+      <c r="D21" s="39" t="n"/>
+      <c r="E21" s="40" t="n"/>
+      <c r="F21" s="41">
         <f>IF(C21="","",IFERROR(INDEX(Config!$B$25:$B$28,MATCH(C21,Config!$A$25:$A$28,0)),""))</f>
         <v/>
       </c>
       <c r="G21" s="19">
-        <f>IF(OR(C21="",D21="",F21=""),"",ROUND(D21*F21,0))</f>
-        <v/>
-      </c>
-      <c r="H21" s="41" t="n"/>
-      <c r="I21" s="38" t="n"/>
+        <f>IF(OR(C21="",F21=""),"",IF(IF(IFERROR(INDEX(Config!$C$25:$C$28,MATCH(C21,Config!$A$25:$A$28,0)),"Produção do mês")="Recebido no mês",N(O21),N(D21))=0,"",ROUND(IF(IFERROR(INDEX(Config!$C$25:$C$28,MATCH(C21,Config!$A$25:$A$28,0)),"Produção do mês")="Recebido no mês",N(O21),N(D21))*F21,0)))</f>
+        <v/>
+      </c>
+      <c r="H21" s="42" t="n"/>
+      <c r="I21" s="39" t="n"/>
       <c r="J21" s="19">
         <f>IF(G21="","",IF(I21="",G21,G21-I21))</f>
         <v/>
@@ -3561,7 +3581,7 @@
         <f>IF(G21="","",D21-G21)</f>
         <v/>
       </c>
-      <c r="L21" s="38" t="n"/>
+      <c r="L21" s="39" t="n"/>
       <c r="M21" s="19">
         <f>IF(G21="","",K21-N(L21))</f>
         <v/>
@@ -3570,7 +3590,7 @@
         <f>IF(OR(G21="",E21=""),"",E21*Config!$B$11)</f>
         <v/>
       </c>
-      <c r="O21" s="42">
+      <c r="O21" s="43">
         <f>IF(A21="","",MATCH(A21,Config!$H$5:$H$16,0))</f>
         <v/>
       </c>
@@ -3579,18 +3599,18 @@
       <c r="A22" s="27" t="n"/>
       <c r="B22" s="27" t="n"/>
       <c r="C22" s="26" t="n"/>
-      <c r="D22" s="38" t="n"/>
-      <c r="E22" s="39" t="n"/>
-      <c r="F22" s="40">
+      <c r="D22" s="39" t="n"/>
+      <c r="E22" s="40" t="n"/>
+      <c r="F22" s="41">
         <f>IF(C22="","",IFERROR(INDEX(Config!$B$25:$B$28,MATCH(C22,Config!$A$25:$A$28,0)),""))</f>
         <v/>
       </c>
       <c r="G22" s="19">
-        <f>IF(OR(C22="",D22="",F22=""),"",ROUND(D22*F22,0))</f>
-        <v/>
-      </c>
-      <c r="H22" s="41" t="n"/>
-      <c r="I22" s="38" t="n"/>
+        <f>IF(OR(C22="",F22=""),"",IF(IF(IFERROR(INDEX(Config!$C$25:$C$28,MATCH(C22,Config!$A$25:$A$28,0)),"Produção do mês")="Recebido no mês",N(O22),N(D22))=0,"",ROUND(IF(IFERROR(INDEX(Config!$C$25:$C$28,MATCH(C22,Config!$A$25:$A$28,0)),"Produção do mês")="Recebido no mês",N(O22),N(D22))*F22,0)))</f>
+        <v/>
+      </c>
+      <c r="H22" s="42" t="n"/>
+      <c r="I22" s="39" t="n"/>
       <c r="J22" s="19">
         <f>IF(G22="","",IF(I22="",G22,G22-I22))</f>
         <v/>
@@ -3599,7 +3619,7 @@
         <f>IF(G22="","",D22-G22)</f>
         <v/>
       </c>
-      <c r="L22" s="38" t="n"/>
+      <c r="L22" s="39" t="n"/>
       <c r="M22" s="19">
         <f>IF(G22="","",K22-N(L22))</f>
         <v/>
@@ -3608,7 +3628,7 @@
         <f>IF(OR(G22="",E22=""),"",E22*Config!$B$11)</f>
         <v/>
       </c>
-      <c r="O22" s="42">
+      <c r="O22" s="43">
         <f>IF(A22="","",MATCH(A22,Config!$H$5:$H$16,0))</f>
         <v/>
       </c>
@@ -3617,18 +3637,18 @@
       <c r="A23" s="27" t="n"/>
       <c r="B23" s="27" t="n"/>
       <c r="C23" s="26" t="n"/>
-      <c r="D23" s="38" t="n"/>
-      <c r="E23" s="39" t="n"/>
-      <c r="F23" s="40">
+      <c r="D23" s="39" t="n"/>
+      <c r="E23" s="40" t="n"/>
+      <c r="F23" s="41">
         <f>IF(C23="","",IFERROR(INDEX(Config!$B$25:$B$28,MATCH(C23,Config!$A$25:$A$28,0)),""))</f>
         <v/>
       </c>
       <c r="G23" s="19">
-        <f>IF(OR(C23="",D23="",F23=""),"",ROUND(D23*F23,0))</f>
-        <v/>
-      </c>
-      <c r="H23" s="41" t="n"/>
-      <c r="I23" s="38" t="n"/>
+        <f>IF(OR(C23="",F23=""),"",IF(IF(IFERROR(INDEX(Config!$C$25:$C$28,MATCH(C23,Config!$A$25:$A$28,0)),"Produção do mês")="Recebido no mês",N(O23),N(D23))=0,"",ROUND(IF(IFERROR(INDEX(Config!$C$25:$C$28,MATCH(C23,Config!$A$25:$A$28,0)),"Produção do mês")="Recebido no mês",N(O23),N(D23))*F23,0)))</f>
+        <v/>
+      </c>
+      <c r="H23" s="42" t="n"/>
+      <c r="I23" s="39" t="n"/>
       <c r="J23" s="19">
         <f>IF(G23="","",IF(I23="",G23,G23-I23))</f>
         <v/>
@@ -3637,7 +3657,7 @@
         <f>IF(G23="","",D23-G23)</f>
         <v/>
       </c>
-      <c r="L23" s="38" t="n"/>
+      <c r="L23" s="39" t="n"/>
       <c r="M23" s="19">
         <f>IF(G23="","",K23-N(L23))</f>
         <v/>
@@ -3646,7 +3666,7 @@
         <f>IF(OR(G23="",E23=""),"",E23*Config!$B$11)</f>
         <v/>
       </c>
-      <c r="O23" s="42">
+      <c r="O23" s="43">
         <f>IF(A23="","",MATCH(A23,Config!$H$5:$H$16,0))</f>
         <v/>
       </c>
@@ -3655,18 +3675,18 @@
       <c r="A24" s="27" t="n"/>
       <c r="B24" s="27" t="n"/>
       <c r="C24" s="26" t="n"/>
-      <c r="D24" s="38" t="n"/>
-      <c r="E24" s="39" t="n"/>
-      <c r="F24" s="40">
+      <c r="D24" s="39" t="n"/>
+      <c r="E24" s="40" t="n"/>
+      <c r="F24" s="41">
         <f>IF(C24="","",IFERROR(INDEX(Config!$B$25:$B$28,MATCH(C24,Config!$A$25:$A$28,0)),""))</f>
         <v/>
       </c>
       <c r="G24" s="19">
-        <f>IF(OR(C24="",D24="",F24=""),"",ROUND(D24*F24,0))</f>
-        <v/>
-      </c>
-      <c r="H24" s="41" t="n"/>
-      <c r="I24" s="38" t="n"/>
+        <f>IF(OR(C24="",F24=""),"",IF(IF(IFERROR(INDEX(Config!$C$25:$C$28,MATCH(C24,Config!$A$25:$A$28,0)),"Produção do mês")="Recebido no mês",N(O24),N(D24))=0,"",ROUND(IF(IFERROR(INDEX(Config!$C$25:$C$28,MATCH(C24,Config!$A$25:$A$28,0)),"Produção do mês")="Recebido no mês",N(O24),N(D24))*F24,0)))</f>
+        <v/>
+      </c>
+      <c r="H24" s="42" t="n"/>
+      <c r="I24" s="39" t="n"/>
       <c r="J24" s="19">
         <f>IF(G24="","",IF(I24="",G24,G24-I24))</f>
         <v/>
@@ -3675,7 +3695,7 @@
         <f>IF(G24="","",D24-G24)</f>
         <v/>
       </c>
-      <c r="L24" s="38" t="n"/>
+      <c r="L24" s="39" t="n"/>
       <c r="M24" s="19">
         <f>IF(G24="","",K24-N(L24))</f>
         <v/>
@@ -3684,7 +3704,7 @@
         <f>IF(OR(G24="",E24=""),"",E24*Config!$B$11)</f>
         <v/>
       </c>
-      <c r="O24" s="42">
+      <c r="O24" s="43">
         <f>IF(A24="","",MATCH(A24,Config!$H$5:$H$16,0))</f>
         <v/>
       </c>
@@ -3693,18 +3713,18 @@
       <c r="A25" s="27" t="n"/>
       <c r="B25" s="27" t="n"/>
       <c r="C25" s="26" t="n"/>
-      <c r="D25" s="38" t="n"/>
-      <c r="E25" s="39" t="n"/>
-      <c r="F25" s="40">
+      <c r="D25" s="39" t="n"/>
+      <c r="E25" s="40" t="n"/>
+      <c r="F25" s="41">
         <f>IF(C25="","",IFERROR(INDEX(Config!$B$25:$B$28,MATCH(C25,Config!$A$25:$A$28,0)),""))</f>
         <v/>
       </c>
       <c r="G25" s="19">
-        <f>IF(OR(C25="",D25="",F25=""),"",ROUND(D25*F25,0))</f>
-        <v/>
-      </c>
-      <c r="H25" s="41" t="n"/>
-      <c r="I25" s="38" t="n"/>
+        <f>IF(OR(C25="",F25=""),"",IF(IF(IFERROR(INDEX(Config!$C$25:$C$28,MATCH(C25,Config!$A$25:$A$28,0)),"Produção do mês")="Recebido no mês",N(O25),N(D25))=0,"",ROUND(IF(IFERROR(INDEX(Config!$C$25:$C$28,MATCH(C25,Config!$A$25:$A$28,0)),"Produção do mês")="Recebido no mês",N(O25),N(D25))*F25,0)))</f>
+        <v/>
+      </c>
+      <c r="H25" s="42" t="n"/>
+      <c r="I25" s="39" t="n"/>
       <c r="J25" s="19">
         <f>IF(G25="","",IF(I25="",G25,G25-I25))</f>
         <v/>
@@ -3713,7 +3733,7 @@
         <f>IF(G25="","",D25-G25)</f>
         <v/>
       </c>
-      <c r="L25" s="38" t="n"/>
+      <c r="L25" s="39" t="n"/>
       <c r="M25" s="19">
         <f>IF(G25="","",K25-N(L25))</f>
         <v/>
@@ -3722,7 +3742,7 @@
         <f>IF(OR(G25="",E25=""),"",E25*Config!$B$11)</f>
         <v/>
       </c>
-      <c r="O25" s="42">
+      <c r="O25" s="43">
         <f>IF(A25="","",MATCH(A25,Config!$H$5:$H$16,0))</f>
         <v/>
       </c>
@@ -3731,18 +3751,18 @@
       <c r="A26" s="27" t="n"/>
       <c r="B26" s="27" t="n"/>
       <c r="C26" s="26" t="n"/>
-      <c r="D26" s="38" t="n"/>
-      <c r="E26" s="39" t="n"/>
-      <c r="F26" s="40">
+      <c r="D26" s="39" t="n"/>
+      <c r="E26" s="40" t="n"/>
+      <c r="F26" s="41">
         <f>IF(C26="","",IFERROR(INDEX(Config!$B$25:$B$28,MATCH(C26,Config!$A$25:$A$28,0)),""))</f>
         <v/>
       </c>
       <c r="G26" s="19">
-        <f>IF(OR(C26="",D26="",F26=""),"",ROUND(D26*F26,0))</f>
-        <v/>
-      </c>
-      <c r="H26" s="41" t="n"/>
-      <c r="I26" s="38" t="n"/>
+        <f>IF(OR(C26="",F26=""),"",IF(IF(IFERROR(INDEX(Config!$C$25:$C$28,MATCH(C26,Config!$A$25:$A$28,0)),"Produção do mês")="Recebido no mês",N(O26),N(D26))=0,"",ROUND(IF(IFERROR(INDEX(Config!$C$25:$C$28,MATCH(C26,Config!$A$25:$A$28,0)),"Produção do mês")="Recebido no mês",N(O26),N(D26))*F26,0)))</f>
+        <v/>
+      </c>
+      <c r="H26" s="42" t="n"/>
+      <c r="I26" s="39" t="n"/>
       <c r="J26" s="19">
         <f>IF(G26="","",IF(I26="",G26,G26-I26))</f>
         <v/>
@@ -3751,7 +3771,7 @@
         <f>IF(G26="","",D26-G26)</f>
         <v/>
       </c>
-      <c r="L26" s="38" t="n"/>
+      <c r="L26" s="39" t="n"/>
       <c r="M26" s="19">
         <f>IF(G26="","",K26-N(L26))</f>
         <v/>
@@ -3760,7 +3780,7 @@
         <f>IF(OR(G26="",E26=""),"",E26*Config!$B$11)</f>
         <v/>
       </c>
-      <c r="O26" s="42">
+      <c r="O26" s="43">
         <f>IF(A26="","",MATCH(A26,Config!$H$5:$H$16,0))</f>
         <v/>
       </c>
@@ -3769,18 +3789,18 @@
       <c r="A27" s="27" t="n"/>
       <c r="B27" s="27" t="n"/>
       <c r="C27" s="26" t="n"/>
-      <c r="D27" s="38" t="n"/>
-      <c r="E27" s="39" t="n"/>
-      <c r="F27" s="40">
+      <c r="D27" s="39" t="n"/>
+      <c r="E27" s="40" t="n"/>
+      <c r="F27" s="41">
         <f>IF(C27="","",IFERROR(INDEX(Config!$B$25:$B$28,MATCH(C27,Config!$A$25:$A$28,0)),""))</f>
         <v/>
       </c>
       <c r="G27" s="19">
-        <f>IF(OR(C27="",D27="",F27=""),"",ROUND(D27*F27,0))</f>
-        <v/>
-      </c>
-      <c r="H27" s="41" t="n"/>
-      <c r="I27" s="38" t="n"/>
+        <f>IF(OR(C27="",F27=""),"",IF(IF(IFERROR(INDEX(Config!$C$25:$C$28,MATCH(C27,Config!$A$25:$A$28,0)),"Produção do mês")="Recebido no mês",N(O27),N(D27))=0,"",ROUND(IF(IFERROR(INDEX(Config!$C$25:$C$28,MATCH(C27,Config!$A$25:$A$28,0)),"Produção do mês")="Recebido no mês",N(O27),N(D27))*F27,0)))</f>
+        <v/>
+      </c>
+      <c r="H27" s="42" t="n"/>
+      <c r="I27" s="39" t="n"/>
       <c r="J27" s="19">
         <f>IF(G27="","",IF(I27="",G27,G27-I27))</f>
         <v/>
@@ -3789,7 +3809,7 @@
         <f>IF(G27="","",D27-G27)</f>
         <v/>
       </c>
-      <c r="L27" s="38" t="n"/>
+      <c r="L27" s="39" t="n"/>
       <c r="M27" s="19">
         <f>IF(G27="","",K27-N(L27))</f>
         <v/>
@@ -3798,7 +3818,7 @@
         <f>IF(OR(G27="",E27=""),"",E27*Config!$B$11)</f>
         <v/>
       </c>
-      <c r="O27" s="42">
+      <c r="O27" s="43">
         <f>IF(A27="","",MATCH(A27,Config!$H$5:$H$16,0))</f>
         <v/>
       </c>
@@ -3807,18 +3827,18 @@
       <c r="A28" s="27" t="n"/>
       <c r="B28" s="27" t="n"/>
       <c r="C28" s="26" t="n"/>
-      <c r="D28" s="38" t="n"/>
-      <c r="E28" s="39" t="n"/>
-      <c r="F28" s="40">
+      <c r="D28" s="39" t="n"/>
+      <c r="E28" s="40" t="n"/>
+      <c r="F28" s="41">
         <f>IF(C28="","",IFERROR(INDEX(Config!$B$25:$B$28,MATCH(C28,Config!$A$25:$A$28,0)),""))</f>
         <v/>
       </c>
       <c r="G28" s="19">
-        <f>IF(OR(C28="",D28="",F28=""),"",ROUND(D28*F28,0))</f>
-        <v/>
-      </c>
-      <c r="H28" s="41" t="n"/>
-      <c r="I28" s="38" t="n"/>
+        <f>IF(OR(C28="",F28=""),"",IF(IF(IFERROR(INDEX(Config!$C$25:$C$28,MATCH(C28,Config!$A$25:$A$28,0)),"Produção do mês")="Recebido no mês",N(O28),N(D28))=0,"",ROUND(IF(IFERROR(INDEX(Config!$C$25:$C$28,MATCH(C28,Config!$A$25:$A$28,0)),"Produção do mês")="Recebido no mês",N(O28),N(D28))*F28,0)))</f>
+        <v/>
+      </c>
+      <c r="H28" s="42" t="n"/>
+      <c r="I28" s="39" t="n"/>
       <c r="J28" s="19">
         <f>IF(G28="","",IF(I28="",G28,G28-I28))</f>
         <v/>
@@ -3827,7 +3847,7 @@
         <f>IF(G28="","",D28-G28)</f>
         <v/>
       </c>
-      <c r="L28" s="38" t="n"/>
+      <c r="L28" s="39" t="n"/>
       <c r="M28" s="19">
         <f>IF(G28="","",K28-N(L28))</f>
         <v/>
@@ -3836,7 +3856,7 @@
         <f>IF(OR(G28="",E28=""),"",E28*Config!$B$11)</f>
         <v/>
       </c>
-      <c r="O28" s="42">
+      <c r="O28" s="43">
         <f>IF(A28="","",MATCH(A28,Config!$H$5:$H$16,0))</f>
         <v/>
       </c>
@@ -3845,18 +3865,18 @@
       <c r="A29" s="27" t="n"/>
       <c r="B29" s="27" t="n"/>
       <c r="C29" s="26" t="n"/>
-      <c r="D29" s="38" t="n"/>
-      <c r="E29" s="39" t="n"/>
-      <c r="F29" s="40">
+      <c r="D29" s="39" t="n"/>
+      <c r="E29" s="40" t="n"/>
+      <c r="F29" s="41">
         <f>IF(C29="","",IFERROR(INDEX(Config!$B$25:$B$28,MATCH(C29,Config!$A$25:$A$28,0)),""))</f>
         <v/>
       </c>
       <c r="G29" s="19">
-        <f>IF(OR(C29="",D29="",F29=""),"",ROUND(D29*F29,0))</f>
-        <v/>
-      </c>
-      <c r="H29" s="41" t="n"/>
-      <c r="I29" s="38" t="n"/>
+        <f>IF(OR(C29="",F29=""),"",IF(IF(IFERROR(INDEX(Config!$C$25:$C$28,MATCH(C29,Config!$A$25:$A$28,0)),"Produção do mês")="Recebido no mês",N(O29),N(D29))=0,"",ROUND(IF(IFERROR(INDEX(Config!$C$25:$C$28,MATCH(C29,Config!$A$25:$A$28,0)),"Produção do mês")="Recebido no mês",N(O29),N(D29))*F29,0)))</f>
+        <v/>
+      </c>
+      <c r="H29" s="42" t="n"/>
+      <c r="I29" s="39" t="n"/>
       <c r="J29" s="19">
         <f>IF(G29="","",IF(I29="",G29,G29-I29))</f>
         <v/>
@@ -3865,7 +3885,7 @@
         <f>IF(G29="","",D29-G29)</f>
         <v/>
       </c>
-      <c r="L29" s="38" t="n"/>
+      <c r="L29" s="39" t="n"/>
       <c r="M29" s="19">
         <f>IF(G29="","",K29-N(L29))</f>
         <v/>
@@ -3874,7 +3894,7 @@
         <f>IF(OR(G29="",E29=""),"",E29*Config!$B$11)</f>
         <v/>
       </c>
-      <c r="O29" s="42">
+      <c r="O29" s="43">
         <f>IF(A29="","",MATCH(A29,Config!$H$5:$H$16,0))</f>
         <v/>
       </c>
@@ -3883,18 +3903,18 @@
       <c r="A30" s="27" t="n"/>
       <c r="B30" s="27" t="n"/>
       <c r="C30" s="26" t="n"/>
-      <c r="D30" s="38" t="n"/>
-      <c r="E30" s="39" t="n"/>
-      <c r="F30" s="40">
+      <c r="D30" s="39" t="n"/>
+      <c r="E30" s="40" t="n"/>
+      <c r="F30" s="41">
         <f>IF(C30="","",IFERROR(INDEX(Config!$B$25:$B$28,MATCH(C30,Config!$A$25:$A$28,0)),""))</f>
         <v/>
       </c>
       <c r="G30" s="19">
-        <f>IF(OR(C30="",D30="",F30=""),"",ROUND(D30*F30,0))</f>
-        <v/>
-      </c>
-      <c r="H30" s="41" t="n"/>
-      <c r="I30" s="38" t="n"/>
+        <f>IF(OR(C30="",F30=""),"",IF(IF(IFERROR(INDEX(Config!$C$25:$C$28,MATCH(C30,Config!$A$25:$A$28,0)),"Produção do mês")="Recebido no mês",N(O30),N(D30))=0,"",ROUND(IF(IFERROR(INDEX(Config!$C$25:$C$28,MATCH(C30,Config!$A$25:$A$28,0)),"Produção do mês")="Recebido no mês",N(O30),N(D30))*F30,0)))</f>
+        <v/>
+      </c>
+      <c r="H30" s="42" t="n"/>
+      <c r="I30" s="39" t="n"/>
       <c r="J30" s="19">
         <f>IF(G30="","",IF(I30="",G30,G30-I30))</f>
         <v/>
@@ -3903,7 +3923,7 @@
         <f>IF(G30="","",D30-G30)</f>
         <v/>
       </c>
-      <c r="L30" s="38" t="n"/>
+      <c r="L30" s="39" t="n"/>
       <c r="M30" s="19">
         <f>IF(G30="","",K30-N(L30))</f>
         <v/>
@@ -3912,7 +3932,7 @@
         <f>IF(OR(G30="",E30=""),"",E30*Config!$B$11)</f>
         <v/>
       </c>
-      <c r="O30" s="42">
+      <c r="O30" s="43">
         <f>IF(A30="","",MATCH(A30,Config!$H$5:$H$16,0))</f>
         <v/>
       </c>
@@ -3921,18 +3941,18 @@
       <c r="A31" s="27" t="n"/>
       <c r="B31" s="27" t="n"/>
       <c r="C31" s="26" t="n"/>
-      <c r="D31" s="38" t="n"/>
-      <c r="E31" s="39" t="n"/>
-      <c r="F31" s="40">
+      <c r="D31" s="39" t="n"/>
+      <c r="E31" s="40" t="n"/>
+      <c r="F31" s="41">
         <f>IF(C31="","",IFERROR(INDEX(Config!$B$25:$B$28,MATCH(C31,Config!$A$25:$A$28,0)),""))</f>
         <v/>
       </c>
       <c r="G31" s="19">
-        <f>IF(OR(C31="",D31="",F31=""),"",ROUND(D31*F31,0))</f>
-        <v/>
-      </c>
-      <c r="H31" s="41" t="n"/>
-      <c r="I31" s="38" t="n"/>
+        <f>IF(OR(C31="",F31=""),"",IF(IF(IFERROR(INDEX(Config!$C$25:$C$28,MATCH(C31,Config!$A$25:$A$28,0)),"Produção do mês")="Recebido no mês",N(O31),N(D31))=0,"",ROUND(IF(IFERROR(INDEX(Config!$C$25:$C$28,MATCH(C31,Config!$A$25:$A$28,0)),"Produção do mês")="Recebido no mês",N(O31),N(D31))*F31,0)))</f>
+        <v/>
+      </c>
+      <c r="H31" s="42" t="n"/>
+      <c r="I31" s="39" t="n"/>
       <c r="J31" s="19">
         <f>IF(G31="","",IF(I31="",G31,G31-I31))</f>
         <v/>
@@ -3941,7 +3961,7 @@
         <f>IF(G31="","",D31-G31)</f>
         <v/>
       </c>
-      <c r="L31" s="38" t="n"/>
+      <c r="L31" s="39" t="n"/>
       <c r="M31" s="19">
         <f>IF(G31="","",K31-N(L31))</f>
         <v/>
@@ -3950,7 +3970,7 @@
         <f>IF(OR(G31="",E31=""),"",E31*Config!$B$11)</f>
         <v/>
       </c>
-      <c r="O31" s="42">
+      <c r="O31" s="43">
         <f>IF(A31="","",MATCH(A31,Config!$H$5:$H$16,0))</f>
         <v/>
       </c>
@@ -3959,18 +3979,18 @@
       <c r="A32" s="27" t="n"/>
       <c r="B32" s="27" t="n"/>
       <c r="C32" s="26" t="n"/>
-      <c r="D32" s="38" t="n"/>
-      <c r="E32" s="39" t="n"/>
-      <c r="F32" s="40">
+      <c r="D32" s="39" t="n"/>
+      <c r="E32" s="40" t="n"/>
+      <c r="F32" s="41">
         <f>IF(C32="","",IFERROR(INDEX(Config!$B$25:$B$28,MATCH(C32,Config!$A$25:$A$28,0)),""))</f>
         <v/>
       </c>
       <c r="G32" s="19">
-        <f>IF(OR(C32="",D32="",F32=""),"",ROUND(D32*F32,0))</f>
-        <v/>
-      </c>
-      <c r="H32" s="41" t="n"/>
-      <c r="I32" s="38" t="n"/>
+        <f>IF(OR(C32="",F32=""),"",IF(IF(IFERROR(INDEX(Config!$C$25:$C$28,MATCH(C32,Config!$A$25:$A$28,0)),"Produção do mês")="Recebido no mês",N(O32),N(D32))=0,"",ROUND(IF(IFERROR(INDEX(Config!$C$25:$C$28,MATCH(C32,Config!$A$25:$A$28,0)),"Produção do mês")="Recebido no mês",N(O32),N(D32))*F32,0)))</f>
+        <v/>
+      </c>
+      <c r="H32" s="42" t="n"/>
+      <c r="I32" s="39" t="n"/>
       <c r="J32" s="19">
         <f>IF(G32="","",IF(I32="",G32,G32-I32))</f>
         <v/>
@@ -3979,7 +3999,7 @@
         <f>IF(G32="","",D32-G32)</f>
         <v/>
       </c>
-      <c r="L32" s="38" t="n"/>
+      <c r="L32" s="39" t="n"/>
       <c r="M32" s="19">
         <f>IF(G32="","",K32-N(L32))</f>
         <v/>
@@ -3988,7 +4008,7 @@
         <f>IF(OR(G32="",E32=""),"",E32*Config!$B$11)</f>
         <v/>
       </c>
-      <c r="O32" s="42">
+      <c r="O32" s="43">
         <f>IF(A32="","",MATCH(A32,Config!$H$5:$H$16,0))</f>
         <v/>
       </c>
@@ -3997,18 +4017,18 @@
       <c r="A33" s="27" t="n"/>
       <c r="B33" s="27" t="n"/>
       <c r="C33" s="26" t="n"/>
-      <c r="D33" s="38" t="n"/>
-      <c r="E33" s="39" t="n"/>
-      <c r="F33" s="40">
+      <c r="D33" s="39" t="n"/>
+      <c r="E33" s="40" t="n"/>
+      <c r="F33" s="41">
         <f>IF(C33="","",IFERROR(INDEX(Config!$B$25:$B$28,MATCH(C33,Config!$A$25:$A$28,0)),""))</f>
         <v/>
       </c>
       <c r="G33" s="19">
-        <f>IF(OR(C33="",D33="",F33=""),"",ROUND(D33*F33,0))</f>
-        <v/>
-      </c>
-      <c r="H33" s="41" t="n"/>
-      <c r="I33" s="38" t="n"/>
+        <f>IF(OR(C33="",F33=""),"",IF(IF(IFERROR(INDEX(Config!$C$25:$C$28,MATCH(C33,Config!$A$25:$A$28,0)),"Produção do mês")="Recebido no mês",N(O33),N(D33))=0,"",ROUND(IF(IFERROR(INDEX(Config!$C$25:$C$28,MATCH(C33,Config!$A$25:$A$28,0)),"Produção do mês")="Recebido no mês",N(O33),N(D33))*F33,0)))</f>
+        <v/>
+      </c>
+      <c r="H33" s="42" t="n"/>
+      <c r="I33" s="39" t="n"/>
       <c r="J33" s="19">
         <f>IF(G33="","",IF(I33="",G33,G33-I33))</f>
         <v/>
@@ -4017,7 +4037,7 @@
         <f>IF(G33="","",D33-G33)</f>
         <v/>
       </c>
-      <c r="L33" s="38" t="n"/>
+      <c r="L33" s="39" t="n"/>
       <c r="M33" s="19">
         <f>IF(G33="","",K33-N(L33))</f>
         <v/>
@@ -4026,7 +4046,7 @@
         <f>IF(OR(G33="",E33=""),"",E33*Config!$B$11)</f>
         <v/>
       </c>
-      <c r="O33" s="42">
+      <c r="O33" s="43">
         <f>IF(A33="","",MATCH(A33,Config!$H$5:$H$16,0))</f>
         <v/>
       </c>
@@ -4035,18 +4055,18 @@
       <c r="A34" s="27" t="n"/>
       <c r="B34" s="27" t="n"/>
       <c r="C34" s="26" t="n"/>
-      <c r="D34" s="38" t="n"/>
-      <c r="E34" s="39" t="n"/>
-      <c r="F34" s="40">
+      <c r="D34" s="39" t="n"/>
+      <c r="E34" s="40" t="n"/>
+      <c r="F34" s="41">
         <f>IF(C34="","",IFERROR(INDEX(Config!$B$25:$B$28,MATCH(C34,Config!$A$25:$A$28,0)),""))</f>
         <v/>
       </c>
       <c r="G34" s="19">
-        <f>IF(OR(C34="",D34="",F34=""),"",ROUND(D34*F34,0))</f>
-        <v/>
-      </c>
-      <c r="H34" s="41" t="n"/>
-      <c r="I34" s="38" t="n"/>
+        <f>IF(OR(C34="",F34=""),"",IF(IF(IFERROR(INDEX(Config!$C$25:$C$28,MATCH(C34,Config!$A$25:$A$28,0)),"Produção do mês")="Recebido no mês",N(O34),N(D34))=0,"",ROUND(IF(IFERROR(INDEX(Config!$C$25:$C$28,MATCH(C34,Config!$A$25:$A$28,0)),"Produção do mês")="Recebido no mês",N(O34),N(D34))*F34,0)))</f>
+        <v/>
+      </c>
+      <c r="H34" s="42" t="n"/>
+      <c r="I34" s="39" t="n"/>
       <c r="J34" s="19">
         <f>IF(G34="","",IF(I34="",G34,G34-I34))</f>
         <v/>
@@ -4055,7 +4075,7 @@
         <f>IF(G34="","",D34-G34)</f>
         <v/>
       </c>
-      <c r="L34" s="38" t="n"/>
+      <c r="L34" s="39" t="n"/>
       <c r="M34" s="19">
         <f>IF(G34="","",K34-N(L34))</f>
         <v/>
@@ -4064,7 +4084,7 @@
         <f>IF(OR(G34="",E34=""),"",E34*Config!$B$11)</f>
         <v/>
       </c>
-      <c r="O34" s="42">
+      <c r="O34" s="43">
         <f>IF(A34="","",MATCH(A34,Config!$H$5:$H$16,0))</f>
         <v/>
       </c>
@@ -4073,18 +4093,18 @@
       <c r="A35" s="27" t="n"/>
       <c r="B35" s="27" t="n"/>
       <c r="C35" s="26" t="n"/>
-      <c r="D35" s="38" t="n"/>
-      <c r="E35" s="39" t="n"/>
-      <c r="F35" s="40">
+      <c r="D35" s="39" t="n"/>
+      <c r="E35" s="40" t="n"/>
+      <c r="F35" s="41">
         <f>IF(C35="","",IFERROR(INDEX(Config!$B$25:$B$28,MATCH(C35,Config!$A$25:$A$28,0)),""))</f>
         <v/>
       </c>
       <c r="G35" s="19">
-        <f>IF(OR(C35="",D35="",F35=""),"",ROUND(D35*F35,0))</f>
-        <v/>
-      </c>
-      <c r="H35" s="41" t="n"/>
-      <c r="I35" s="38" t="n"/>
+        <f>IF(OR(C35="",F35=""),"",IF(IF(IFERROR(INDEX(Config!$C$25:$C$28,MATCH(C35,Config!$A$25:$A$28,0)),"Produção do mês")="Recebido no mês",N(O35),N(D35))=0,"",ROUND(IF(IFERROR(INDEX(Config!$C$25:$C$28,MATCH(C35,Config!$A$25:$A$28,0)),"Produção do mês")="Recebido no mês",N(O35),N(D35))*F35,0)))</f>
+        <v/>
+      </c>
+      <c r="H35" s="42" t="n"/>
+      <c r="I35" s="39" t="n"/>
       <c r="J35" s="19">
         <f>IF(G35="","",IF(I35="",G35,G35-I35))</f>
         <v/>
@@ -4093,7 +4113,7 @@
         <f>IF(G35="","",D35-G35)</f>
         <v/>
       </c>
-      <c r="L35" s="38" t="n"/>
+      <c r="L35" s="39" t="n"/>
       <c r="M35" s="19">
         <f>IF(G35="","",K35-N(L35))</f>
         <v/>
@@ -4102,7 +4122,7 @@
         <f>IF(OR(G35="",E35=""),"",E35*Config!$B$11)</f>
         <v/>
       </c>
-      <c r="O35" s="42">
+      <c r="O35" s="43">
         <f>IF(A35="","",MATCH(A35,Config!$H$5:$H$16,0))</f>
         <v/>
       </c>
@@ -4111,18 +4131,18 @@
       <c r="A36" s="27" t="n"/>
       <c r="B36" s="27" t="n"/>
       <c r="C36" s="26" t="n"/>
-      <c r="D36" s="38" t="n"/>
-      <c r="E36" s="39" t="n"/>
-      <c r="F36" s="40">
+      <c r="D36" s="39" t="n"/>
+      <c r="E36" s="40" t="n"/>
+      <c r="F36" s="41">
         <f>IF(C36="","",IFERROR(INDEX(Config!$B$25:$B$28,MATCH(C36,Config!$A$25:$A$28,0)),""))</f>
         <v/>
       </c>
       <c r="G36" s="19">
-        <f>IF(OR(C36="",D36="",F36=""),"",ROUND(D36*F36,0))</f>
-        <v/>
-      </c>
-      <c r="H36" s="41" t="n"/>
-      <c r="I36" s="38" t="n"/>
+        <f>IF(OR(C36="",F36=""),"",IF(IF(IFERROR(INDEX(Config!$C$25:$C$28,MATCH(C36,Config!$A$25:$A$28,0)),"Produção do mês")="Recebido no mês",N(O36),N(D36))=0,"",ROUND(IF(IFERROR(INDEX(Config!$C$25:$C$28,MATCH(C36,Config!$A$25:$A$28,0)),"Produção do mês")="Recebido no mês",N(O36),N(D36))*F36,0)))</f>
+        <v/>
+      </c>
+      <c r="H36" s="42" t="n"/>
+      <c r="I36" s="39" t="n"/>
       <c r="J36" s="19">
         <f>IF(G36="","",IF(I36="",G36,G36-I36))</f>
         <v/>
@@ -4131,7 +4151,7 @@
         <f>IF(G36="","",D36-G36)</f>
         <v/>
       </c>
-      <c r="L36" s="38" t="n"/>
+      <c r="L36" s="39" t="n"/>
       <c r="M36" s="19">
         <f>IF(G36="","",K36-N(L36))</f>
         <v/>
@@ -4140,7 +4160,7 @@
         <f>IF(OR(G36="",E36=""),"",E36*Config!$B$11)</f>
         <v/>
       </c>
-      <c r="O36" s="42">
+      <c r="O36" s="43">
         <f>IF(A36="","",MATCH(A36,Config!$H$5:$H$16,0))</f>
         <v/>
       </c>
@@ -4149,18 +4169,18 @@
       <c r="A37" s="27" t="n"/>
       <c r="B37" s="27" t="n"/>
       <c r="C37" s="26" t="n"/>
-      <c r="D37" s="38" t="n"/>
-      <c r="E37" s="39" t="n"/>
-      <c r="F37" s="40">
+      <c r="D37" s="39" t="n"/>
+      <c r="E37" s="40" t="n"/>
+      <c r="F37" s="41">
         <f>IF(C37="","",IFERROR(INDEX(Config!$B$25:$B$28,MATCH(C37,Config!$A$25:$A$28,0)),""))</f>
         <v/>
       </c>
       <c r="G37" s="19">
-        <f>IF(OR(C37="",D37="",F37=""),"",ROUND(D37*F37,0))</f>
-        <v/>
-      </c>
-      <c r="H37" s="41" t="n"/>
-      <c r="I37" s="38" t="n"/>
+        <f>IF(OR(C37="",F37=""),"",IF(IF(IFERROR(INDEX(Config!$C$25:$C$28,MATCH(C37,Config!$A$25:$A$28,0)),"Produção do mês")="Recebido no mês",N(O37),N(D37))=0,"",ROUND(IF(IFERROR(INDEX(Config!$C$25:$C$28,MATCH(C37,Config!$A$25:$A$28,0)),"Produção do mês")="Recebido no mês",N(O37),N(D37))*F37,0)))</f>
+        <v/>
+      </c>
+      <c r="H37" s="42" t="n"/>
+      <c r="I37" s="39" t="n"/>
       <c r="J37" s="19">
         <f>IF(G37="","",IF(I37="",G37,G37-I37))</f>
         <v/>
@@ -4169,7 +4189,7 @@
         <f>IF(G37="","",D37-G37)</f>
         <v/>
       </c>
-      <c r="L37" s="38" t="n"/>
+      <c r="L37" s="39" t="n"/>
       <c r="M37" s="19">
         <f>IF(G37="","",K37-N(L37))</f>
         <v/>
@@ -4178,7 +4198,7 @@
         <f>IF(OR(G37="",E37=""),"",E37*Config!$B$11)</f>
         <v/>
       </c>
-      <c r="O37" s="42">
+      <c r="O37" s="43">
         <f>IF(A37="","",MATCH(A37,Config!$H$5:$H$16,0))</f>
         <v/>
       </c>
@@ -4187,18 +4207,18 @@
       <c r="A38" s="27" t="n"/>
       <c r="B38" s="27" t="n"/>
       <c r="C38" s="26" t="n"/>
-      <c r="D38" s="38" t="n"/>
-      <c r="E38" s="39" t="n"/>
-      <c r="F38" s="40">
+      <c r="D38" s="39" t="n"/>
+      <c r="E38" s="40" t="n"/>
+      <c r="F38" s="41">
         <f>IF(C38="","",IFERROR(INDEX(Config!$B$25:$B$28,MATCH(C38,Config!$A$25:$A$28,0)),""))</f>
         <v/>
       </c>
       <c r="G38" s="19">
-        <f>IF(OR(C38="",D38="",F38=""),"",ROUND(D38*F38,0))</f>
-        <v/>
-      </c>
-      <c r="H38" s="41" t="n"/>
-      <c r="I38" s="38" t="n"/>
+        <f>IF(OR(C38="",F38=""),"",IF(IF(IFERROR(INDEX(Config!$C$25:$C$28,MATCH(C38,Config!$A$25:$A$28,0)),"Produção do mês")="Recebido no mês",N(O38),N(D38))=0,"",ROUND(IF(IFERROR(INDEX(Config!$C$25:$C$28,MATCH(C38,Config!$A$25:$A$28,0)),"Produção do mês")="Recebido no mês",N(O38),N(D38))*F38,0)))</f>
+        <v/>
+      </c>
+      <c r="H38" s="42" t="n"/>
+      <c r="I38" s="39" t="n"/>
       <c r="J38" s="19">
         <f>IF(G38="","",IF(I38="",G38,G38-I38))</f>
         <v/>
@@ -4207,7 +4227,7 @@
         <f>IF(G38="","",D38-G38)</f>
         <v/>
       </c>
-      <c r="L38" s="38" t="n"/>
+      <c r="L38" s="39" t="n"/>
       <c r="M38" s="19">
         <f>IF(G38="","",K38-N(L38))</f>
         <v/>
@@ -4216,7 +4236,7 @@
         <f>IF(OR(G38="",E38=""),"",E38*Config!$B$11)</f>
         <v/>
       </c>
-      <c r="O38" s="42">
+      <c r="O38" s="43">
         <f>IF(A38="","",MATCH(A38,Config!$H$5:$H$16,0))</f>
         <v/>
       </c>
@@ -4225,18 +4245,18 @@
       <c r="A39" s="27" t="n"/>
       <c r="B39" s="27" t="n"/>
       <c r="C39" s="26" t="n"/>
-      <c r="D39" s="38" t="n"/>
-      <c r="E39" s="39" t="n"/>
-      <c r="F39" s="40">
+      <c r="D39" s="39" t="n"/>
+      <c r="E39" s="40" t="n"/>
+      <c r="F39" s="41">
         <f>IF(C39="","",IFERROR(INDEX(Config!$B$25:$B$28,MATCH(C39,Config!$A$25:$A$28,0)),""))</f>
         <v/>
       </c>
       <c r="G39" s="19">
-        <f>IF(OR(C39="",D39="",F39=""),"",ROUND(D39*F39,0))</f>
-        <v/>
-      </c>
-      <c r="H39" s="41" t="n"/>
-      <c r="I39" s="38" t="n"/>
+        <f>IF(OR(C39="",F39=""),"",IF(IF(IFERROR(INDEX(Config!$C$25:$C$28,MATCH(C39,Config!$A$25:$A$28,0)),"Produção do mês")="Recebido no mês",N(O39),N(D39))=0,"",ROUND(IF(IFERROR(INDEX(Config!$C$25:$C$28,MATCH(C39,Config!$A$25:$A$28,0)),"Produção do mês")="Recebido no mês",N(O39),N(D39))*F39,0)))</f>
+        <v/>
+      </c>
+      <c r="H39" s="42" t="n"/>
+      <c r="I39" s="39" t="n"/>
       <c r="J39" s="19">
         <f>IF(G39="","",IF(I39="",G39,G39-I39))</f>
         <v/>
@@ -4245,7 +4265,7 @@
         <f>IF(G39="","",D39-G39)</f>
         <v/>
       </c>
-      <c r="L39" s="38" t="n"/>
+      <c r="L39" s="39" t="n"/>
       <c r="M39" s="19">
         <f>IF(G39="","",K39-N(L39))</f>
         <v/>
@@ -4254,7 +4274,7 @@
         <f>IF(OR(G39="",E39=""),"",E39*Config!$B$11)</f>
         <v/>
       </c>
-      <c r="O39" s="42">
+      <c r="O39" s="43">
         <f>IF(A39="","",MATCH(A39,Config!$H$5:$H$16,0))</f>
         <v/>
       </c>
@@ -4263,18 +4283,18 @@
       <c r="A40" s="27" t="n"/>
       <c r="B40" s="27" t="n"/>
       <c r="C40" s="26" t="n"/>
-      <c r="D40" s="38" t="n"/>
-      <c r="E40" s="39" t="n"/>
-      <c r="F40" s="40">
+      <c r="D40" s="39" t="n"/>
+      <c r="E40" s="40" t="n"/>
+      <c r="F40" s="41">
         <f>IF(C40="","",IFERROR(INDEX(Config!$B$25:$B$28,MATCH(C40,Config!$A$25:$A$28,0)),""))</f>
         <v/>
       </c>
       <c r="G40" s="19">
-        <f>IF(OR(C40="",D40="",F40=""),"",ROUND(D40*F40,0))</f>
-        <v/>
-      </c>
-      <c r="H40" s="41" t="n"/>
-      <c r="I40" s="38" t="n"/>
+        <f>IF(OR(C40="",F40=""),"",IF(IF(IFERROR(INDEX(Config!$C$25:$C$28,MATCH(C40,Config!$A$25:$A$28,0)),"Produção do mês")="Recebido no mês",N(O40),N(D40))=0,"",ROUND(IF(IFERROR(INDEX(Config!$C$25:$C$28,MATCH(C40,Config!$A$25:$A$28,0)),"Produção do mês")="Recebido no mês",N(O40),N(D40))*F40,0)))</f>
+        <v/>
+      </c>
+      <c r="H40" s="42" t="n"/>
+      <c r="I40" s="39" t="n"/>
       <c r="J40" s="19">
         <f>IF(G40="","",IF(I40="",G40,G40-I40))</f>
         <v/>
@@ -4283,7 +4303,7 @@
         <f>IF(G40="","",D40-G40)</f>
         <v/>
       </c>
-      <c r="L40" s="38" t="n"/>
+      <c r="L40" s="39" t="n"/>
       <c r="M40" s="19">
         <f>IF(G40="","",K40-N(L40))</f>
         <v/>
@@ -4292,7 +4312,7 @@
         <f>IF(OR(G40="",E40=""),"",E40*Config!$B$11)</f>
         <v/>
       </c>
-      <c r="O40" s="42">
+      <c r="O40" s="43">
         <f>IF(A40="","",MATCH(A40,Config!$H$5:$H$16,0))</f>
         <v/>
       </c>
@@ -4305,7 +4325,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="37" t="inlineStr">
+      <c r="A43" s="38" t="inlineStr">
         <is>
           <t>No exemplo, a produção de janeiro a junho veio do fechamento do dia (a agenda na planilha 01 começou em julho); julho e agosto são o Painel da 01 por profissional; setembro está em andamento (até 11/09), sem repasse pago ainda.</t>
         </is>
@@ -4335,10 +4355,10 @@
     <dataValidation sqref="A5:A40" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>=Config!$H$5:$H$16</formula1>
     </dataValidation>
-    <dataValidation sqref="C5:C40" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="C5:C40" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>=OFFSET(Config!$A$25,0,0,MAX(1,COUNTA(Config!$A$25:$A$28)),1)</formula1>
     </dataValidation>
-    <dataValidation sqref="H5:H40" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="date" operator="greaterThan">
+    <dataValidation sqref="H5:H40" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="date" operator="greaterThan">
       <formula1>1</formula1>
     </dataValidation>
   </dataValidations>
@@ -4421,11 +4441,11 @@
       <c r="C5" s="31" t="n">
         <v>17932.05</v>
       </c>
-      <c r="D5" s="43">
+      <c r="D5" s="44">
         <f>IF(AND(B5="",C5=""),0,Config!$C$21)</f>
         <v>18000</v>
       </c>
-      <c r="E5" s="43">
+      <c r="E5" s="44">
         <f>B5-C5-D5</f>
         <v>-10622.05</v>
       </c>
@@ -4447,11 +4467,11 @@
       <c r="C6" s="31" t="n">
         <v>17610.54</v>
       </c>
-      <c r="D6" s="43">
+      <c r="D6" s="44">
         <f>IF(AND(B6="",C6=""),0,Config!$C$21)</f>
         <v>18000</v>
       </c>
-      <c r="E6" s="43">
+      <c r="E6" s="44">
         <f>B6-C6-D6</f>
         <v>-9960.54</v>
       </c>
@@ -4473,11 +4493,11 @@
       <c r="C7" s="31" t="n">
         <v>17901.13</v>
       </c>
-      <c r="D7" s="43">
+      <c r="D7" s="44">
         <f>IF(AND(B7="",C7=""),0,Config!$C$21)</f>
         <v>18000</v>
       </c>
-      <c r="E7" s="43">
+      <c r="E7" s="44">
         <f>B7-C7-D7</f>
         <v>4638.87</v>
       </c>
@@ -4499,11 +4519,11 @@
       <c r="C8" s="31" t="n">
         <v>22254.1</v>
       </c>
-      <c r="D8" s="43">
+      <c r="D8" s="44">
         <f>IF(AND(B8="",C8=""),0,Config!$C$21)</f>
         <v>18000</v>
       </c>
-      <c r="E8" s="43">
+      <c r="E8" s="44">
         <f>B8-C8-D8</f>
         <v>-99.0999999999985</v>
       </c>
@@ -4525,11 +4545,11 @@
       <c r="C9" s="31" t="n">
         <v>21500.29</v>
       </c>
-      <c r="D9" s="43">
+      <c r="D9" s="44">
         <f>IF(AND(B9="",C9=""),0,Config!$C$21)</f>
         <v>18000</v>
       </c>
-      <c r="E9" s="43">
+      <c r="E9" s="44">
         <f>B9-C9-D9</f>
         <v>5879.71</v>
       </c>
@@ -4551,11 +4571,11 @@
       <c r="C10" s="31" t="n">
         <v>22202.87</v>
       </c>
-      <c r="D10" s="43">
+      <c r="D10" s="44">
         <f>IF(AND(B10="",C10=""),0,Config!$C$21)</f>
         <v>18000</v>
       </c>
-      <c r="E10" s="43">
+      <c r="E10" s="44">
         <f>B10-C10-D10</f>
         <v>7037.13</v>
       </c>
@@ -4577,11 +4597,11 @@
       <c r="C11" s="31" t="n">
         <v>21562.6</v>
       </c>
-      <c r="D11" s="43">
+      <c r="D11" s="44">
         <f>IF(AND(B11="",C11=""),0,Config!$C$21)</f>
         <v>18000</v>
       </c>
-      <c r="E11" s="43">
+      <c r="E11" s="44">
         <f>B11-C11-D11</f>
         <v>4908.4</v>
       </c>
@@ -4603,11 +4623,11 @@
       <c r="C12" s="31" t="n">
         <v>22248.61</v>
       </c>
-      <c r="D12" s="43">
+      <c r="D12" s="44">
         <f>IF(AND(B12="",C12=""),0,Config!$C$21)</f>
         <v>18000</v>
       </c>
-      <c r="E12" s="43">
+      <c r="E12" s="44">
         <f>B12-C12-D12</f>
         <v>15592.39</v>
       </c>
@@ -4629,11 +4649,11 @@
       <c r="C13" s="31" t="n">
         <v>13630</v>
       </c>
-      <c r="D13" s="43">
+      <c r="D13" s="44">
         <f>IF(AND(B13="",C13=""),0,Config!$C$21)</f>
         <v>18000</v>
       </c>
-      <c r="E13" s="43">
+      <c r="E13" s="44">
         <f>B13-C13-D13</f>
         <v>-10920</v>
       </c>
@@ -4651,11 +4671,11 @@
       </c>
       <c r="B14" s="31" t="n"/>
       <c r="C14" s="31" t="n"/>
-      <c r="D14" s="43">
+      <c r="D14" s="44">
         <f>IF(AND(B14="",C14=""),0,Config!$C$21)</f>
         <v>0</v>
       </c>
-      <c r="E14" s="43">
+      <c r="E14" s="44">
         <f>B14-C14-D14</f>
         <v>0</v>
       </c>
@@ -4673,11 +4693,11 @@
       </c>
       <c r="B15" s="31" t="n"/>
       <c r="C15" s="31" t="n"/>
-      <c r="D15" s="43">
+      <c r="D15" s="44">
         <f>IF(AND(B15="",C15=""),0,Config!$C$21)</f>
         <v>0</v>
       </c>
-      <c r="E15" s="43">
+      <c r="E15" s="44">
         <f>B15-C15-D15</f>
         <v>0</v>
       </c>
@@ -4695,11 +4715,11 @@
       </c>
       <c r="B16" s="31" t="n"/>
       <c r="C16" s="31" t="n"/>
-      <c r="D16" s="43">
+      <c r="D16" s="44">
         <f>IF(AND(B16="",C16=""),0,Config!$C$21)</f>
         <v>0</v>
       </c>
-      <c r="E16" s="43">
+      <c r="E16" s="44">
         <f>B16-C16-D16</f>
         <v>0</v>
       </c>
@@ -4710,7 +4730,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="37" t="inlineStr">
+      <c r="A18" s="38" t="inlineStr">
         <is>
           <t>Entradas = Entrou no mês (Painel da planilha 09) menos devoluções dos sócios (Outras entradas). Saídas sem sócios = Saiu no mês menos pró-labore, retiradas extras, distribuição de lucro e despesas pessoais dos sócios (o repasse à parceira fica dentro). Meses não fechados ficam em branco (setembro: até 11/09).</t>
         </is>
@@ -4807,7 +4827,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="41" t="n">
+      <c r="A5" s="42" t="n">
         <v>46050</v>
       </c>
       <c r="B5" s="27" t="inlineStr">
@@ -4839,7 +4859,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="41" t="n">
+      <c r="A6" s="42" t="n">
         <v>46050</v>
       </c>
       <c r="B6" s="27" t="inlineStr">
@@ -4871,7 +4891,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="41" t="n">
+      <c r="A7" s="42" t="n">
         <v>46059</v>
       </c>
       <c r="B7" s="27" t="inlineStr">
@@ -4903,7 +4923,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="41" t="n">
+      <c r="A8" s="42" t="n">
         <v>46081</v>
       </c>
       <c r="B8" s="27" t="inlineStr">
@@ -4935,7 +4955,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="41" t="n">
+      <c r="A9" s="42" t="n">
         <v>46081</v>
       </c>
       <c r="B9" s="27" t="inlineStr">
@@ -4967,7 +4987,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="41" t="n">
+      <c r="A10" s="42" t="n">
         <v>46092</v>
       </c>
       <c r="B10" s="27" t="inlineStr">
@@ -4999,7 +5019,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="41" t="n">
+      <c r="A11" s="42" t="n">
         <v>46097</v>
       </c>
       <c r="B11" s="27" t="inlineStr">
@@ -5031,7 +5051,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="41" t="n">
+      <c r="A12" s="42" t="n">
         <v>46109</v>
       </c>
       <c r="B12" s="27" t="inlineStr">
@@ -5063,7 +5083,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="41" t="n">
+      <c r="A13" s="42" t="n">
         <v>46109</v>
       </c>
       <c r="B13" s="27" t="inlineStr">
@@ -5095,7 +5115,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="41" t="n">
+      <c r="A14" s="42" t="n">
         <v>46126</v>
       </c>
       <c r="B14" s="27" t="inlineStr">
@@ -5127,7 +5147,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="41" t="n">
+      <c r="A15" s="42" t="n">
         <v>46140</v>
       </c>
       <c r="B15" s="27" t="inlineStr">
@@ -5159,7 +5179,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="41" t="n">
+      <c r="A16" s="42" t="n">
         <v>46140</v>
       </c>
       <c r="B16" s="27" t="inlineStr">
@@ -5191,7 +5211,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="41" t="n">
+      <c r="A17" s="42" t="n">
         <v>46148</v>
       </c>
       <c r="B17" s="27" t="inlineStr">
@@ -5223,7 +5243,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="41" t="n">
+      <c r="A18" s="42" t="n">
         <v>46170</v>
       </c>
       <c r="B18" s="27" t="inlineStr">
@@ -5255,7 +5275,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="41" t="n">
+      <c r="A19" s="42" t="n">
         <v>46170</v>
       </c>
       <c r="B19" s="27" t="inlineStr">
@@ -5287,7 +5307,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="41" t="n">
+      <c r="A20" s="42" t="n">
         <v>46192</v>
       </c>
       <c r="B20" s="27" t="inlineStr">
@@ -5319,7 +5339,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="41" t="n">
+      <c r="A21" s="42" t="n">
         <v>46201</v>
       </c>
       <c r="B21" s="27" t="inlineStr">
@@ -5351,7 +5371,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="41" t="n">
+      <c r="A22" s="42" t="n">
         <v>46201</v>
       </c>
       <c r="B22" s="27" t="inlineStr">
@@ -5383,7 +5403,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="41" t="n">
+      <c r="A23" s="42" t="n">
         <v>46213</v>
       </c>
       <c r="B23" s="27" t="inlineStr">
@@ -5419,7 +5439,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="41" t="n">
+      <c r="A24" s="42" t="n">
         <v>46213</v>
       </c>
       <c r="B24" s="27" t="inlineStr">
@@ -5455,7 +5475,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="41" t="n">
+      <c r="A25" s="42" t="n">
         <v>46214</v>
       </c>
       <c r="B25" s="27" t="inlineStr">
@@ -5487,7 +5507,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="41" t="n">
+      <c r="A26" s="42" t="n">
         <v>46231</v>
       </c>
       <c r="B26" s="27" t="inlineStr">
@@ -5519,7 +5539,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="41" t="n">
+      <c r="A27" s="42" t="n">
         <v>46231</v>
       </c>
       <c r="B27" s="27" t="inlineStr">
@@ -5551,7 +5571,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="41" t="n">
+      <c r="A28" s="42" t="n">
         <v>46240</v>
       </c>
       <c r="B28" s="27" t="inlineStr">
@@ -5583,7 +5603,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="41" t="n">
+      <c r="A29" s="42" t="n">
         <v>46262</v>
       </c>
       <c r="B29" s="27" t="inlineStr">
@@ -5615,7 +5635,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="41" t="n">
+      <c r="A30" s="42" t="n">
         <v>46262</v>
       </c>
       <c r="B30" s="27" t="inlineStr">
@@ -5647,7 +5667,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="41" t="n"/>
+      <c r="A31" s="42" t="n"/>
       <c r="B31" s="27" t="n"/>
       <c r="C31" s="27" t="n"/>
       <c r="D31" s="26" t="n"/>
@@ -5663,7 +5683,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="41" t="n"/>
+      <c r="A32" s="42" t="n"/>
       <c r="B32" s="27" t="n"/>
       <c r="C32" s="27" t="n"/>
       <c r="D32" s="26" t="n"/>
@@ -5679,7 +5699,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="41" t="n"/>
+      <c r="A33" s="42" t="n"/>
       <c r="B33" s="27" t="n"/>
       <c r="C33" s="27" t="n"/>
       <c r="D33" s="26" t="n"/>
@@ -5695,7 +5715,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="41" t="n"/>
+      <c r="A34" s="42" t="n"/>
       <c r="B34" s="27" t="n"/>
       <c r="C34" s="27" t="n"/>
       <c r="D34" s="26" t="n"/>
@@ -5711,7 +5731,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="41" t="n"/>
+      <c r="A35" s="42" t="n"/>
       <c r="B35" s="27" t="n"/>
       <c r="C35" s="27" t="n"/>
       <c r="D35" s="26" t="n"/>
@@ -5727,7 +5747,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="41" t="n"/>
+      <c r="A36" s="42" t="n"/>
       <c r="B36" s="27" t="n"/>
       <c r="C36" s="27" t="n"/>
       <c r="D36" s="26" t="n"/>
@@ -5743,7 +5763,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="41" t="n"/>
+      <c r="A37" s="42" t="n"/>
       <c r="B37" s="27" t="n"/>
       <c r="C37" s="27" t="n"/>
       <c r="D37" s="26" t="n"/>
@@ -5759,7 +5779,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="41" t="n"/>
+      <c r="A38" s="42" t="n"/>
       <c r="B38" s="27" t="n"/>
       <c r="C38" s="27" t="n"/>
       <c r="D38" s="26" t="n"/>
@@ -5775,7 +5795,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="41" t="n"/>
+      <c r="A39" s="42" t="n"/>
       <c r="B39" s="27" t="n"/>
       <c r="C39" s="27" t="n"/>
       <c r="D39" s="26" t="n"/>
@@ -5791,7 +5811,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="41" t="n"/>
+      <c r="A40" s="42" t="n"/>
       <c r="B40" s="27" t="n"/>
       <c r="C40" s="27" t="n"/>
       <c r="D40" s="26" t="n"/>
@@ -5807,7 +5827,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="41" t="n"/>
+      <c r="A41" s="42" t="n"/>
       <c r="B41" s="27" t="n"/>
       <c r="C41" s="27" t="n"/>
       <c r="D41" s="26" t="n"/>
@@ -5823,7 +5843,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="41" t="n"/>
+      <c r="A42" s="42" t="n"/>
       <c r="B42" s="27" t="n"/>
       <c r="C42" s="27" t="n"/>
       <c r="D42" s="26" t="n"/>
@@ -5839,7 +5859,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="41" t="n"/>
+      <c r="A43" s="42" t="n"/>
       <c r="B43" s="27" t="n"/>
       <c r="C43" s="27" t="n"/>
       <c r="D43" s="26" t="n"/>
@@ -5855,7 +5875,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="41" t="n"/>
+      <c r="A44" s="42" t="n"/>
       <c r="B44" s="27" t="n"/>
       <c r="C44" s="27" t="n"/>
       <c r="D44" s="26" t="n"/>
@@ -5871,7 +5891,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="41" t="n"/>
+      <c r="A45" s="42" t="n"/>
       <c r="B45" s="27" t="n"/>
       <c r="C45" s="27" t="n"/>
       <c r="D45" s="26" t="n"/>
@@ -5887,7 +5907,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="41" t="n"/>
+      <c r="A46" s="42" t="n"/>
       <c r="B46" s="27" t="n"/>
       <c r="C46" s="27" t="n"/>
       <c r="D46" s="26" t="n"/>
@@ -5903,7 +5923,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="41" t="n"/>
+      <c r="A47" s="42" t="n"/>
       <c r="B47" s="27" t="n"/>
       <c r="C47" s="27" t="n"/>
       <c r="D47" s="26" t="n"/>
@@ -5919,7 +5939,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="41" t="n"/>
+      <c r="A48" s="42" t="n"/>
       <c r="B48" s="27" t="n"/>
       <c r="C48" s="27" t="n"/>
       <c r="D48" s="26" t="n"/>
@@ -5935,7 +5955,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="41" t="n"/>
+      <c r="A49" s="42" t="n"/>
       <c r="B49" s="27" t="n"/>
       <c r="C49" s="27" t="n"/>
       <c r="D49" s="26" t="n"/>
@@ -5951,7 +5971,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="41" t="n"/>
+      <c r="A50" s="42" t="n"/>
       <c r="B50" s="27" t="n"/>
       <c r="C50" s="27" t="n"/>
       <c r="D50" s="26" t="n"/>
@@ -5967,7 +5987,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="41" t="n"/>
+      <c r="A51" s="42" t="n"/>
       <c r="B51" s="27" t="n"/>
       <c r="C51" s="27" t="n"/>
       <c r="D51" s="26" t="n"/>
@@ -5983,7 +6003,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="41" t="n"/>
+      <c r="A52" s="42" t="n"/>
       <c r="B52" s="27" t="n"/>
       <c r="C52" s="27" t="n"/>
       <c r="D52" s="26" t="n"/>
@@ -5999,7 +6019,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="41" t="n"/>
+      <c r="A53" s="42" t="n"/>
       <c r="B53" s="27" t="n"/>
       <c r="C53" s="27" t="n"/>
       <c r="D53" s="26" t="n"/>
@@ -6015,7 +6035,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="41" t="n"/>
+      <c r="A54" s="42" t="n"/>
       <c r="B54" s="27" t="n"/>
       <c r="C54" s="27" t="n"/>
       <c r="D54" s="26" t="n"/>
@@ -6031,7 +6051,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="41" t="n"/>
+      <c r="A55" s="42" t="n"/>
       <c r="B55" s="27" t="n"/>
       <c r="C55" s="27" t="n"/>
       <c r="D55" s="26" t="n"/>
@@ -6047,7 +6067,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="41" t="n"/>
+      <c r="A56" s="42" t="n"/>
       <c r="B56" s="27" t="n"/>
       <c r="C56" s="27" t="n"/>
       <c r="D56" s="26" t="n"/>
@@ -6063,7 +6083,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="41" t="n"/>
+      <c r="A57" s="42" t="n"/>
       <c r="B57" s="27" t="n"/>
       <c r="C57" s="27" t="n"/>
       <c r="D57" s="26" t="n"/>
@@ -6079,7 +6099,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="41" t="n"/>
+      <c r="A58" s="42" t="n"/>
       <c r="B58" s="27" t="n"/>
       <c r="C58" s="27" t="n"/>
       <c r="D58" s="26" t="n"/>
@@ -6095,7 +6115,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="41" t="n"/>
+      <c r="A59" s="42" t="n"/>
       <c r="B59" s="27" t="n"/>
       <c r="C59" s="27" t="n"/>
       <c r="D59" s="26" t="n"/>
@@ -6111,7 +6131,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="41" t="n"/>
+      <c r="A60" s="42" t="n"/>
       <c r="B60" s="27" t="n"/>
       <c r="C60" s="27" t="n"/>
       <c r="D60" s="26" t="n"/>
@@ -6127,7 +6147,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="41" t="n"/>
+      <c r="A61" s="42" t="n"/>
       <c r="B61" s="27" t="n"/>
       <c r="C61" s="27" t="n"/>
       <c r="D61" s="26" t="n"/>
@@ -6143,7 +6163,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="41" t="n"/>
+      <c r="A62" s="42" t="n"/>
       <c r="B62" s="27" t="n"/>
       <c r="C62" s="27" t="n"/>
       <c r="D62" s="26" t="n"/>
@@ -6159,7 +6179,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="41" t="n"/>
+      <c r="A63" s="42" t="n"/>
       <c r="B63" s="27" t="n"/>
       <c r="C63" s="27" t="n"/>
       <c r="D63" s="26" t="n"/>
@@ -6175,7 +6195,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="41" t="n"/>
+      <c r="A64" s="42" t="n"/>
       <c r="B64" s="27" t="n"/>
       <c r="C64" s="27" t="n"/>
       <c r="D64" s="26" t="n"/>
@@ -6191,7 +6211,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="41" t="n"/>
+      <c r="A65" s="42" t="n"/>
       <c r="B65" s="27" t="n"/>
       <c r="C65" s="27" t="n"/>
       <c r="D65" s="26" t="n"/>
@@ -6207,7 +6227,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="41" t="n"/>
+      <c r="A66" s="42" t="n"/>
       <c r="B66" s="27" t="n"/>
       <c r="C66" s="27" t="n"/>
       <c r="D66" s="26" t="n"/>
@@ -6223,7 +6243,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="41" t="n"/>
+      <c r="A67" s="42" t="n"/>
       <c r="B67" s="27" t="n"/>
       <c r="C67" s="27" t="n"/>
       <c r="D67" s="26" t="n"/>
@@ -6239,7 +6259,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="41" t="n"/>
+      <c r="A68" s="42" t="n"/>
       <c r="B68" s="27" t="n"/>
       <c r="C68" s="27" t="n"/>
       <c r="D68" s="26" t="n"/>
@@ -6255,7 +6275,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="41" t="n"/>
+      <c r="A69" s="42" t="n"/>
       <c r="B69" s="27" t="n"/>
       <c r="C69" s="27" t="n"/>
       <c r="D69" s="26" t="n"/>
@@ -6271,7 +6291,7 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="41" t="n"/>
+      <c r="A70" s="42" t="n"/>
       <c r="B70" s="27" t="n"/>
       <c r="C70" s="27" t="n"/>
       <c r="D70" s="26" t="n"/>
@@ -6287,7 +6307,7 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="41" t="n"/>
+      <c r="A71" s="42" t="n"/>
       <c r="B71" s="27" t="n"/>
       <c r="C71" s="27" t="n"/>
       <c r="D71" s="26" t="n"/>
@@ -6303,7 +6323,7 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="41" t="n"/>
+      <c r="A72" s="42" t="n"/>
       <c r="B72" s="27" t="n"/>
       <c r="C72" s="27" t="n"/>
       <c r="D72" s="26" t="n"/>
@@ -6319,7 +6339,7 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="41" t="n"/>
+      <c r="A73" s="42" t="n"/>
       <c r="B73" s="27" t="n"/>
       <c r="C73" s="27" t="n"/>
       <c r="D73" s="26" t="n"/>
@@ -6335,7 +6355,7 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="41" t="n"/>
+      <c r="A74" s="42" t="n"/>
       <c r="B74" s="27" t="n"/>
       <c r="C74" s="27" t="n"/>
       <c r="D74" s="26" t="n"/>
@@ -6351,7 +6371,7 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="41" t="n"/>
+      <c r="A75" s="42" t="n"/>
       <c r="B75" s="27" t="n"/>
       <c r="C75" s="27" t="n"/>
       <c r="D75" s="26" t="n"/>
@@ -6367,7 +6387,7 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="41" t="n"/>
+      <c r="A76" s="42" t="n"/>
       <c r="B76" s="27" t="n"/>
       <c r="C76" s="27" t="n"/>
       <c r="D76" s="26" t="n"/>
@@ -6383,7 +6403,7 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="41" t="n"/>
+      <c r="A77" s="42" t="n"/>
       <c r="B77" s="27" t="n"/>
       <c r="C77" s="27" t="n"/>
       <c r="D77" s="26" t="n"/>
@@ -6399,7 +6419,7 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="41" t="n"/>
+      <c r="A78" s="42" t="n"/>
       <c r="B78" s="27" t="n"/>
       <c r="C78" s="27" t="n"/>
       <c r="D78" s="26" t="n"/>
@@ -6415,7 +6435,7 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="41" t="n"/>
+      <c r="A79" s="42" t="n"/>
       <c r="B79" s="27" t="n"/>
       <c r="C79" s="27" t="n"/>
       <c r="D79" s="26" t="n"/>
@@ -6431,7 +6451,7 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="41" t="n"/>
+      <c r="A80" s="42" t="n"/>
       <c r="B80" s="27" t="n"/>
       <c r="C80" s="27" t="n"/>
       <c r="D80" s="26" t="n"/>
@@ -6447,7 +6467,7 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="41" t="n"/>
+      <c r="A81" s="42" t="n"/>
       <c r="B81" s="27" t="n"/>
       <c r="C81" s="27" t="n"/>
       <c r="D81" s="26" t="n"/>
@@ -6463,7 +6483,7 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="41" t="n"/>
+      <c r="A82" s="42" t="n"/>
       <c r="B82" s="27" t="n"/>
       <c r="C82" s="27" t="n"/>
       <c r="D82" s="26" t="n"/>
@@ -6479,7 +6499,7 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="41" t="n"/>
+      <c r="A83" s="42" t="n"/>
       <c r="B83" s="27" t="n"/>
       <c r="C83" s="27" t="n"/>
       <c r="D83" s="26" t="n"/>
@@ -6495,7 +6515,7 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="41" t="n"/>
+      <c r="A84" s="42" t="n"/>
       <c r="B84" s="27" t="n"/>
       <c r="C84" s="27" t="n"/>
       <c r="D84" s="26" t="n"/>
@@ -6511,7 +6531,7 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="41" t="n"/>
+      <c r="A85" s="42" t="n"/>
       <c r="B85" s="27" t="n"/>
       <c r="C85" s="27" t="n"/>
       <c r="D85" s="26" t="n"/>
@@ -6527,7 +6547,7 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="41" t="n"/>
+      <c r="A86" s="42" t="n"/>
       <c r="B86" s="27" t="n"/>
       <c r="C86" s="27" t="n"/>
       <c r="D86" s="26" t="n"/>
@@ -6543,7 +6563,7 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="41" t="n"/>
+      <c r="A87" s="42" t="n"/>
       <c r="B87" s="27" t="n"/>
       <c r="C87" s="27" t="n"/>
       <c r="D87" s="26" t="n"/>
@@ -6559,7 +6579,7 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="41" t="n"/>
+      <c r="A88" s="42" t="n"/>
       <c r="B88" s="27" t="n"/>
       <c r="C88" s="27" t="n"/>
       <c r="D88" s="26" t="n"/>
@@ -6575,7 +6595,7 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="41" t="n"/>
+      <c r="A89" s="42" t="n"/>
       <c r="B89" s="27" t="n"/>
       <c r="C89" s="27" t="n"/>
       <c r="D89" s="26" t="n"/>
@@ -6591,7 +6611,7 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="41" t="n"/>
+      <c r="A90" s="42" t="n"/>
       <c r="B90" s="27" t="n"/>
       <c r="C90" s="27" t="n"/>
       <c r="D90" s="26" t="n"/>
@@ -6607,7 +6627,7 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="41" t="n"/>
+      <c r="A91" s="42" t="n"/>
       <c r="B91" s="27" t="n"/>
       <c r="C91" s="27" t="n"/>
       <c r="D91" s="26" t="n"/>
@@ -6623,7 +6643,7 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="41" t="n"/>
+      <c r="A92" s="42" t="n"/>
       <c r="B92" s="27" t="n"/>
       <c r="C92" s="27" t="n"/>
       <c r="D92" s="26" t="n"/>
@@ -6639,7 +6659,7 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="41" t="n"/>
+      <c r="A93" s="42" t="n"/>
       <c r="B93" s="27" t="n"/>
       <c r="C93" s="27" t="n"/>
       <c r="D93" s="26" t="n"/>
@@ -6655,7 +6675,7 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="41" t="n"/>
+      <c r="A94" s="42" t="n"/>
       <c r="B94" s="27" t="n"/>
       <c r="C94" s="27" t="n"/>
       <c r="D94" s="26" t="n"/>
@@ -6671,7 +6691,7 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="41" t="n"/>
+      <c r="A95" s="42" t="n"/>
       <c r="B95" s="27" t="n"/>
       <c r="C95" s="27" t="n"/>
       <c r="D95" s="26" t="n"/>
@@ -6687,7 +6707,7 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="41" t="n"/>
+      <c r="A96" s="42" t="n"/>
       <c r="B96" s="27" t="n"/>
       <c r="C96" s="27" t="n"/>
       <c r="D96" s="26" t="n"/>
@@ -6703,7 +6723,7 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="41" t="n"/>
+      <c r="A97" s="42" t="n"/>
       <c r="B97" s="27" t="n"/>
       <c r="C97" s="27" t="n"/>
       <c r="D97" s="26" t="n"/>
@@ -6719,7 +6739,7 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="41" t="n"/>
+      <c r="A98" s="42" t="n"/>
       <c r="B98" s="27" t="n"/>
       <c r="C98" s="27" t="n"/>
       <c r="D98" s="26" t="n"/>
@@ -6735,7 +6755,7 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="41" t="n"/>
+      <c r="A99" s="42" t="n"/>
       <c r="B99" s="27" t="n"/>
       <c r="C99" s="27" t="n"/>
       <c r="D99" s="26" t="n"/>
@@ -6751,7 +6771,7 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="41" t="n"/>
+      <c r="A100" s="42" t="n"/>
       <c r="B100" s="27" t="n"/>
       <c r="C100" s="27" t="n"/>
       <c r="D100" s="26" t="n"/>
@@ -6767,7 +6787,7 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="41" t="n"/>
+      <c r="A101" s="42" t="n"/>
       <c r="B101" s="27" t="n"/>
       <c r="C101" s="27" t="n"/>
       <c r="D101" s="26" t="n"/>
@@ -6783,7 +6803,7 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="41" t="n"/>
+      <c r="A102" s="42" t="n"/>
       <c r="B102" s="27" t="n"/>
       <c r="C102" s="27" t="n"/>
       <c r="D102" s="26" t="n"/>
@@ -6799,7 +6819,7 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="41" t="n"/>
+      <c r="A103" s="42" t="n"/>
       <c r="B103" s="27" t="n"/>
       <c r="C103" s="27" t="n"/>
       <c r="D103" s="26" t="n"/>
@@ -6815,7 +6835,7 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="41" t="n"/>
+      <c r="A104" s="42" t="n"/>
       <c r="B104" s="27" t="n"/>
       <c r="C104" s="27" t="n"/>
       <c r="D104" s="26" t="n"/>
@@ -6831,7 +6851,7 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="41" t="n"/>
+      <c r="A105" s="42" t="n"/>
       <c r="B105" s="27" t="n"/>
       <c r="C105" s="27" t="n"/>
       <c r="D105" s="26" t="n"/>
@@ -6847,7 +6867,7 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="41" t="n"/>
+      <c r="A106" s="42" t="n"/>
       <c r="B106" s="27" t="n"/>
       <c r="C106" s="27" t="n"/>
       <c r="D106" s="26" t="n"/>
@@ -6863,7 +6883,7 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="41" t="n"/>
+      <c r="A107" s="42" t="n"/>
       <c r="B107" s="27" t="n"/>
       <c r="C107" s="27" t="n"/>
       <c r="D107" s="26" t="n"/>
@@ -6879,7 +6899,7 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="41" t="n"/>
+      <c r="A108" s="42" t="n"/>
       <c r="B108" s="27" t="n"/>
       <c r="C108" s="27" t="n"/>
       <c r="D108" s="26" t="n"/>
@@ -6895,7 +6915,7 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="41" t="n"/>
+      <c r="A109" s="42" t="n"/>
       <c r="B109" s="27" t="n"/>
       <c r="C109" s="27" t="n"/>
       <c r="D109" s="26" t="n"/>
@@ -6911,7 +6931,7 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="41" t="n"/>
+      <c r="A110" s="42" t="n"/>
       <c r="B110" s="27" t="n"/>
       <c r="C110" s="27" t="n"/>
       <c r="D110" s="26" t="n"/>
@@ -6927,7 +6947,7 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="41" t="n"/>
+      <c r="A111" s="42" t="n"/>
       <c r="B111" s="27" t="n"/>
       <c r="C111" s="27" t="n"/>
       <c r="D111" s="26" t="n"/>
@@ -6943,7 +6963,7 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="41" t="n"/>
+      <c r="A112" s="42" t="n"/>
       <c r="B112" s="27" t="n"/>
       <c r="C112" s="27" t="n"/>
       <c r="D112" s="26" t="n"/>
@@ -6959,7 +6979,7 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="41" t="n"/>
+      <c r="A113" s="42" t="n"/>
       <c r="B113" s="27" t="n"/>
       <c r="C113" s="27" t="n"/>
       <c r="D113" s="26" t="n"/>
@@ -6975,7 +6995,7 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="41" t="n"/>
+      <c r="A114" s="42" t="n"/>
       <c r="B114" s="27" t="n"/>
       <c r="C114" s="27" t="n"/>
       <c r="D114" s="26" t="n"/>
@@ -6991,7 +7011,7 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="41" t="n"/>
+      <c r="A115" s="42" t="n"/>
       <c r="B115" s="27" t="n"/>
       <c r="C115" s="27" t="n"/>
       <c r="D115" s="26" t="n"/>
@@ -7007,7 +7027,7 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="41" t="n"/>
+      <c r="A116" s="42" t="n"/>
       <c r="B116" s="27" t="n"/>
       <c r="C116" s="27" t="n"/>
       <c r="D116" s="26" t="n"/>
@@ -7023,7 +7043,7 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="41" t="n"/>
+      <c r="A117" s="42" t="n"/>
       <c r="B117" s="27" t="n"/>
       <c r="C117" s="27" t="n"/>
       <c r="D117" s="26" t="n"/>
@@ -7039,7 +7059,7 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="41" t="n"/>
+      <c r="A118" s="42" t="n"/>
       <c r="B118" s="27" t="n"/>
       <c r="C118" s="27" t="n"/>
       <c r="D118" s="26" t="n"/>
@@ -7055,7 +7075,7 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="41" t="n"/>
+      <c r="A119" s="42" t="n"/>
       <c r="B119" s="27" t="n"/>
       <c r="C119" s="27" t="n"/>
       <c r="D119" s="26" t="n"/>
@@ -7071,7 +7091,7 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="41" t="n"/>
+      <c r="A120" s="42" t="n"/>
       <c r="B120" s="27" t="n"/>
       <c r="C120" s="27" t="n"/>
       <c r="D120" s="26" t="n"/>
@@ -7087,7 +7107,7 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="41" t="n"/>
+      <c r="A121" s="42" t="n"/>
       <c r="B121" s="27" t="n"/>
       <c r="C121" s="27" t="n"/>
       <c r="D121" s="26" t="n"/>
@@ -7103,7 +7123,7 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="41" t="n"/>
+      <c r="A122" s="42" t="n"/>
       <c r="B122" s="27" t="n"/>
       <c r="C122" s="27" t="n"/>
       <c r="D122" s="26" t="n"/>
@@ -7119,7 +7139,7 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="41" t="n"/>
+      <c r="A123" s="42" t="n"/>
       <c r="B123" s="27" t="n"/>
       <c r="C123" s="27" t="n"/>
       <c r="D123" s="26" t="n"/>
@@ -7135,7 +7155,7 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="41" t="n"/>
+      <c r="A124" s="42" t="n"/>
       <c r="B124" s="27" t="n"/>
       <c r="C124" s="27" t="n"/>
       <c r="D124" s="26" t="n"/>
@@ -7151,7 +7171,7 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="41" t="n"/>
+      <c r="A125" s="42" t="n"/>
       <c r="B125" s="27" t="n"/>
       <c r="C125" s="27" t="n"/>
       <c r="D125" s="26" t="n"/>
@@ -7167,7 +7187,7 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="41" t="n"/>
+      <c r="A126" s="42" t="n"/>
       <c r="B126" s="27" t="n"/>
       <c r="C126" s="27" t="n"/>
       <c r="D126" s="26" t="n"/>
@@ -7183,7 +7203,7 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="41" t="n"/>
+      <c r="A127" s="42" t="n"/>
       <c r="B127" s="27" t="n"/>
       <c r="C127" s="27" t="n"/>
       <c r="D127" s="26" t="n"/>
@@ -7199,7 +7219,7 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="41" t="n"/>
+      <c r="A128" s="42" t="n"/>
       <c r="B128" s="27" t="n"/>
       <c r="C128" s="27" t="n"/>
       <c r="D128" s="26" t="n"/>
@@ -7215,7 +7235,7 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="41" t="n"/>
+      <c r="A129" s="42" t="n"/>
       <c r="B129" s="27" t="n"/>
       <c r="C129" s="27" t="n"/>
       <c r="D129" s="26" t="n"/>
@@ -7231,7 +7251,7 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="41" t="n"/>
+      <c r="A130" s="42" t="n"/>
       <c r="B130" s="27" t="n"/>
       <c r="C130" s="27" t="n"/>
       <c r="D130" s="26" t="n"/>
@@ -7247,7 +7267,7 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="41" t="n"/>
+      <c r="A131" s="42" t="n"/>
       <c r="B131" s="27" t="n"/>
       <c r="C131" s="27" t="n"/>
       <c r="D131" s="26" t="n"/>
@@ -7263,7 +7283,7 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="41" t="n"/>
+      <c r="A132" s="42" t="n"/>
       <c r="B132" s="27" t="n"/>
       <c r="C132" s="27" t="n"/>
       <c r="D132" s="26" t="n"/>
@@ -7279,7 +7299,7 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="41" t="n"/>
+      <c r="A133" s="42" t="n"/>
       <c r="B133" s="27" t="n"/>
       <c r="C133" s="27" t="n"/>
       <c r="D133" s="26" t="n"/>
@@ -7295,7 +7315,7 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="41" t="n"/>
+      <c r="A134" s="42" t="n"/>
       <c r="B134" s="27" t="n"/>
       <c r="C134" s="27" t="n"/>
       <c r="D134" s="26" t="n"/>
@@ -7311,7 +7331,7 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="41" t="n"/>
+      <c r="A135" s="42" t="n"/>
       <c r="B135" s="27" t="n"/>
       <c r="C135" s="27" t="n"/>
       <c r="D135" s="26" t="n"/>
@@ -7327,7 +7347,7 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="41" t="n"/>
+      <c r="A136" s="42" t="n"/>
       <c r="B136" s="27" t="n"/>
       <c r="C136" s="27" t="n"/>
       <c r="D136" s="26" t="n"/>
@@ -7343,7 +7363,7 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="41" t="n"/>
+      <c r="A137" s="42" t="n"/>
       <c r="B137" s="27" t="n"/>
       <c r="C137" s="27" t="n"/>
       <c r="D137" s="26" t="n"/>
@@ -7359,7 +7379,7 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="41" t="n"/>
+      <c r="A138" s="42" t="n"/>
       <c r="B138" s="27" t="n"/>
       <c r="C138" s="27" t="n"/>
       <c r="D138" s="26" t="n"/>
@@ -7375,7 +7395,7 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="41" t="n"/>
+      <c r="A139" s="42" t="n"/>
       <c r="B139" s="27" t="n"/>
       <c r="C139" s="27" t="n"/>
       <c r="D139" s="26" t="n"/>
@@ -7391,7 +7411,7 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="41" t="n"/>
+      <c r="A140" s="42" t="n"/>
       <c r="B140" s="27" t="n"/>
       <c r="C140" s="27" t="n"/>
       <c r="D140" s="26" t="n"/>
@@ -7407,7 +7427,7 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="41" t="n"/>
+      <c r="A141" s="42" t="n"/>
       <c r="B141" s="27" t="n"/>
       <c r="C141" s="27" t="n"/>
       <c r="D141" s="26" t="n"/>
@@ -7423,7 +7443,7 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="41" t="n"/>
+      <c r="A142" s="42" t="n"/>
       <c r="B142" s="27" t="n"/>
       <c r="C142" s="27" t="n"/>
       <c r="D142" s="26" t="n"/>
@@ -7439,7 +7459,7 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="41" t="n"/>
+      <c r="A143" s="42" t="n"/>
       <c r="B143" s="27" t="n"/>
       <c r="C143" s="27" t="n"/>
       <c r="D143" s="26" t="n"/>
@@ -7455,7 +7475,7 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="41" t="n"/>
+      <c r="A144" s="42" t="n"/>
       <c r="B144" s="27" t="n"/>
       <c r="C144" s="27" t="n"/>
       <c r="D144" s="26" t="n"/>
@@ -7471,7 +7491,7 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="41" t="n"/>
+      <c r="A145" s="42" t="n"/>
       <c r="B145" s="27" t="n"/>
       <c r="C145" s="27" t="n"/>
       <c r="D145" s="26" t="n"/>
@@ -7487,7 +7507,7 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="41" t="n"/>
+      <c r="A146" s="42" t="n"/>
       <c r="B146" s="27" t="n"/>
       <c r="C146" s="27" t="n"/>
       <c r="D146" s="26" t="n"/>
@@ -7503,7 +7523,7 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="41" t="n"/>
+      <c r="A147" s="42" t="n"/>
       <c r="B147" s="27" t="n"/>
       <c r="C147" s="27" t="n"/>
       <c r="D147" s="26" t="n"/>
@@ -7519,7 +7539,7 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="41" t="n"/>
+      <c r="A148" s="42" t="n"/>
       <c r="B148" s="27" t="n"/>
       <c r="C148" s="27" t="n"/>
       <c r="D148" s="26" t="n"/>
@@ -7535,7 +7555,7 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="41" t="n"/>
+      <c r="A149" s="42" t="n"/>
       <c r="B149" s="27" t="n"/>
       <c r="C149" s="27" t="n"/>
       <c r="D149" s="26" t="n"/>
@@ -7551,7 +7571,7 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="41" t="n"/>
+      <c r="A150" s="42" t="n"/>
       <c r="B150" s="27" t="n"/>
       <c r="C150" s="27" t="n"/>
       <c r="D150" s="26" t="n"/>
@@ -7567,7 +7587,7 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="41" t="n"/>
+      <c r="A151" s="42" t="n"/>
       <c r="B151" s="27" t="n"/>
       <c r="C151" s="27" t="n"/>
       <c r="D151" s="26" t="n"/>
@@ -7583,7 +7603,7 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="41" t="n"/>
+      <c r="A152" s="42" t="n"/>
       <c r="B152" s="27" t="n"/>
       <c r="C152" s="27" t="n"/>
       <c r="D152" s="26" t="n"/>
@@ -7599,7 +7619,7 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="41" t="n"/>
+      <c r="A153" s="42" t="n"/>
       <c r="B153" s="27" t="n"/>
       <c r="C153" s="27" t="n"/>
       <c r="D153" s="26" t="n"/>
@@ -7615,7 +7635,7 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="41" t="n"/>
+      <c r="A154" s="42" t="n"/>
       <c r="B154" s="27" t="n"/>
       <c r="C154" s="27" t="n"/>
       <c r="D154" s="26" t="n"/>
@@ -7631,7 +7651,7 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="41" t="n"/>
+      <c r="A155" s="42" t="n"/>
       <c r="B155" s="27" t="n"/>
       <c r="C155" s="27" t="n"/>
       <c r="D155" s="26" t="n"/>
@@ -7647,7 +7667,7 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="41" t="n"/>
+      <c r="A156" s="42" t="n"/>
       <c r="B156" s="27" t="n"/>
       <c r="C156" s="27" t="n"/>
       <c r="D156" s="26" t="n"/>
@@ -7663,7 +7683,7 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="41" t="n"/>
+      <c r="A157" s="42" t="n"/>
       <c r="B157" s="27" t="n"/>
       <c r="C157" s="27" t="n"/>
       <c r="D157" s="26" t="n"/>
@@ -7679,7 +7699,7 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="41" t="n"/>
+      <c r="A158" s="42" t="n"/>
       <c r="B158" s="27" t="n"/>
       <c r="C158" s="27" t="n"/>
       <c r="D158" s="26" t="n"/>
@@ -7695,7 +7715,7 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="41" t="n"/>
+      <c r="A159" s="42" t="n"/>
       <c r="B159" s="27" t="n"/>
       <c r="C159" s="27" t="n"/>
       <c r="D159" s="26" t="n"/>
@@ -7711,7 +7731,7 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="41" t="n"/>
+      <c r="A160" s="42" t="n"/>
       <c r="B160" s="27" t="n"/>
       <c r="C160" s="27" t="n"/>
       <c r="D160" s="26" t="n"/>
@@ -7727,7 +7747,7 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="41" t="n"/>
+      <c r="A161" s="42" t="n"/>
       <c r="B161" s="27" t="n"/>
       <c r="C161" s="27" t="n"/>
       <c r="D161" s="26" t="n"/>
@@ -7743,7 +7763,7 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="41" t="n"/>
+      <c r="A162" s="42" t="n"/>
       <c r="B162" s="27" t="n"/>
       <c r="C162" s="27" t="n"/>
       <c r="D162" s="26" t="n"/>
@@ -7759,7 +7779,7 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="41" t="n"/>
+      <c r="A163" s="42" t="n"/>
       <c r="B163" s="27" t="n"/>
       <c r="C163" s="27" t="n"/>
       <c r="D163" s="26" t="n"/>
@@ -7775,7 +7795,7 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="41" t="n"/>
+      <c r="A164" s="42" t="n"/>
       <c r="B164" s="27" t="n"/>
       <c r="C164" s="27" t="n"/>
       <c r="D164" s="26" t="n"/>
@@ -7791,7 +7811,7 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="41" t="n"/>
+      <c r="A165" s="42" t="n"/>
       <c r="B165" s="27" t="n"/>
       <c r="C165" s="27" t="n"/>
       <c r="D165" s="26" t="n"/>
@@ -7807,7 +7827,7 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="41" t="n"/>
+      <c r="A166" s="42" t="n"/>
       <c r="B166" s="27" t="n"/>
       <c r="C166" s="27" t="n"/>
       <c r="D166" s="26" t="n"/>
@@ -7823,7 +7843,7 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="41" t="n"/>
+      <c r="A167" s="42" t="n"/>
       <c r="B167" s="27" t="n"/>
       <c r="C167" s="27" t="n"/>
       <c r="D167" s="26" t="n"/>
@@ -7839,7 +7859,7 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="41" t="n"/>
+      <c r="A168" s="42" t="n"/>
       <c r="B168" s="27" t="n"/>
       <c r="C168" s="27" t="n"/>
       <c r="D168" s="26" t="n"/>
@@ -7855,7 +7875,7 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="41" t="n"/>
+      <c r="A169" s="42" t="n"/>
       <c r="B169" s="27" t="n"/>
       <c r="C169" s="27" t="n"/>
       <c r="D169" s="26" t="n"/>
@@ -7871,7 +7891,7 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="41" t="n"/>
+      <c r="A170" s="42" t="n"/>
       <c r="B170" s="27" t="n"/>
       <c r="C170" s="27" t="n"/>
       <c r="D170" s="26" t="n"/>
@@ -7887,7 +7907,7 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="41" t="n"/>
+      <c r="A171" s="42" t="n"/>
       <c r="B171" s="27" t="n"/>
       <c r="C171" s="27" t="n"/>
       <c r="D171" s="26" t="n"/>
@@ -7903,7 +7923,7 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="41" t="n"/>
+      <c r="A172" s="42" t="n"/>
       <c r="B172" s="27" t="n"/>
       <c r="C172" s="27" t="n"/>
       <c r="D172" s="26" t="n"/>
@@ -7919,7 +7939,7 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="41" t="n"/>
+      <c r="A173" s="42" t="n"/>
       <c r="B173" s="27" t="n"/>
       <c r="C173" s="27" t="n"/>
       <c r="D173" s="26" t="n"/>
@@ -7935,7 +7955,7 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="41" t="n"/>
+      <c r="A174" s="42" t="n"/>
       <c r="B174" s="27" t="n"/>
       <c r="C174" s="27" t="n"/>
       <c r="D174" s="26" t="n"/>
@@ -7951,7 +7971,7 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="41" t="n"/>
+      <c r="A175" s="42" t="n"/>
       <c r="B175" s="27" t="n"/>
       <c r="C175" s="27" t="n"/>
       <c r="D175" s="26" t="n"/>
@@ -7967,7 +7987,7 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="41" t="n"/>
+      <c r="A176" s="42" t="n"/>
       <c r="B176" s="27" t="n"/>
       <c r="C176" s="27" t="n"/>
       <c r="D176" s="26" t="n"/>
@@ -7983,7 +8003,7 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="41" t="n"/>
+      <c r="A177" s="42" t="n"/>
       <c r="B177" s="27" t="n"/>
       <c r="C177" s="27" t="n"/>
       <c r="D177" s="26" t="n"/>
@@ -7999,7 +8019,7 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="41" t="n"/>
+      <c r="A178" s="42" t="n"/>
       <c r="B178" s="27" t="n"/>
       <c r="C178" s="27" t="n"/>
       <c r="D178" s="26" t="n"/>
@@ -8015,7 +8035,7 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="41" t="n"/>
+      <c r="A179" s="42" t="n"/>
       <c r="B179" s="27" t="n"/>
       <c r="C179" s="27" t="n"/>
       <c r="D179" s="26" t="n"/>
@@ -8031,7 +8051,7 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="41" t="n"/>
+      <c r="A180" s="42" t="n"/>
       <c r="B180" s="27" t="n"/>
       <c r="C180" s="27" t="n"/>
       <c r="D180" s="26" t="n"/>
@@ -8047,7 +8067,7 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="41" t="n"/>
+      <c r="A181" s="42" t="n"/>
       <c r="B181" s="27" t="n"/>
       <c r="C181" s="27" t="n"/>
       <c r="D181" s="26" t="n"/>
@@ -8063,7 +8083,7 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="41" t="n"/>
+      <c r="A182" s="42" t="n"/>
       <c r="B182" s="27" t="n"/>
       <c r="C182" s="27" t="n"/>
       <c r="D182" s="26" t="n"/>
@@ -8079,7 +8099,7 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="41" t="n"/>
+      <c r="A183" s="42" t="n"/>
       <c r="B183" s="27" t="n"/>
       <c r="C183" s="27" t="n"/>
       <c r="D183" s="26" t="n"/>
@@ -8095,7 +8115,7 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="41" t="n"/>
+      <c r="A184" s="42" t="n"/>
       <c r="B184" s="27" t="n"/>
       <c r="C184" s="27" t="n"/>
       <c r="D184" s="26" t="n"/>
@@ -8111,7 +8131,7 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="41" t="n"/>
+      <c r="A185" s="42" t="n"/>
       <c r="B185" s="27" t="n"/>
       <c r="C185" s="27" t="n"/>
       <c r="D185" s="26" t="n"/>
@@ -8127,7 +8147,7 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="41" t="n"/>
+      <c r="A186" s="42" t="n"/>
       <c r="B186" s="27" t="n"/>
       <c r="C186" s="27" t="n"/>
       <c r="D186" s="26" t="n"/>
@@ -8143,7 +8163,7 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="41" t="n"/>
+      <c r="A187" s="42" t="n"/>
       <c r="B187" s="27" t="n"/>
       <c r="C187" s="27" t="n"/>
       <c r="D187" s="26" t="n"/>
@@ -8159,7 +8179,7 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="41" t="n"/>
+      <c r="A188" s="42" t="n"/>
       <c r="B188" s="27" t="n"/>
       <c r="C188" s="27" t="n"/>
       <c r="D188" s="26" t="n"/>
@@ -8175,7 +8195,7 @@
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="41" t="n"/>
+      <c r="A189" s="42" t="n"/>
       <c r="B189" s="27" t="n"/>
       <c r="C189" s="27" t="n"/>
       <c r="D189" s="26" t="n"/>
@@ -8191,7 +8211,7 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="41" t="n"/>
+      <c r="A190" s="42" t="n"/>
       <c r="B190" s="27" t="n"/>
       <c r="C190" s="27" t="n"/>
       <c r="D190" s="26" t="n"/>
@@ -8207,7 +8227,7 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="41" t="n"/>
+      <c r="A191" s="42" t="n"/>
       <c r="B191" s="27" t="n"/>
       <c r="C191" s="27" t="n"/>
       <c r="D191" s="26" t="n"/>
@@ -8223,7 +8243,7 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="41" t="n"/>
+      <c r="A192" s="42" t="n"/>
       <c r="B192" s="27" t="n"/>
       <c r="C192" s="27" t="n"/>
       <c r="D192" s="26" t="n"/>
@@ -8239,7 +8259,7 @@
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="41" t="n"/>
+      <c r="A193" s="42" t="n"/>
       <c r="B193" s="27" t="n"/>
       <c r="C193" s="27" t="n"/>
       <c r="D193" s="26" t="n"/>
@@ -8255,7 +8275,7 @@
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="41" t="n"/>
+      <c r="A194" s="42" t="n"/>
       <c r="B194" s="27" t="n"/>
       <c r="C194" s="27" t="n"/>
       <c r="D194" s="26" t="n"/>
@@ -8271,7 +8291,7 @@
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="41" t="n"/>
+      <c r="A195" s="42" t="n"/>
       <c r="B195" s="27" t="n"/>
       <c r="C195" s="27" t="n"/>
       <c r="D195" s="26" t="n"/>
@@ -8287,7 +8307,7 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="41" t="n"/>
+      <c r="A196" s="42" t="n"/>
       <c r="B196" s="27" t="n"/>
       <c r="C196" s="27" t="n"/>
       <c r="D196" s="26" t="n"/>
@@ -8303,7 +8323,7 @@
       </c>
     </row>
     <row r="197">
-      <c r="A197" s="41" t="n"/>
+      <c r="A197" s="42" t="n"/>
       <c r="B197" s="27" t="n"/>
       <c r="C197" s="27" t="n"/>
       <c r="D197" s="26" t="n"/>
@@ -8319,7 +8339,7 @@
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="41" t="n"/>
+      <c r="A198" s="42" t="n"/>
       <c r="B198" s="27" t="n"/>
       <c r="C198" s="27" t="n"/>
       <c r="D198" s="26" t="n"/>
@@ -8335,7 +8355,7 @@
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="41" t="n"/>
+      <c r="A199" s="42" t="n"/>
       <c r="B199" s="27" t="n"/>
       <c r="C199" s="27" t="n"/>
       <c r="D199" s="26" t="n"/>
@@ -8351,7 +8371,7 @@
       </c>
     </row>
     <row r="200">
-      <c r="A200" s="41" t="n"/>
+      <c r="A200" s="42" t="n"/>
       <c r="B200" s="27" t="n"/>
       <c r="C200" s="27" t="n"/>
       <c r="D200" s="26" t="n"/>
@@ -8367,7 +8387,7 @@
       </c>
     </row>
     <row r="201">
-      <c r="A201" s="41" t="n"/>
+      <c r="A201" s="42" t="n"/>
       <c r="B201" s="27" t="n"/>
       <c r="C201" s="27" t="n"/>
       <c r="D201" s="26" t="n"/>
@@ -8383,7 +8403,7 @@
       </c>
     </row>
     <row r="202">
-      <c r="A202" s="41" t="n"/>
+      <c r="A202" s="42" t="n"/>
       <c r="B202" s="27" t="n"/>
       <c r="C202" s="27" t="n"/>
       <c r="D202" s="26" t="n"/>
@@ -8399,7 +8419,7 @@
       </c>
     </row>
     <row r="203">
-      <c r="A203" s="41" t="n"/>
+      <c r="A203" s="42" t="n"/>
       <c r="B203" s="27" t="n"/>
       <c r="C203" s="27" t="n"/>
       <c r="D203" s="26" t="n"/>
@@ -8415,7 +8435,7 @@
       </c>
     </row>
     <row r="204">
-      <c r="A204" s="41" t="n"/>
+      <c r="A204" s="42" t="n"/>
       <c r="B204" s="27" t="n"/>
       <c r="C204" s="27" t="n"/>
       <c r="D204" s="26" t="n"/>
@@ -8431,7 +8451,7 @@
       </c>
     </row>
     <row r="205">
-      <c r="A205" s="41" t="n"/>
+      <c r="A205" s="42" t="n"/>
       <c r="B205" s="27" t="n"/>
       <c r="C205" s="27" t="n"/>
       <c r="D205" s="26" t="n"/>
@@ -8447,7 +8467,7 @@
       </c>
     </row>
     <row r="206">
-      <c r="A206" s="41" t="n"/>
+      <c r="A206" s="42" t="n"/>
       <c r="B206" s="27" t="n"/>
       <c r="C206" s="27" t="n"/>
       <c r="D206" s="26" t="n"/>
@@ -8463,7 +8483,7 @@
       </c>
     </row>
     <row r="207">
-      <c r="A207" s="41" t="n"/>
+      <c r="A207" s="42" t="n"/>
       <c r="B207" s="27" t="n"/>
       <c r="C207" s="27" t="n"/>
       <c r="D207" s="26" t="n"/>
@@ -8479,7 +8499,7 @@
       </c>
     </row>
     <row r="208">
-      <c r="A208" s="41" t="n"/>
+      <c r="A208" s="42" t="n"/>
       <c r="B208" s="27" t="n"/>
       <c r="C208" s="27" t="n"/>
       <c r="D208" s="26" t="n"/>
@@ -8495,7 +8515,7 @@
       </c>
     </row>
     <row r="209">
-      <c r="A209" s="41" t="n"/>
+      <c r="A209" s="42" t="n"/>
       <c r="B209" s="27" t="n"/>
       <c r="C209" s="27" t="n"/>
       <c r="D209" s="26" t="n"/>
@@ -8511,7 +8531,7 @@
       </c>
     </row>
     <row r="210">
-      <c r="A210" s="41" t="n"/>
+      <c r="A210" s="42" t="n"/>
       <c r="B210" s="27" t="n"/>
       <c r="C210" s="27" t="n"/>
       <c r="D210" s="26" t="n"/>
@@ -8527,7 +8547,7 @@
       </c>
     </row>
     <row r="211">
-      <c r="A211" s="41" t="n"/>
+      <c r="A211" s="42" t="n"/>
       <c r="B211" s="27" t="n"/>
       <c r="C211" s="27" t="n"/>
       <c r="D211" s="26" t="n"/>
@@ -8543,7 +8563,7 @@
       </c>
     </row>
     <row r="212">
-      <c r="A212" s="41" t="n"/>
+      <c r="A212" s="42" t="n"/>
       <c r="B212" s="27" t="n"/>
       <c r="C212" s="27" t="n"/>
       <c r="D212" s="26" t="n"/>
@@ -8559,7 +8579,7 @@
       </c>
     </row>
     <row r="213">
-      <c r="A213" s="41" t="n"/>
+      <c r="A213" s="42" t="n"/>
       <c r="B213" s="27" t="n"/>
       <c r="C213" s="27" t="n"/>
       <c r="D213" s="26" t="n"/>
@@ -8575,7 +8595,7 @@
       </c>
     </row>
     <row r="214">
-      <c r="A214" s="41" t="n"/>
+      <c r="A214" s="42" t="n"/>
       <c r="B214" s="27" t="n"/>
       <c r="C214" s="27" t="n"/>
       <c r="D214" s="26" t="n"/>
@@ -8591,7 +8611,7 @@
       </c>
     </row>
     <row r="215">
-      <c r="A215" s="41" t="n"/>
+      <c r="A215" s="42" t="n"/>
       <c r="B215" s="27" t="n"/>
       <c r="C215" s="27" t="n"/>
       <c r="D215" s="26" t="n"/>
@@ -8607,7 +8627,7 @@
       </c>
     </row>
     <row r="216">
-      <c r="A216" s="41" t="n"/>
+      <c r="A216" s="42" t="n"/>
       <c r="B216" s="27" t="n"/>
       <c r="C216" s="27" t="n"/>
       <c r="D216" s="26" t="n"/>
@@ -8623,7 +8643,7 @@
       </c>
     </row>
     <row r="217">
-      <c r="A217" s="41" t="n"/>
+      <c r="A217" s="42" t="n"/>
       <c r="B217" s="27" t="n"/>
       <c r="C217" s="27" t="n"/>
       <c r="D217" s="26" t="n"/>
@@ -8639,7 +8659,7 @@
       </c>
     </row>
     <row r="218">
-      <c r="A218" s="41" t="n"/>
+      <c r="A218" s="42" t="n"/>
       <c r="B218" s="27" t="n"/>
       <c r="C218" s="27" t="n"/>
       <c r="D218" s="26" t="n"/>
@@ -8655,7 +8675,7 @@
       </c>
     </row>
     <row r="219">
-      <c r="A219" s="41" t="n"/>
+      <c r="A219" s="42" t="n"/>
       <c r="B219" s="27" t="n"/>
       <c r="C219" s="27" t="n"/>
       <c r="D219" s="26" t="n"/>
@@ -8671,7 +8691,7 @@
       </c>
     </row>
     <row r="220">
-      <c r="A220" s="41" t="n"/>
+      <c r="A220" s="42" t="n"/>
       <c r="B220" s="27" t="n"/>
       <c r="C220" s="27" t="n"/>
       <c r="D220" s="26" t="n"/>
@@ -8687,7 +8707,7 @@
       </c>
     </row>
     <row r="221">
-      <c r="A221" s="41" t="n"/>
+      <c r="A221" s="42" t="n"/>
       <c r="B221" s="27" t="n"/>
       <c r="C221" s="27" t="n"/>
       <c r="D221" s="26" t="n"/>
@@ -8703,7 +8723,7 @@
       </c>
     </row>
     <row r="222">
-      <c r="A222" s="41" t="n"/>
+      <c r="A222" s="42" t="n"/>
       <c r="B222" s="27" t="n"/>
       <c r="C222" s="27" t="n"/>
       <c r="D222" s="26" t="n"/>
@@ -8719,7 +8739,7 @@
       </c>
     </row>
     <row r="223">
-      <c r="A223" s="41" t="n"/>
+      <c r="A223" s="42" t="n"/>
       <c r="B223" s="27" t="n"/>
       <c r="C223" s="27" t="n"/>
       <c r="D223" s="26" t="n"/>
@@ -8735,7 +8755,7 @@
       </c>
     </row>
     <row r="224">
-      <c r="A224" s="41" t="n"/>
+      <c r="A224" s="42" t="n"/>
       <c r="B224" s="27" t="n"/>
       <c r="C224" s="27" t="n"/>
       <c r="D224" s="26" t="n"/>
@@ -8751,7 +8771,7 @@
       </c>
     </row>
     <row r="225">
-      <c r="A225" s="41" t="n"/>
+      <c r="A225" s="42" t="n"/>
       <c r="B225" s="27" t="n"/>
       <c r="C225" s="27" t="n"/>
       <c r="D225" s="26" t="n"/>
@@ -8767,7 +8787,7 @@
       </c>
     </row>
     <row r="226">
-      <c r="A226" s="41" t="n"/>
+      <c r="A226" s="42" t="n"/>
       <c r="B226" s="27" t="n"/>
       <c r="C226" s="27" t="n"/>
       <c r="D226" s="26" t="n"/>
@@ -8783,7 +8803,7 @@
       </c>
     </row>
     <row r="227">
-      <c r="A227" s="41" t="n"/>
+      <c r="A227" s="42" t="n"/>
       <c r="B227" s="27" t="n"/>
       <c r="C227" s="27" t="n"/>
       <c r="D227" s="26" t="n"/>
@@ -8799,7 +8819,7 @@
       </c>
     </row>
     <row r="228">
-      <c r="A228" s="41" t="n"/>
+      <c r="A228" s="42" t="n"/>
       <c r="B228" s="27" t="n"/>
       <c r="C228" s="27" t="n"/>
       <c r="D228" s="26" t="n"/>
@@ -8815,7 +8835,7 @@
       </c>
     </row>
     <row r="229">
-      <c r="A229" s="41" t="n"/>
+      <c r="A229" s="42" t="n"/>
       <c r="B229" s="27" t="n"/>
       <c r="C229" s="27" t="n"/>
       <c r="D229" s="26" t="n"/>
@@ -8831,7 +8851,7 @@
       </c>
     </row>
     <row r="230">
-      <c r="A230" s="41" t="n"/>
+      <c r="A230" s="42" t="n"/>
       <c r="B230" s="27" t="n"/>
       <c r="C230" s="27" t="n"/>
       <c r="D230" s="26" t="n"/>
@@ -8847,7 +8867,7 @@
       </c>
     </row>
     <row r="231">
-      <c r="A231" s="41" t="n"/>
+      <c r="A231" s="42" t="n"/>
       <c r="B231" s="27" t="n"/>
       <c r="C231" s="27" t="n"/>
       <c r="D231" s="26" t="n"/>
@@ -8863,7 +8883,7 @@
       </c>
     </row>
     <row r="232">
-      <c r="A232" s="41" t="n"/>
+      <c r="A232" s="42" t="n"/>
       <c r="B232" s="27" t="n"/>
       <c r="C232" s="27" t="n"/>
       <c r="D232" s="26" t="n"/>
@@ -8879,7 +8899,7 @@
       </c>
     </row>
     <row r="233">
-      <c r="A233" s="41" t="n"/>
+      <c r="A233" s="42" t="n"/>
       <c r="B233" s="27" t="n"/>
       <c r="C233" s="27" t="n"/>
       <c r="D233" s="26" t="n"/>
@@ -8895,7 +8915,7 @@
       </c>
     </row>
     <row r="234">
-      <c r="A234" s="41" t="n"/>
+      <c r="A234" s="42" t="n"/>
       <c r="B234" s="27" t="n"/>
       <c r="C234" s="27" t="n"/>
       <c r="D234" s="26" t="n"/>
@@ -8911,7 +8931,7 @@
       </c>
     </row>
     <row r="235">
-      <c r="A235" s="41" t="n"/>
+      <c r="A235" s="42" t="n"/>
       <c r="B235" s="27" t="n"/>
       <c r="C235" s="27" t="n"/>
       <c r="D235" s="26" t="n"/>
@@ -8927,7 +8947,7 @@
       </c>
     </row>
     <row r="236">
-      <c r="A236" s="41" t="n"/>
+      <c r="A236" s="42" t="n"/>
       <c r="B236" s="27" t="n"/>
       <c r="C236" s="27" t="n"/>
       <c r="D236" s="26" t="n"/>
@@ -8943,7 +8963,7 @@
       </c>
     </row>
     <row r="237">
-      <c r="A237" s="41" t="n"/>
+      <c r="A237" s="42" t="n"/>
       <c r="B237" s="27" t="n"/>
       <c r="C237" s="27" t="n"/>
       <c r="D237" s="26" t="n"/>
@@ -8959,7 +8979,7 @@
       </c>
     </row>
     <row r="238">
-      <c r="A238" s="41" t="n"/>
+      <c r="A238" s="42" t="n"/>
       <c r="B238" s="27" t="n"/>
       <c r="C238" s="27" t="n"/>
       <c r="D238" s="26" t="n"/>
@@ -8975,7 +8995,7 @@
       </c>
     </row>
     <row r="239">
-      <c r="A239" s="41" t="n"/>
+      <c r="A239" s="42" t="n"/>
       <c r="B239" s="27" t="n"/>
       <c r="C239" s="27" t="n"/>
       <c r="D239" s="26" t="n"/>
@@ -8991,7 +9011,7 @@
       </c>
     </row>
     <row r="240">
-      <c r="A240" s="41" t="n"/>
+      <c r="A240" s="42" t="n"/>
       <c r="B240" s="27" t="n"/>
       <c r="C240" s="27" t="n"/>
       <c r="D240" s="26" t="n"/>
@@ -9007,7 +9027,7 @@
       </c>
     </row>
     <row r="241">
-      <c r="A241" s="41" t="n"/>
+      <c r="A241" s="42" t="n"/>
       <c r="B241" s="27" t="n"/>
       <c r="C241" s="27" t="n"/>
       <c r="D241" s="26" t="n"/>
@@ -9023,7 +9043,7 @@
       </c>
     </row>
     <row r="242">
-      <c r="A242" s="41" t="n"/>
+      <c r="A242" s="42" t="n"/>
       <c r="B242" s="27" t="n"/>
       <c r="C242" s="27" t="n"/>
       <c r="D242" s="26" t="n"/>
@@ -9039,7 +9059,7 @@
       </c>
     </row>
     <row r="243">
-      <c r="A243" s="41" t="n"/>
+      <c r="A243" s="42" t="n"/>
       <c r="B243" s="27" t="n"/>
       <c r="C243" s="27" t="n"/>
       <c r="D243" s="26" t="n"/>
@@ -9055,7 +9075,7 @@
       </c>
     </row>
     <row r="244">
-      <c r="A244" s="41" t="n"/>
+      <c r="A244" s="42" t="n"/>
       <c r="B244" s="27" t="n"/>
       <c r="C244" s="27" t="n"/>
       <c r="D244" s="26" t="n"/>
@@ -9071,7 +9091,7 @@
       </c>
     </row>
     <row r="245">
-      <c r="A245" s="41" t="n"/>
+      <c r="A245" s="42" t="n"/>
       <c r="B245" s="27" t="n"/>
       <c r="C245" s="27" t="n"/>
       <c r="D245" s="26" t="n"/>
@@ -9087,7 +9107,7 @@
       </c>
     </row>
     <row r="246">
-      <c r="A246" s="41" t="n"/>
+      <c r="A246" s="42" t="n"/>
       <c r="B246" s="27" t="n"/>
       <c r="C246" s="27" t="n"/>
       <c r="D246" s="26" t="n"/>
@@ -9103,7 +9123,7 @@
       </c>
     </row>
     <row r="247">
-      <c r="A247" s="41" t="n"/>
+      <c r="A247" s="42" t="n"/>
       <c r="B247" s="27" t="n"/>
       <c r="C247" s="27" t="n"/>
       <c r="D247" s="26" t="n"/>
@@ -9119,7 +9139,7 @@
       </c>
     </row>
     <row r="248">
-      <c r="A248" s="41" t="n"/>
+      <c r="A248" s="42" t="n"/>
       <c r="B248" s="27" t="n"/>
       <c r="C248" s="27" t="n"/>
       <c r="D248" s="26" t="n"/>
@@ -9135,7 +9155,7 @@
       </c>
     </row>
     <row r="249">
-      <c r="A249" s="41" t="n"/>
+      <c r="A249" s="42" t="n"/>
       <c r="B249" s="27" t="n"/>
       <c r="C249" s="27" t="n"/>
       <c r="D249" s="26" t="n"/>
@@ -9151,7 +9171,7 @@
       </c>
     </row>
     <row r="250">
-      <c r="A250" s="41" t="n"/>
+      <c r="A250" s="42" t="n"/>
       <c r="B250" s="27" t="n"/>
       <c r="C250" s="27" t="n"/>
       <c r="D250" s="26" t="n"/>
@@ -9167,7 +9187,7 @@
       </c>
     </row>
     <row r="251">
-      <c r="A251" s="41" t="n"/>
+      <c r="A251" s="42" t="n"/>
       <c r="B251" s="27" t="n"/>
       <c r="C251" s="27" t="n"/>
       <c r="D251" s="26" t="n"/>
@@ -9183,7 +9203,7 @@
       </c>
     </row>
     <row r="252">
-      <c r="A252" s="41" t="n"/>
+      <c r="A252" s="42" t="n"/>
       <c r="B252" s="27" t="n"/>
       <c r="C252" s="27" t="n"/>
       <c r="D252" s="26" t="n"/>
@@ -9199,7 +9219,7 @@
       </c>
     </row>
     <row r="253">
-      <c r="A253" s="41" t="n"/>
+      <c r="A253" s="42" t="n"/>
       <c r="B253" s="27" t="n"/>
       <c r="C253" s="27" t="n"/>
       <c r="D253" s="26" t="n"/>
@@ -9215,7 +9235,7 @@
       </c>
     </row>
     <row r="254">
-      <c r="A254" s="41" t="n"/>
+      <c r="A254" s="42" t="n"/>
       <c r="B254" s="27" t="n"/>
       <c r="C254" s="27" t="n"/>
       <c r="D254" s="26" t="n"/>
@@ -9231,7 +9251,7 @@
       </c>
     </row>
     <row r="255">
-      <c r="A255" s="41" t="n"/>
+      <c r="A255" s="42" t="n"/>
       <c r="B255" s="27" t="n"/>
       <c r="C255" s="27" t="n"/>
       <c r="D255" s="26" t="n"/>
@@ -9247,7 +9267,7 @@
       </c>
     </row>
     <row r="256">
-      <c r="A256" s="41" t="n"/>
+      <c r="A256" s="42" t="n"/>
       <c r="B256" s="27" t="n"/>
       <c r="C256" s="27" t="n"/>
       <c r="D256" s="26" t="n"/>
@@ -9263,7 +9283,7 @@
       </c>
     </row>
     <row r="257">
-      <c r="A257" s="41" t="n"/>
+      <c r="A257" s="42" t="n"/>
       <c r="B257" s="27" t="n"/>
       <c r="C257" s="27" t="n"/>
       <c r="D257" s="26" t="n"/>
@@ -9279,7 +9299,7 @@
       </c>
     </row>
     <row r="258">
-      <c r="A258" s="41" t="n"/>
+      <c r="A258" s="42" t="n"/>
       <c r="B258" s="27" t="n"/>
       <c r="C258" s="27" t="n"/>
       <c r="D258" s="26" t="n"/>
@@ -9295,7 +9315,7 @@
       </c>
     </row>
     <row r="259">
-      <c r="A259" s="41" t="n"/>
+      <c r="A259" s="42" t="n"/>
       <c r="B259" s="27" t="n"/>
       <c r="C259" s="27" t="n"/>
       <c r="D259" s="26" t="n"/>
@@ -9311,7 +9331,7 @@
       </c>
     </row>
     <row r="260">
-      <c r="A260" s="41" t="n"/>
+      <c r="A260" s="42" t="n"/>
       <c r="B260" s="27" t="n"/>
       <c r="C260" s="27" t="n"/>
       <c r="D260" s="26" t="n"/>
@@ -9327,7 +9347,7 @@
       </c>
     </row>
     <row r="261">
-      <c r="A261" s="41" t="n"/>
+      <c r="A261" s="42" t="n"/>
       <c r="B261" s="27" t="n"/>
       <c r="C261" s="27" t="n"/>
       <c r="D261" s="26" t="n"/>
@@ -9343,7 +9363,7 @@
       </c>
     </row>
     <row r="262">
-      <c r="A262" s="41" t="n"/>
+      <c r="A262" s="42" t="n"/>
       <c r="B262" s="27" t="n"/>
       <c r="C262" s="27" t="n"/>
       <c r="D262" s="26" t="n"/>
@@ -9359,7 +9379,7 @@
       </c>
     </row>
     <row r="263">
-      <c r="A263" s="41" t="n"/>
+      <c r="A263" s="42" t="n"/>
       <c r="B263" s="27" t="n"/>
       <c r="C263" s="27" t="n"/>
       <c r="D263" s="26" t="n"/>
@@ -9375,7 +9395,7 @@
       </c>
     </row>
     <row r="264">
-      <c r="A264" s="41" t="n"/>
+      <c r="A264" s="42" t="n"/>
       <c r="B264" s="27" t="n"/>
       <c r="C264" s="27" t="n"/>
       <c r="D264" s="26" t="n"/>
@@ -9391,7 +9411,7 @@
       </c>
     </row>
     <row r="265">
-      <c r="A265" s="41" t="n"/>
+      <c r="A265" s="42" t="n"/>
       <c r="B265" s="27" t="n"/>
       <c r="C265" s="27" t="n"/>
       <c r="D265" s="26" t="n"/>
@@ -9407,7 +9427,7 @@
       </c>
     </row>
     <row r="266">
-      <c r="A266" s="41" t="n"/>
+      <c r="A266" s="42" t="n"/>
       <c r="B266" s="27" t="n"/>
       <c r="C266" s="27" t="n"/>
       <c r="D266" s="26" t="n"/>
@@ -9423,7 +9443,7 @@
       </c>
     </row>
     <row r="267">
-      <c r="A267" s="41" t="n"/>
+      <c r="A267" s="42" t="n"/>
       <c r="B267" s="27" t="n"/>
       <c r="C267" s="27" t="n"/>
       <c r="D267" s="26" t="n"/>
@@ -9439,7 +9459,7 @@
       </c>
     </row>
     <row r="268">
-      <c r="A268" s="41" t="n"/>
+      <c r="A268" s="42" t="n"/>
       <c r="B268" s="27" t="n"/>
       <c r="C268" s="27" t="n"/>
       <c r="D268" s="26" t="n"/>
@@ -9455,7 +9475,7 @@
       </c>
     </row>
     <row r="269">
-      <c r="A269" s="41" t="n"/>
+      <c r="A269" s="42" t="n"/>
       <c r="B269" s="27" t="n"/>
       <c r="C269" s="27" t="n"/>
       <c r="D269" s="26" t="n"/>
@@ -9471,7 +9491,7 @@
       </c>
     </row>
     <row r="270">
-      <c r="A270" s="41" t="n"/>
+      <c r="A270" s="42" t="n"/>
       <c r="B270" s="27" t="n"/>
       <c r="C270" s="27" t="n"/>
       <c r="D270" s="26" t="n"/>
@@ -9487,7 +9507,7 @@
       </c>
     </row>
     <row r="271">
-      <c r="A271" s="41" t="n"/>
+      <c r="A271" s="42" t="n"/>
       <c r="B271" s="27" t="n"/>
       <c r="C271" s="27" t="n"/>
       <c r="D271" s="26" t="n"/>
@@ -9503,7 +9523,7 @@
       </c>
     </row>
     <row r="272">
-      <c r="A272" s="41" t="n"/>
+      <c r="A272" s="42" t="n"/>
       <c r="B272" s="27" t="n"/>
       <c r="C272" s="27" t="n"/>
       <c r="D272" s="26" t="n"/>
@@ -9519,7 +9539,7 @@
       </c>
     </row>
     <row r="273">
-      <c r="A273" s="41" t="n"/>
+      <c r="A273" s="42" t="n"/>
       <c r="B273" s="27" t="n"/>
       <c r="C273" s="27" t="n"/>
       <c r="D273" s="26" t="n"/>
@@ -9535,7 +9555,7 @@
       </c>
     </row>
     <row r="274">
-      <c r="A274" s="41" t="n"/>
+      <c r="A274" s="42" t="n"/>
       <c r="B274" s="27" t="n"/>
       <c r="C274" s="27" t="n"/>
       <c r="D274" s="26" t="n"/>
@@ -9551,7 +9571,7 @@
       </c>
     </row>
     <row r="275">
-      <c r="A275" s="41" t="n"/>
+      <c r="A275" s="42" t="n"/>
       <c r="B275" s="27" t="n"/>
       <c r="C275" s="27" t="n"/>
       <c r="D275" s="26" t="n"/>
@@ -9567,7 +9587,7 @@
       </c>
     </row>
     <row r="276">
-      <c r="A276" s="41" t="n"/>
+      <c r="A276" s="42" t="n"/>
       <c r="B276" s="27" t="n"/>
       <c r="C276" s="27" t="n"/>
       <c r="D276" s="26" t="n"/>
@@ -9583,7 +9603,7 @@
       </c>
     </row>
     <row r="277">
-      <c r="A277" s="41" t="n"/>
+      <c r="A277" s="42" t="n"/>
       <c r="B277" s="27" t="n"/>
       <c r="C277" s="27" t="n"/>
       <c r="D277" s="26" t="n"/>
@@ -9599,7 +9619,7 @@
       </c>
     </row>
     <row r="278">
-      <c r="A278" s="41" t="n"/>
+      <c r="A278" s="42" t="n"/>
       <c r="B278" s="27" t="n"/>
       <c r="C278" s="27" t="n"/>
       <c r="D278" s="26" t="n"/>
@@ -9615,7 +9635,7 @@
       </c>
     </row>
     <row r="279">
-      <c r="A279" s="41" t="n"/>
+      <c r="A279" s="42" t="n"/>
       <c r="B279" s="27" t="n"/>
       <c r="C279" s="27" t="n"/>
       <c r="D279" s="26" t="n"/>
@@ -9631,7 +9651,7 @@
       </c>
     </row>
     <row r="280">
-      <c r="A280" s="41" t="n"/>
+      <c r="A280" s="42" t="n"/>
       <c r="B280" s="27" t="n"/>
       <c r="C280" s="27" t="n"/>
       <c r="D280" s="26" t="n"/>
@@ -9647,7 +9667,7 @@
       </c>
     </row>
     <row r="281">
-      <c r="A281" s="41" t="n"/>
+      <c r="A281" s="42" t="n"/>
       <c r="B281" s="27" t="n"/>
       <c r="C281" s="27" t="n"/>
       <c r="D281" s="26" t="n"/>
@@ -9663,7 +9683,7 @@
       </c>
     </row>
     <row r="282">
-      <c r="A282" s="41" t="n"/>
+      <c r="A282" s="42" t="n"/>
       <c r="B282" s="27" t="n"/>
       <c r="C282" s="27" t="n"/>
       <c r="D282" s="26" t="n"/>
@@ -9679,7 +9699,7 @@
       </c>
     </row>
     <row r="283">
-      <c r="A283" s="41" t="n"/>
+      <c r="A283" s="42" t="n"/>
       <c r="B283" s="27" t="n"/>
       <c r="C283" s="27" t="n"/>
       <c r="D283" s="26" t="n"/>
@@ -9695,7 +9715,7 @@
       </c>
     </row>
     <row r="284">
-      <c r="A284" s="41" t="n"/>
+      <c r="A284" s="42" t="n"/>
       <c r="B284" s="27" t="n"/>
       <c r="C284" s="27" t="n"/>
       <c r="D284" s="26" t="n"/>
@@ -9711,7 +9731,7 @@
       </c>
     </row>
     <row r="285">
-      <c r="A285" s="41" t="n"/>
+      <c r="A285" s="42" t="n"/>
       <c r="B285" s="27" t="n"/>
       <c r="C285" s="27" t="n"/>
       <c r="D285" s="26" t="n"/>
@@ -9727,7 +9747,7 @@
       </c>
     </row>
     <row r="286">
-      <c r="A286" s="41" t="n"/>
+      <c r="A286" s="42" t="n"/>
       <c r="B286" s="27" t="n"/>
       <c r="C286" s="27" t="n"/>
       <c r="D286" s="26" t="n"/>
@@ -9743,7 +9763,7 @@
       </c>
     </row>
     <row r="287">
-      <c r="A287" s="41" t="n"/>
+      <c r="A287" s="42" t="n"/>
       <c r="B287" s="27" t="n"/>
       <c r="C287" s="27" t="n"/>
       <c r="D287" s="26" t="n"/>
@@ -9759,7 +9779,7 @@
       </c>
     </row>
     <row r="288">
-      <c r="A288" s="41" t="n"/>
+      <c r="A288" s="42" t="n"/>
       <c r="B288" s="27" t="n"/>
       <c r="C288" s="27" t="n"/>
       <c r="D288" s="26" t="n"/>
@@ -9775,7 +9795,7 @@
       </c>
     </row>
     <row r="289">
-      <c r="A289" s="41" t="n"/>
+      <c r="A289" s="42" t="n"/>
       <c r="B289" s="27" t="n"/>
       <c r="C289" s="27" t="n"/>
       <c r="D289" s="26" t="n"/>
@@ -9791,7 +9811,7 @@
       </c>
     </row>
     <row r="290">
-      <c r="A290" s="41" t="n"/>
+      <c r="A290" s="42" t="n"/>
       <c r="B290" s="27" t="n"/>
       <c r="C290" s="27" t="n"/>
       <c r="D290" s="26" t="n"/>
@@ -9807,7 +9827,7 @@
       </c>
     </row>
     <row r="291">
-      <c r="A291" s="41" t="n"/>
+      <c r="A291" s="42" t="n"/>
       <c r="B291" s="27" t="n"/>
       <c r="C291" s="27" t="n"/>
       <c r="D291" s="26" t="n"/>
@@ -9823,7 +9843,7 @@
       </c>
     </row>
     <row r="292">
-      <c r="A292" s="41" t="n"/>
+      <c r="A292" s="42" t="n"/>
       <c r="B292" s="27" t="n"/>
       <c r="C292" s="27" t="n"/>
       <c r="D292" s="26" t="n"/>
@@ -9839,7 +9859,7 @@
       </c>
     </row>
     <row r="293">
-      <c r="A293" s="41" t="n"/>
+      <c r="A293" s="42" t="n"/>
       <c r="B293" s="27" t="n"/>
       <c r="C293" s="27" t="n"/>
       <c r="D293" s="26" t="n"/>
@@ -9855,7 +9875,7 @@
       </c>
     </row>
     <row r="294">
-      <c r="A294" s="41" t="n"/>
+      <c r="A294" s="42" t="n"/>
       <c r="B294" s="27" t="n"/>
       <c r="C294" s="27" t="n"/>
       <c r="D294" s="26" t="n"/>
@@ -9871,7 +9891,7 @@
       </c>
     </row>
     <row r="295">
-      <c r="A295" s="41" t="n"/>
+      <c r="A295" s="42" t="n"/>
       <c r="B295" s="27" t="n"/>
       <c r="C295" s="27" t="n"/>
       <c r="D295" s="26" t="n"/>
@@ -9887,7 +9907,7 @@
       </c>
     </row>
     <row r="296">
-      <c r="A296" s="41" t="n"/>
+      <c r="A296" s="42" t="n"/>
       <c r="B296" s="27" t="n"/>
       <c r="C296" s="27" t="n"/>
       <c r="D296" s="26" t="n"/>
@@ -9903,7 +9923,7 @@
       </c>
     </row>
     <row r="297">
-      <c r="A297" s="41" t="n"/>
+      <c r="A297" s="42" t="n"/>
       <c r="B297" s="27" t="n"/>
       <c r="C297" s="27" t="n"/>
       <c r="D297" s="26" t="n"/>
@@ -9919,7 +9939,7 @@
       </c>
     </row>
     <row r="298">
-      <c r="A298" s="41" t="n"/>
+      <c r="A298" s="42" t="n"/>
       <c r="B298" s="27" t="n"/>
       <c r="C298" s="27" t="n"/>
       <c r="D298" s="26" t="n"/>
@@ -9935,7 +9955,7 @@
       </c>
     </row>
     <row r="299">
-      <c r="A299" s="41" t="n"/>
+      <c r="A299" s="42" t="n"/>
       <c r="B299" s="27" t="n"/>
       <c r="C299" s="27" t="n"/>
       <c r="D299" s="26" t="n"/>
@@ -9951,7 +9971,7 @@
       </c>
     </row>
     <row r="300">
-      <c r="A300" s="41" t="n"/>
+      <c r="A300" s="42" t="n"/>
       <c r="B300" s="27" t="n"/>
       <c r="C300" s="27" t="n"/>
       <c r="D300" s="26" t="n"/>
@@ -9967,7 +9987,7 @@
       </c>
     </row>
     <row r="301">
-      <c r="A301" s="41" t="n"/>
+      <c r="A301" s="42" t="n"/>
       <c r="B301" s="27" t="n"/>
       <c r="C301" s="27" t="n"/>
       <c r="D301" s="26" t="n"/>
@@ -9983,7 +10003,7 @@
       </c>
     </row>
     <row r="302">
-      <c r="A302" s="41" t="n"/>
+      <c r="A302" s="42" t="n"/>
       <c r="B302" s="27" t="n"/>
       <c r="C302" s="27" t="n"/>
       <c r="D302" s="26" t="n"/>
@@ -9999,7 +10019,7 @@
       </c>
     </row>
     <row r="303">
-      <c r="A303" s="41" t="n"/>
+      <c r="A303" s="42" t="n"/>
       <c r="B303" s="27" t="n"/>
       <c r="C303" s="27" t="n"/>
       <c r="D303" s="26" t="n"/>
@@ -10015,7 +10035,7 @@
       </c>
     </row>
     <row r="304">
-      <c r="A304" s="41" t="n"/>
+      <c r="A304" s="42" t="n"/>
       <c r="B304" s="27" t="n"/>
       <c r="C304" s="27" t="n"/>
       <c r="D304" s="26" t="n"/>
@@ -10031,7 +10051,7 @@
       </c>
     </row>
     <row r="305">
-      <c r="A305" s="41" t="n"/>
+      <c r="A305" s="42" t="n"/>
       <c r="B305" s="27" t="n"/>
       <c r="C305" s="27" t="n"/>
       <c r="D305" s="26" t="n"/>
@@ -10047,7 +10067,7 @@
       </c>
     </row>
     <row r="306">
-      <c r="A306" s="41" t="n"/>
+      <c r="A306" s="42" t="n"/>
       <c r="B306" s="27" t="n"/>
       <c r="C306" s="27" t="n"/>
       <c r="D306" s="26" t="n"/>
@@ -10063,7 +10083,7 @@
       </c>
     </row>
     <row r="307">
-      <c r="A307" s="41" t="n"/>
+      <c r="A307" s="42" t="n"/>
       <c r="B307" s="27" t="n"/>
       <c r="C307" s="27" t="n"/>
       <c r="D307" s="26" t="n"/>
@@ -10079,7 +10099,7 @@
       </c>
     </row>
     <row r="308">
-      <c r="A308" s="41" t="n"/>
+      <c r="A308" s="42" t="n"/>
       <c r="B308" s="27" t="n"/>
       <c r="C308" s="27" t="n"/>
       <c r="D308" s="26" t="n"/>
@@ -10095,7 +10115,7 @@
       </c>
     </row>
     <row r="309">
-      <c r="A309" s="41" t="n"/>
+      <c r="A309" s="42" t="n"/>
       <c r="B309" s="27" t="n"/>
       <c r="C309" s="27" t="n"/>
       <c r="D309" s="26" t="n"/>
@@ -10111,7 +10131,7 @@
       </c>
     </row>
     <row r="310">
-      <c r="A310" s="41" t="n"/>
+      <c r="A310" s="42" t="n"/>
       <c r="B310" s="27" t="n"/>
       <c r="C310" s="27" t="n"/>
       <c r="D310" s="26" t="n"/>
@@ -10127,7 +10147,7 @@
       </c>
     </row>
     <row r="311">
-      <c r="A311" s="41" t="n"/>
+      <c r="A311" s="42" t="n"/>
       <c r="B311" s="27" t="n"/>
       <c r="C311" s="27" t="n"/>
       <c r="D311" s="26" t="n"/>
@@ -10143,7 +10163,7 @@
       </c>
     </row>
     <row r="312">
-      <c r="A312" s="41" t="n"/>
+      <c r="A312" s="42" t="n"/>
       <c r="B312" s="27" t="n"/>
       <c r="C312" s="27" t="n"/>
       <c r="D312" s="26" t="n"/>
@@ -10159,7 +10179,7 @@
       </c>
     </row>
     <row r="313">
-      <c r="A313" s="41" t="n"/>
+      <c r="A313" s="42" t="n"/>
       <c r="B313" s="27" t="n"/>
       <c r="C313" s="27" t="n"/>
       <c r="D313" s="26" t="n"/>
@@ -10175,7 +10195,7 @@
       </c>
     </row>
     <row r="314">
-      <c r="A314" s="41" t="n"/>
+      <c r="A314" s="42" t="n"/>
       <c r="B314" s="27" t="n"/>
       <c r="C314" s="27" t="n"/>
       <c r="D314" s="26" t="n"/>
@@ -10191,7 +10211,7 @@
       </c>
     </row>
     <row r="315">
-      <c r="A315" s="41" t="n"/>
+      <c r="A315" s="42" t="n"/>
       <c r="B315" s="27" t="n"/>
       <c r="C315" s="27" t="n"/>
       <c r="D315" s="26" t="n"/>
@@ -10207,7 +10227,7 @@
       </c>
     </row>
     <row r="316">
-      <c r="A316" s="41" t="n"/>
+      <c r="A316" s="42" t="n"/>
       <c r="B316" s="27" t="n"/>
       <c r="C316" s="27" t="n"/>
       <c r="D316" s="26" t="n"/>
@@ -10223,7 +10243,7 @@
       </c>
     </row>
     <row r="317">
-      <c r="A317" s="41" t="n"/>
+      <c r="A317" s="42" t="n"/>
       <c r="B317" s="27" t="n"/>
       <c r="C317" s="27" t="n"/>
       <c r="D317" s="26" t="n"/>
@@ -10239,7 +10259,7 @@
       </c>
     </row>
     <row r="318">
-      <c r="A318" s="41" t="n"/>
+      <c r="A318" s="42" t="n"/>
       <c r="B318" s="27" t="n"/>
       <c r="C318" s="27" t="n"/>
       <c r="D318" s="26" t="n"/>
@@ -10255,7 +10275,7 @@
       </c>
     </row>
     <row r="319">
-      <c r="A319" s="41" t="n"/>
+      <c r="A319" s="42" t="n"/>
       <c r="B319" s="27" t="n"/>
       <c r="C319" s="27" t="n"/>
       <c r="D319" s="26" t="n"/>
@@ -10271,7 +10291,7 @@
       </c>
     </row>
     <row r="320">
-      <c r="A320" s="41" t="n"/>
+      <c r="A320" s="42" t="n"/>
       <c r="B320" s="27" t="n"/>
       <c r="C320" s="27" t="n"/>
       <c r="D320" s="26" t="n"/>
@@ -10287,7 +10307,7 @@
       </c>
     </row>
     <row r="321">
-      <c r="A321" s="41" t="n"/>
+      <c r="A321" s="42" t="n"/>
       <c r="B321" s="27" t="n"/>
       <c r="C321" s="27" t="n"/>
       <c r="D321" s="26" t="n"/>
@@ -10303,7 +10323,7 @@
       </c>
     </row>
     <row r="322">
-      <c r="A322" s="41" t="n"/>
+      <c r="A322" s="42" t="n"/>
       <c r="B322" s="27" t="n"/>
       <c r="C322" s="27" t="n"/>
       <c r="D322" s="26" t="n"/>
@@ -10319,7 +10339,7 @@
       </c>
     </row>
     <row r="323">
-      <c r="A323" s="41" t="n"/>
+      <c r="A323" s="42" t="n"/>
       <c r="B323" s="27" t="n"/>
       <c r="C323" s="27" t="n"/>
       <c r="D323" s="26" t="n"/>
@@ -10335,7 +10355,7 @@
       </c>
     </row>
     <row r="324">
-      <c r="A324" s="41" t="n"/>
+      <c r="A324" s="42" t="n"/>
       <c r="B324" s="27" t="n"/>
       <c r="C324" s="27" t="n"/>
       <c r="D324" s="26" t="n"/>
@@ -10351,7 +10371,7 @@
       </c>
     </row>
     <row r="325">
-      <c r="A325" s="41" t="n"/>
+      <c r="A325" s="42" t="n"/>
       <c r="B325" s="27" t="n"/>
       <c r="C325" s="27" t="n"/>
       <c r="D325" s="26" t="n"/>
@@ -10367,7 +10387,7 @@
       </c>
     </row>
     <row r="326">
-      <c r="A326" s="41" t="n"/>
+      <c r="A326" s="42" t="n"/>
       <c r="B326" s="27" t="n"/>
       <c r="C326" s="27" t="n"/>
       <c r="D326" s="26" t="n"/>
@@ -10383,7 +10403,7 @@
       </c>
     </row>
     <row r="327">
-      <c r="A327" s="41" t="n"/>
+      <c r="A327" s="42" t="n"/>
       <c r="B327" s="27" t="n"/>
       <c r="C327" s="27" t="n"/>
       <c r="D327" s="26" t="n"/>
@@ -10399,7 +10419,7 @@
       </c>
     </row>
     <row r="328">
-      <c r="A328" s="41" t="n"/>
+      <c r="A328" s="42" t="n"/>
       <c r="B328" s="27" t="n"/>
       <c r="C328" s="27" t="n"/>
       <c r="D328" s="26" t="n"/>
@@ -10415,7 +10435,7 @@
       </c>
     </row>
     <row r="329">
-      <c r="A329" s="41" t="n"/>
+      <c r="A329" s="42" t="n"/>
       <c r="B329" s="27" t="n"/>
       <c r="C329" s="27" t="n"/>
       <c r="D329" s="26" t="n"/>
@@ -10431,7 +10451,7 @@
       </c>
     </row>
     <row r="330">
-      <c r="A330" s="41" t="n"/>
+      <c r="A330" s="42" t="n"/>
       <c r="B330" s="27" t="n"/>
       <c r="C330" s="27" t="n"/>
       <c r="D330" s="26" t="n"/>
@@ -10447,7 +10467,7 @@
       </c>
     </row>
     <row r="331">
-      <c r="A331" s="41" t="n"/>
+      <c r="A331" s="42" t="n"/>
       <c r="B331" s="27" t="n"/>
       <c r="C331" s="27" t="n"/>
       <c r="D331" s="26" t="n"/>
@@ -10463,7 +10483,7 @@
       </c>
     </row>
     <row r="332">
-      <c r="A332" s="41" t="n"/>
+      <c r="A332" s="42" t="n"/>
       <c r="B332" s="27" t="n"/>
       <c r="C332" s="27" t="n"/>
       <c r="D332" s="26" t="n"/>
@@ -10479,7 +10499,7 @@
       </c>
     </row>
     <row r="333">
-      <c r="A333" s="41" t="n"/>
+      <c r="A333" s="42" t="n"/>
       <c r="B333" s="27" t="n"/>
       <c r="C333" s="27" t="n"/>
       <c r="D333" s="26" t="n"/>
@@ -10495,7 +10515,7 @@
       </c>
     </row>
     <row r="334">
-      <c r="A334" s="41" t="n"/>
+      <c r="A334" s="42" t="n"/>
       <c r="B334" s="27" t="n"/>
       <c r="C334" s="27" t="n"/>
       <c r="D334" s="26" t="n"/>
@@ -10511,7 +10531,7 @@
       </c>
     </row>
     <row r="335">
-      <c r="A335" s="41" t="n"/>
+      <c r="A335" s="42" t="n"/>
       <c r="B335" s="27" t="n"/>
       <c r="C335" s="27" t="n"/>
       <c r="D335" s="26" t="n"/>
@@ -10527,7 +10547,7 @@
       </c>
     </row>
     <row r="336">
-      <c r="A336" s="41" t="n"/>
+      <c r="A336" s="42" t="n"/>
       <c r="B336" s="27" t="n"/>
       <c r="C336" s="27" t="n"/>
       <c r="D336" s="26" t="n"/>
@@ -10543,7 +10563,7 @@
       </c>
     </row>
     <row r="337">
-      <c r="A337" s="41" t="n"/>
+      <c r="A337" s="42" t="n"/>
       <c r="B337" s="27" t="n"/>
       <c r="C337" s="27" t="n"/>
       <c r="D337" s="26" t="n"/>
@@ -10559,7 +10579,7 @@
       </c>
     </row>
     <row r="338">
-      <c r="A338" s="41" t="n"/>
+      <c r="A338" s="42" t="n"/>
       <c r="B338" s="27" t="n"/>
       <c r="C338" s="27" t="n"/>
       <c r="D338" s="26" t="n"/>
@@ -10575,7 +10595,7 @@
       </c>
     </row>
     <row r="339">
-      <c r="A339" s="41" t="n"/>
+      <c r="A339" s="42" t="n"/>
       <c r="B339" s="27" t="n"/>
       <c r="C339" s="27" t="n"/>
       <c r="D339" s="26" t="n"/>
@@ -10591,7 +10611,7 @@
       </c>
     </row>
     <row r="340">
-      <c r="A340" s="41" t="n"/>
+      <c r="A340" s="42" t="n"/>
       <c r="B340" s="27" t="n"/>
       <c r="C340" s="27" t="n"/>
       <c r="D340" s="26" t="n"/>
@@ -10607,7 +10627,7 @@
       </c>
     </row>
     <row r="341">
-      <c r="A341" s="41" t="n"/>
+      <c r="A341" s="42" t="n"/>
       <c r="B341" s="27" t="n"/>
       <c r="C341" s="27" t="n"/>
       <c r="D341" s="26" t="n"/>
@@ -10623,7 +10643,7 @@
       </c>
     </row>
     <row r="342">
-      <c r="A342" s="41" t="n"/>
+      <c r="A342" s="42" t="n"/>
       <c r="B342" s="27" t="n"/>
       <c r="C342" s="27" t="n"/>
       <c r="D342" s="26" t="n"/>
@@ -10639,7 +10659,7 @@
       </c>
     </row>
     <row r="343">
-      <c r="A343" s="41" t="n"/>
+      <c r="A343" s="42" t="n"/>
       <c r="B343" s="27" t="n"/>
       <c r="C343" s="27" t="n"/>
       <c r="D343" s="26" t="n"/>
@@ -10655,7 +10675,7 @@
       </c>
     </row>
     <row r="344">
-      <c r="A344" s="41" t="n"/>
+      <c r="A344" s="42" t="n"/>
       <c r="B344" s="27" t="n"/>
       <c r="C344" s="27" t="n"/>
       <c r="D344" s="26" t="n"/>
@@ -10671,7 +10691,7 @@
       </c>
     </row>
     <row r="345">
-      <c r="A345" s="41" t="n"/>
+      <c r="A345" s="42" t="n"/>
       <c r="B345" s="27" t="n"/>
       <c r="C345" s="27" t="n"/>
       <c r="D345" s="26" t="n"/>
@@ -10687,7 +10707,7 @@
       </c>
     </row>
     <row r="346">
-      <c r="A346" s="41" t="n"/>
+      <c r="A346" s="42" t="n"/>
       <c r="B346" s="27" t="n"/>
       <c r="C346" s="27" t="n"/>
       <c r="D346" s="26" t="n"/>
@@ -10703,7 +10723,7 @@
       </c>
     </row>
     <row r="347">
-      <c r="A347" s="41" t="n"/>
+      <c r="A347" s="42" t="n"/>
       <c r="B347" s="27" t="n"/>
       <c r="C347" s="27" t="n"/>
       <c r="D347" s="26" t="n"/>
@@ -10719,7 +10739,7 @@
       </c>
     </row>
     <row r="348">
-      <c r="A348" s="41" t="n"/>
+      <c r="A348" s="42" t="n"/>
       <c r="B348" s="27" t="n"/>
       <c r="C348" s="27" t="n"/>
       <c r="D348" s="26" t="n"/>
@@ -10735,7 +10755,7 @@
       </c>
     </row>
     <row r="349">
-      <c r="A349" s="41" t="n"/>
+      <c r="A349" s="42" t="n"/>
       <c r="B349" s="27" t="n"/>
       <c r="C349" s="27" t="n"/>
       <c r="D349" s="26" t="n"/>
@@ -10751,7 +10771,7 @@
       </c>
     </row>
     <row r="350">
-      <c r="A350" s="41" t="n"/>
+      <c r="A350" s="42" t="n"/>
       <c r="B350" s="27" t="n"/>
       <c r="C350" s="27" t="n"/>
       <c r="D350" s="26" t="n"/>
@@ -10767,7 +10787,7 @@
       </c>
     </row>
     <row r="351">
-      <c r="A351" s="41" t="n"/>
+      <c r="A351" s="42" t="n"/>
       <c r="B351" s="27" t="n"/>
       <c r="C351" s="27" t="n"/>
       <c r="D351" s="26" t="n"/>
@@ -10783,7 +10803,7 @@
       </c>
     </row>
     <row r="352">
-      <c r="A352" s="41" t="n"/>
+      <c r="A352" s="42" t="n"/>
       <c r="B352" s="27" t="n"/>
       <c r="C352" s="27" t="n"/>
       <c r="D352" s="26" t="n"/>
@@ -10799,7 +10819,7 @@
       </c>
     </row>
     <row r="353">
-      <c r="A353" s="41" t="n"/>
+      <c r="A353" s="42" t="n"/>
       <c r="B353" s="27" t="n"/>
       <c r="C353" s="27" t="n"/>
       <c r="D353" s="26" t="n"/>
@@ -10815,7 +10835,7 @@
       </c>
     </row>
     <row r="354">
-      <c r="A354" s="41" t="n"/>
+      <c r="A354" s="42" t="n"/>
       <c r="B354" s="27" t="n"/>
       <c r="C354" s="27" t="n"/>
       <c r="D354" s="26" t="n"/>
@@ -10831,7 +10851,7 @@
       </c>
     </row>
     <row r="355">
-      <c r="A355" s="41" t="n"/>
+      <c r="A355" s="42" t="n"/>
       <c r="B355" s="27" t="n"/>
       <c r="C355" s="27" t="n"/>
       <c r="D355" s="26" t="n"/>
@@ -10847,7 +10867,7 @@
       </c>
     </row>
     <row r="356">
-      <c r="A356" s="41" t="n"/>
+      <c r="A356" s="42" t="n"/>
       <c r="B356" s="27" t="n"/>
       <c r="C356" s="27" t="n"/>
       <c r="D356" s="26" t="n"/>
@@ -10863,7 +10883,7 @@
       </c>
     </row>
     <row r="357">
-      <c r="A357" s="41" t="n"/>
+      <c r="A357" s="42" t="n"/>
       <c r="B357" s="27" t="n"/>
       <c r="C357" s="27" t="n"/>
       <c r="D357" s="26" t="n"/>
@@ -10879,7 +10899,7 @@
       </c>
     </row>
     <row r="358">
-      <c r="A358" s="41" t="n"/>
+      <c r="A358" s="42" t="n"/>
       <c r="B358" s="27" t="n"/>
       <c r="C358" s="27" t="n"/>
       <c r="D358" s="26" t="n"/>
@@ -10895,7 +10915,7 @@
       </c>
     </row>
     <row r="359">
-      <c r="A359" s="41" t="n"/>
+      <c r="A359" s="42" t="n"/>
       <c r="B359" s="27" t="n"/>
       <c r="C359" s="27" t="n"/>
       <c r="D359" s="26" t="n"/>
@@ -10911,7 +10931,7 @@
       </c>
     </row>
     <row r="360">
-      <c r="A360" s="41" t="n"/>
+      <c r="A360" s="42" t="n"/>
       <c r="B360" s="27" t="n"/>
       <c r="C360" s="27" t="n"/>
       <c r="D360" s="26" t="n"/>
@@ -10927,7 +10947,7 @@
       </c>
     </row>
     <row r="361">
-      <c r="A361" s="41" t="n"/>
+      <c r="A361" s="42" t="n"/>
       <c r="B361" s="27" t="n"/>
       <c r="C361" s="27" t="n"/>
       <c r="D361" s="26" t="n"/>
@@ -10943,7 +10963,7 @@
       </c>
     </row>
     <row r="362">
-      <c r="A362" s="41" t="n"/>
+      <c r="A362" s="42" t="n"/>
       <c r="B362" s="27" t="n"/>
       <c r="C362" s="27" t="n"/>
       <c r="D362" s="26" t="n"/>
@@ -10959,7 +10979,7 @@
       </c>
     </row>
     <row r="363">
-      <c r="A363" s="41" t="n"/>
+      <c r="A363" s="42" t="n"/>
       <c r="B363" s="27" t="n"/>
       <c r="C363" s="27" t="n"/>
       <c r="D363" s="26" t="n"/>
@@ -10975,7 +10995,7 @@
       </c>
     </row>
     <row r="364">
-      <c r="A364" s="41" t="n"/>
+      <c r="A364" s="42" t="n"/>
       <c r="B364" s="27" t="n"/>
       <c r="C364" s="27" t="n"/>
       <c r="D364" s="26" t="n"/>
@@ -10991,7 +11011,7 @@
       </c>
     </row>
     <row r="365">
-      <c r="A365" s="41" t="n"/>
+      <c r="A365" s="42" t="n"/>
       <c r="B365" s="27" t="n"/>
       <c r="C365" s="27" t="n"/>
       <c r="D365" s="26" t="n"/>
@@ -11007,7 +11027,7 @@
       </c>
     </row>
     <row r="366">
-      <c r="A366" s="41" t="n"/>
+      <c r="A366" s="42" t="n"/>
       <c r="B366" s="27" t="n"/>
       <c r="C366" s="27" t="n"/>
       <c r="D366" s="26" t="n"/>
@@ -11023,7 +11043,7 @@
       </c>
     </row>
     <row r="367">
-      <c r="A367" s="41" t="n"/>
+      <c r="A367" s="42" t="n"/>
       <c r="B367" s="27" t="n"/>
       <c r="C367" s="27" t="n"/>
       <c r="D367" s="26" t="n"/>
@@ -11039,7 +11059,7 @@
       </c>
     </row>
     <row r="368">
-      <c r="A368" s="41" t="n"/>
+      <c r="A368" s="42" t="n"/>
       <c r="B368" s="27" t="n"/>
       <c r="C368" s="27" t="n"/>
       <c r="D368" s="26" t="n"/>
@@ -11055,7 +11075,7 @@
       </c>
     </row>
     <row r="369">
-      <c r="A369" s="41" t="n"/>
+      <c r="A369" s="42" t="n"/>
       <c r="B369" s="27" t="n"/>
       <c r="C369" s="27" t="n"/>
       <c r="D369" s="26" t="n"/>
@@ -11071,7 +11091,7 @@
       </c>
     </row>
     <row r="370">
-      <c r="A370" s="41" t="n"/>
+      <c r="A370" s="42" t="n"/>
       <c r="B370" s="27" t="n"/>
       <c r="C370" s="27" t="n"/>
       <c r="D370" s="26" t="n"/>
@@ -11087,7 +11107,7 @@
       </c>
     </row>
     <row r="371">
-      <c r="A371" s="41" t="n"/>
+      <c r="A371" s="42" t="n"/>
       <c r="B371" s="27" t="n"/>
       <c r="C371" s="27" t="n"/>
       <c r="D371" s="26" t="n"/>
@@ -11103,7 +11123,7 @@
       </c>
     </row>
     <row r="372">
-      <c r="A372" s="41" t="n"/>
+      <c r="A372" s="42" t="n"/>
       <c r="B372" s="27" t="n"/>
       <c r="C372" s="27" t="n"/>
       <c r="D372" s="26" t="n"/>
@@ -11119,7 +11139,7 @@
       </c>
     </row>
     <row r="373">
-      <c r="A373" s="41" t="n"/>
+      <c r="A373" s="42" t="n"/>
       <c r="B373" s="27" t="n"/>
       <c r="C373" s="27" t="n"/>
       <c r="D373" s="26" t="n"/>
@@ -11135,7 +11155,7 @@
       </c>
     </row>
     <row r="374">
-      <c r="A374" s="41" t="n"/>
+      <c r="A374" s="42" t="n"/>
       <c r="B374" s="27" t="n"/>
       <c r="C374" s="27" t="n"/>
       <c r="D374" s="26" t="n"/>
@@ -11151,7 +11171,7 @@
       </c>
     </row>
     <row r="375">
-      <c r="A375" s="41" t="n"/>
+      <c r="A375" s="42" t="n"/>
       <c r="B375" s="27" t="n"/>
       <c r="C375" s="27" t="n"/>
       <c r="D375" s="26" t="n"/>
@@ -11167,7 +11187,7 @@
       </c>
     </row>
     <row r="376">
-      <c r="A376" s="41" t="n"/>
+      <c r="A376" s="42" t="n"/>
       <c r="B376" s="27" t="n"/>
       <c r="C376" s="27" t="n"/>
       <c r="D376" s="26" t="n"/>
@@ -11183,7 +11203,7 @@
       </c>
     </row>
     <row r="377">
-      <c r="A377" s="41" t="n"/>
+      <c r="A377" s="42" t="n"/>
       <c r="B377" s="27" t="n"/>
       <c r="C377" s="27" t="n"/>
       <c r="D377" s="26" t="n"/>
@@ -11199,7 +11219,7 @@
       </c>
     </row>
     <row r="378">
-      <c r="A378" s="41" t="n"/>
+      <c r="A378" s="42" t="n"/>
       <c r="B378" s="27" t="n"/>
       <c r="C378" s="27" t="n"/>
       <c r="D378" s="26" t="n"/>
@@ -11215,7 +11235,7 @@
       </c>
     </row>
     <row r="379">
-      <c r="A379" s="41" t="n"/>
+      <c r="A379" s="42" t="n"/>
       <c r="B379" s="27" t="n"/>
       <c r="C379" s="27" t="n"/>
       <c r="D379" s="26" t="n"/>
@@ -11231,7 +11251,7 @@
       </c>
     </row>
     <row r="380">
-      <c r="A380" s="41" t="n"/>
+      <c r="A380" s="42" t="n"/>
       <c r="B380" s="27" t="n"/>
       <c r="C380" s="27" t="n"/>
       <c r="D380" s="26" t="n"/>
@@ -11247,7 +11267,7 @@
       </c>
     </row>
     <row r="381">
-      <c r="A381" s="41" t="n"/>
+      <c r="A381" s="42" t="n"/>
       <c r="B381" s="27" t="n"/>
       <c r="C381" s="27" t="n"/>
       <c r="D381" s="26" t="n"/>
@@ -11263,7 +11283,7 @@
       </c>
     </row>
     <row r="382">
-      <c r="A382" s="41" t="n"/>
+      <c r="A382" s="42" t="n"/>
       <c r="B382" s="27" t="n"/>
       <c r="C382" s="27" t="n"/>
       <c r="D382" s="26" t="n"/>
@@ -11279,7 +11299,7 @@
       </c>
     </row>
     <row r="383">
-      <c r="A383" s="41" t="n"/>
+      <c r="A383" s="42" t="n"/>
       <c r="B383" s="27" t="n"/>
       <c r="C383" s="27" t="n"/>
       <c r="D383" s="26" t="n"/>
@@ -11295,7 +11315,7 @@
       </c>
     </row>
     <row r="384">
-      <c r="A384" s="41" t="n"/>
+      <c r="A384" s="42" t="n"/>
       <c r="B384" s="27" t="n"/>
       <c r="C384" s="27" t="n"/>
       <c r="D384" s="26" t="n"/>
@@ -11311,7 +11331,7 @@
       </c>
     </row>
     <row r="385">
-      <c r="A385" s="41" t="n"/>
+      <c r="A385" s="42" t="n"/>
       <c r="B385" s="27" t="n"/>
       <c r="C385" s="27" t="n"/>
       <c r="D385" s="26" t="n"/>
@@ -11327,7 +11347,7 @@
       </c>
     </row>
     <row r="386">
-      <c r="A386" s="41" t="n"/>
+      <c r="A386" s="42" t="n"/>
       <c r="B386" s="27" t="n"/>
       <c r="C386" s="27" t="n"/>
       <c r="D386" s="26" t="n"/>
@@ -11343,7 +11363,7 @@
       </c>
     </row>
     <row r="387">
-      <c r="A387" s="41" t="n"/>
+      <c r="A387" s="42" t="n"/>
       <c r="B387" s="27" t="n"/>
       <c r="C387" s="27" t="n"/>
       <c r="D387" s="26" t="n"/>
@@ -11359,7 +11379,7 @@
       </c>
     </row>
     <row r="388">
-      <c r="A388" s="41" t="n"/>
+      <c r="A388" s="42" t="n"/>
       <c r="B388" s="27" t="n"/>
       <c r="C388" s="27" t="n"/>
       <c r="D388" s="26" t="n"/>
@@ -11375,7 +11395,7 @@
       </c>
     </row>
     <row r="389">
-      <c r="A389" s="41" t="n"/>
+      <c r="A389" s="42" t="n"/>
       <c r="B389" s="27" t="n"/>
       <c r="C389" s="27" t="n"/>
       <c r="D389" s="26" t="n"/>
@@ -11391,7 +11411,7 @@
       </c>
     </row>
     <row r="390">
-      <c r="A390" s="41" t="n"/>
+      <c r="A390" s="42" t="n"/>
       <c r="B390" s="27" t="n"/>
       <c r="C390" s="27" t="n"/>
       <c r="D390" s="26" t="n"/>
@@ -11407,7 +11427,7 @@
       </c>
     </row>
     <row r="391">
-      <c r="A391" s="41" t="n"/>
+      <c r="A391" s="42" t="n"/>
       <c r="B391" s="27" t="n"/>
       <c r="C391" s="27" t="n"/>
       <c r="D391" s="26" t="n"/>
@@ -11423,7 +11443,7 @@
       </c>
     </row>
     <row r="392">
-      <c r="A392" s="41" t="n"/>
+      <c r="A392" s="42" t="n"/>
       <c r="B392" s="27" t="n"/>
       <c r="C392" s="27" t="n"/>
       <c r="D392" s="26" t="n"/>
@@ -11439,7 +11459,7 @@
       </c>
     </row>
     <row r="393">
-      <c r="A393" s="41" t="n"/>
+      <c r="A393" s="42" t="n"/>
       <c r="B393" s="27" t="n"/>
       <c r="C393" s="27" t="n"/>
       <c r="D393" s="26" t="n"/>
@@ -11455,7 +11475,7 @@
       </c>
     </row>
     <row r="394">
-      <c r="A394" s="41" t="n"/>
+      <c r="A394" s="42" t="n"/>
       <c r="B394" s="27" t="n"/>
       <c r="C394" s="27" t="n"/>
       <c r="D394" s="26" t="n"/>
@@ -11471,7 +11491,7 @@
       </c>
     </row>
     <row r="395">
-      <c r="A395" s="41" t="n"/>
+      <c r="A395" s="42" t="n"/>
       <c r="B395" s="27" t="n"/>
       <c r="C395" s="27" t="n"/>
       <c r="D395" s="26" t="n"/>
@@ -11487,7 +11507,7 @@
       </c>
     </row>
     <row r="396">
-      <c r="A396" s="41" t="n"/>
+      <c r="A396" s="42" t="n"/>
       <c r="B396" s="27" t="n"/>
       <c r="C396" s="27" t="n"/>
       <c r="D396" s="26" t="n"/>
@@ -11503,7 +11523,7 @@
       </c>
     </row>
     <row r="397">
-      <c r="A397" s="41" t="n"/>
+      <c r="A397" s="42" t="n"/>
       <c r="B397" s="27" t="n"/>
       <c r="C397" s="27" t="n"/>
       <c r="D397" s="26" t="n"/>
@@ -11519,7 +11539,7 @@
       </c>
     </row>
     <row r="398">
-      <c r="A398" s="41" t="n"/>
+      <c r="A398" s="42" t="n"/>
       <c r="B398" s="27" t="n"/>
       <c r="C398" s="27" t="n"/>
       <c r="D398" s="26" t="n"/>
@@ -11535,7 +11555,7 @@
       </c>
     </row>
     <row r="399">
-      <c r="A399" s="41" t="n"/>
+      <c r="A399" s="42" t="n"/>
       <c r="B399" s="27" t="n"/>
       <c r="C399" s="27" t="n"/>
       <c r="D399" s="26" t="n"/>
@@ -11551,7 +11571,7 @@
       </c>
     </row>
     <row r="400">
-      <c r="A400" s="41" t="n"/>
+      <c r="A400" s="42" t="n"/>
       <c r="B400" s="27" t="n"/>
       <c r="C400" s="27" t="n"/>
       <c r="D400" s="26" t="n"/>
@@ -11567,7 +11587,7 @@
       </c>
     </row>
     <row r="401">
-      <c r="A401" s="41" t="n"/>
+      <c r="A401" s="42" t="n"/>
       <c r="B401" s="27" t="n"/>
       <c r="C401" s="27" t="n"/>
       <c r="D401" s="26" t="n"/>
@@ -11583,7 +11603,7 @@
       </c>
     </row>
     <row r="402">
-      <c r="A402" s="41" t="n"/>
+      <c r="A402" s="42" t="n"/>
       <c r="B402" s="27" t="n"/>
       <c r="C402" s="27" t="n"/>
       <c r="D402" s="26" t="n"/>
@@ -11599,7 +11619,7 @@
       </c>
     </row>
     <row r="403">
-      <c r="A403" s="41" t="n"/>
+      <c r="A403" s="42" t="n"/>
       <c r="B403" s="27" t="n"/>
       <c r="C403" s="27" t="n"/>
       <c r="D403" s="26" t="n"/>
@@ -11615,7 +11635,7 @@
       </c>
     </row>
     <row r="404">
-      <c r="A404" s="41" t="n"/>
+      <c r="A404" s="42" t="n"/>
       <c r="B404" s="27" t="n"/>
       <c r="C404" s="27" t="n"/>
       <c r="D404" s="26" t="n"/>
@@ -11646,7 +11666,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="5">
-    <dataValidation sqref="B5:B404" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="B5:B404" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>=OFFSET(Config!$A$15,0,0,MAX(1,COUNTA(Config!$A$15:$A$20)),1)</formula1>
     </dataValidation>
     <dataValidation sqref="C5:C404" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
@@ -11655,10 +11675,10 @@
     <dataValidation sqref="F5:F404" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>"1º trimestre,2º trimestre,3º trimestre,4º trimestre"</formula1>
     </dataValidation>
-    <dataValidation sqref="A5:A404" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="date" operator="greaterThan">
+    <dataValidation sqref="A5:A404" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="date" operator="greaterThan">
       <formula1>1</formula1>
     </dataValidation>
-    <dataValidation sqref="E5:E404" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="decimal" operator="greaterThanOrEqual">
+    <dataValidation sqref="E5:E404" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="decimal" operator="greaterThanOrEqual">
       <formula1>0</formula1>
     </dataValidation>
   </dataValidations>

--- a/projetos/gestao-ia-planilhas/produto/kit-medicos/11-repasse-e-pro-labore.xlsx
+++ b/projetos/gestao-ia-planilhas/produto/kit-medicos/11-repasse-e-pro-labore.xlsx
@@ -1715,7 +1715,7 @@
       </c>
       <c r="H29" s="19">
         <f>IF(Config!$A$15="","",SUM($G$39:$G$42)*Config!$B$15)</f>
-        <v>3204.435</v>
+        <v>3204.4375</v>
       </c>
       <c r="I29" s="19">
         <f>IF(Config!$A$15="","",SUMIFS(Retiradas!$E$5:$E$404,Retiradas!$B$5:$B$404,Config!$A$15,Retiradas!$C$5:$C$404,"Distribuição de lucro",Retiradas!$G$5:$G$404,"&lt;="&amp;Config!$B$7,Retiradas!$H$5:$H$404,Config!$B$5))</f>
@@ -1757,7 +1757,7 @@
       </c>
       <c r="H30" s="19">
         <f>IF(Config!$A$16="","",SUM($G$39:$G$42)*Config!$B$16)</f>
-        <v>3204.435</v>
+        <v>3204.4375</v>
       </c>
       <c r="I30" s="19">
         <f>IF(Config!$A$16="","",SUMIFS(Retiradas!$E$5:$E$404,Retiradas!$B$5:$B$404,Config!$A$16,Retiradas!$C$5:$C$404,"Distribuição de lucro",Retiradas!$G$5:$G$404,"&lt;="&amp;Config!$B$7,Retiradas!$H$5:$H$404,Config!$B$5))</f>
@@ -2010,7 +2010,7 @@
       </c>
       <c r="C39" s="19">
         <f>SUM('Resultado mensal'!C5:C7)</f>
-        <v>53443.72</v>
+        <v>53443.73</v>
       </c>
       <c r="D39" s="19">
         <f>SUM('Resultado mensal'!D5:D7)</f>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="E39" s="19">
         <f>SUM('Resultado mensal'!E5:E7)</f>
-        <v>-15943.72</v>
+        <v>-15943.73</v>
       </c>
       <c r="F39" s="24" t="str">
         <f>IF(AND(Config!$B$12&gt;=DATE(Config!$B$5,4,1),AND(COUNT('Resultado mensal'!B5:B7)&gt;=3,COUNT('Resultado mensal'!C5:C7)&gt;=3,COUNT('Resultado mensal'!D5:D7)&gt;=3)),"Sim","Em andamento")</f>
@@ -2049,7 +2049,7 @@
       </c>
       <c r="C40" s="19">
         <f>SUM('Resultado mensal'!C8:C10)</f>
-        <v>65957.26</v>
+        <v>65957.25</v>
       </c>
       <c r="D40" s="19">
         <f>SUM('Resultado mensal'!D8:D10)</f>
@@ -2057,7 +2057,7 @@
       </c>
       <c r="E40" s="19">
         <f>SUM('Resultado mensal'!E8:E10)</f>
-        <v>12817.74</v>
+        <v>12817.75</v>
       </c>
       <c r="F40" s="24" t="str">
         <f>IF(AND(Config!$B$12&gt;=DATE(Config!$B$5,7,1),AND(COUNT('Resultado mensal'!B8:B10)&gt;=3,COUNT('Resultado mensal'!C8:C10)&gt;=3,COUNT('Resultado mensal'!D8:D10)&gt;=3)),"Sim","Em andamento")</f>
@@ -2065,7 +2065,7 @@
       </c>
       <c r="G40" s="20">
         <f>IF(AND(F40="Sim",E40&gt;=Config!$B$10),E40*Config!$B$9,0)</f>
-        <v>6408.87</v>
+        <v>6408.875</v>
       </c>
       <c r="H40" s="19">
         <f>SUMIFS(Retiradas!$E$5:$E$404,Retiradas!$C$5:$C$404,"Distribuição de lucro",Retiradas!$F$5:$F$404,A40,Retiradas!$H$5:$H$404,Config!$B$5)</f>
@@ -4672,7 +4672,7 @@
         <v>25650</v>
       </c>
       <c r="C6" s="31" t="n">
-        <v>17610.54</v>
+        <v>17610.55</v>
       </c>
       <c r="D6" s="44">
         <f>IF(AND(B6="",C6=""),0,Config!$C$21)</f>
@@ -4680,7 +4680,7 @@
       </c>
       <c r="E6" s="44">
         <f>B6-C6-D6</f>
-        <v>-9960.54</v>
+        <v>-9960.55</v>
       </c>
       <c r="F6" s="24" t="inlineStr">
         <is>
@@ -4724,7 +4724,7 @@
         <v>40155</v>
       </c>
       <c r="C8" s="31" t="n">
-        <v>22254.1</v>
+        <v>22254.11</v>
       </c>
       <c r="D8" s="44">
         <f>IF(AND(B8="",C8=""),0,Config!$C$21)</f>
@@ -4732,7 +4732,7 @@
       </c>
       <c r="E8" s="44">
         <f>B8-C8-D8</f>
-        <v>-99.0999999999985</v>
+        <v>-99.1100000000006</v>
       </c>
       <c r="F8" s="24" t="inlineStr">
         <is>
@@ -4750,7 +4750,7 @@
         <v>45380</v>
       </c>
       <c r="C9" s="31" t="n">
-        <v>21500.29</v>
+        <v>21500.27</v>
       </c>
       <c r="D9" s="44">
         <f>IF(AND(B9="",C9=""),0,Config!$C$21)</f>
@@ -4758,7 +4758,7 @@
       </c>
       <c r="E9" s="44">
         <f>B9-C9-D9</f>
-        <v>5879.71</v>
+        <v>5879.73</v>
       </c>
       <c r="F9" s="24" t="inlineStr">
         <is>
@@ -4802,7 +4802,7 @@
         <v>44471</v>
       </c>
       <c r="C11" s="31" t="n">
-        <v>21562.6</v>
+        <v>21562.61</v>
       </c>
       <c r="D11" s="44">
         <f>IF(AND(B11="",C11=""),0,Config!$C$21)</f>
@@ -4810,7 +4810,7 @@
       </c>
       <c r="E11" s="44">
         <f>B11-C11-D11</f>
-        <v>4908.4</v>
+        <v>4908.39</v>
       </c>
       <c r="F11" s="24" t="inlineStr">
         <is>
@@ -4828,7 +4828,7 @@
         <v>55841</v>
       </c>
       <c r="C12" s="31" t="n">
-        <v>22248.61</v>
+        <v>22248.6</v>
       </c>
       <c r="D12" s="44">
         <f>IF(AND(B12="",C12=""),0,Config!$C$21)</f>
@@ -4836,7 +4836,7 @@
       </c>
       <c r="E12" s="44">
         <f>B12-C12-D12</f>
-        <v>15592.39</v>
+        <v>15592.4</v>
       </c>
       <c r="F12" s="24" t="inlineStr">
         <is>

--- a/projetos/gestao-ia-planilhas/produto/kit-medicos/11-repasse-e-pro-labore.xlsx
+++ b/projetos/gestao-ia-planilhas/produto/kit-medicos/11-repasse-e-pro-labore.xlsx
@@ -761,6 +761,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="46" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -901,7 +902,7 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Faça upload no Google Drive e abra com o Google Sheets. Fórmulas, listas, cores, semáforos e gráficos funcionam: as regras de cor que dependem do mês escolhido em Config usam INDIRECT, que é a forma que o Sheets aceita para regra condicional apontar para outra aba.</t>
+          <t>Faça upload no Google Drive e abra com o Google Sheets. Fórmulas, listas, cores e semáforos funcionam: as regras de cor que dependem do mês escolhido em Config usam INDIRECT, que é a forma que o Sheets aceita para regra condicional apontar para outra aba.</t>
         </is>
       </c>
     </row>
